--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY344"/>
+  <dimension ref="A1:AY346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24342,42 +24342,42 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>135350579</v>
+        <v>135356982</v>
       </c>
       <c r="B214" t="n">
-        <v>78393</v>
+        <v>83353</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>600238</v>
+        <v>600207</v>
       </c>
       <c r="R214" t="n">
         <v>7331365</v>
@@ -24412,7 +24412,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24431,18 +24431,24 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
+      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
@@ -24453,48 +24459,48 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>135350596</v>
+        <v>135356988</v>
       </c>
       <c r="B215" t="n">
-        <v>78393</v>
+        <v>83353</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>600062</v>
+        <v>600154</v>
       </c>
       <c r="R215" t="n">
-        <v>7331231</v>
+        <v>7331325</v>
       </c>
       <c r="S215" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24523,7 +24529,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -24533,7 +24539,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24542,18 +24548,19 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
+      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
@@ -24564,7 +24571,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>135350679</v>
+        <v>135350579</v>
       </c>
       <c r="B216" t="n">
         <v>78393</v>
@@ -24599,10 +24606,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>600102</v>
+        <v>600238</v>
       </c>
       <c r="R216" t="n">
-        <v>7331208</v>
+        <v>7331365</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -24634,7 +24641,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -24644,7 +24651,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24675,7 +24682,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>135356980</v>
+        <v>135350596</v>
       </c>
       <c r="B217" t="n">
         <v>78393</v>
@@ -24706,17 +24713,17 @@
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>600207</v>
+        <v>600062</v>
       </c>
       <c r="R217" t="n">
-        <v>7331365</v>
+        <v>7331231</v>
       </c>
       <c r="S217" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24745,7 +24752,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24755,7 +24762,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24770,12 +24777,12 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
@@ -24786,7 +24793,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>135357075</v>
+        <v>135350679</v>
       </c>
       <c r="B218" t="n">
         <v>78393</v>
@@ -24817,14 +24824,14 @@
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>600111</v>
+        <v>600102</v>
       </c>
       <c r="R218" t="n">
-        <v>7331594</v>
+        <v>7331208</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24856,7 +24863,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24866,7 +24873,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24881,12 +24888,12 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -24897,45 +24904,45 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>135361449</v>
+        <v>135356980</v>
       </c>
       <c r="B219" t="n">
-        <v>89354</v>
+        <v>78393</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>510</v>
+        <v>314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>600168</v>
+        <v>600207</v>
       </c>
       <c r="R219" t="n">
-        <v>7331283</v>
+        <v>7331365</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24967,7 +24974,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24977,7 +24984,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24992,12 +24999,12 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
@@ -25008,10 +25015,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>135350594</v>
+        <v>135357075</v>
       </c>
       <c r="B220" t="n">
-        <v>79442</v>
+        <v>78393</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25019,34 +25026,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>639</v>
+        <v>314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>600067</v>
+        <v>600111</v>
       </c>
       <c r="R220" t="n">
-        <v>7331229</v>
+        <v>7331594</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -25078,7 +25085,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -25088,12 +25095,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>1 bål på levande gammal björk</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -25108,12 +25110,12 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
@@ -25124,10 +25126,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>135351897</v>
+        <v>135361449</v>
       </c>
       <c r="B221" t="n">
-        <v>92245</v>
+        <v>89354</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25135,37 +25137,37 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>600067</v>
+        <v>600168</v>
       </c>
       <c r="R221" t="n">
-        <v>7331234</v>
+        <v>7331283</v>
       </c>
       <c r="S221" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -25194,7 +25196,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -25204,7 +25206,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25219,12 +25221,12 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
@@ -25235,48 +25237,48 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>135351929</v>
+        <v>135350594</v>
       </c>
       <c r="B222" t="n">
-        <v>92245</v>
+        <v>79442</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>658</v>
+        <v>639</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>600076</v>
+        <v>600067</v>
       </c>
       <c r="R222" t="n">
-        <v>7331493</v>
+        <v>7331229</v>
       </c>
       <c r="S222" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -25305,7 +25307,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -25315,7 +25317,12 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>1 bål på levande gammal björk</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25330,12 +25337,12 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
@@ -25346,7 +25353,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>135354318</v>
+        <v>135351897</v>
       </c>
       <c r="B223" t="n">
         <v>92245</v>
@@ -25377,14 +25384,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>600086</v>
+        <v>600067</v>
       </c>
       <c r="R223" t="n">
-        <v>7331512</v>
+        <v>7331234</v>
       </c>
       <c r="S223" t="n">
         <v>7</v>
@@ -25416,7 +25423,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25426,7 +25433,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25441,12 +25448,12 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
@@ -25457,7 +25464,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>135357068</v>
+        <v>135351929</v>
       </c>
       <c r="B224" t="n">
         <v>92245</v>
@@ -25488,17 +25495,17 @@
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>600081</v>
+        <v>600076</v>
       </c>
       <c r="R224" t="n">
-        <v>7331503</v>
+        <v>7331493</v>
       </c>
       <c r="S224" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -25527,7 +25534,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -25537,7 +25544,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25552,12 +25559,12 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -25568,10 +25575,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>135350575</v>
+        <v>135354318</v>
       </c>
       <c r="B225" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25579,37 +25586,37 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>600288</v>
+        <v>600086</v>
       </c>
       <c r="R225" t="n">
-        <v>7331329</v>
+        <v>7331512</v>
       </c>
       <c r="S225" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -25638,7 +25645,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25648,7 +25655,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25663,12 +25670,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -25679,10 +25686,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>135350592</v>
+        <v>135357068</v>
       </c>
       <c r="B226" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25690,34 +25697,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>600105</v>
+        <v>600081</v>
       </c>
       <c r="R226" t="n">
-        <v>7331205</v>
+        <v>7331503</v>
       </c>
       <c r="S226" t="n">
         <v>5</v>
@@ -25749,7 +25756,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25759,7 +25766,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25774,12 +25781,12 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -25790,7 +25797,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>135350677</v>
+        <v>135350575</v>
       </c>
       <c r="B227" t="n">
         <v>79452</v>
@@ -25825,10 +25832,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>600100</v>
+        <v>600288</v>
       </c>
       <c r="R227" t="n">
-        <v>7331204</v>
+        <v>7331329</v>
       </c>
       <c r="S227" t="n">
         <v>5</v>
@@ -25860,7 +25867,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25870,7 +25877,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25901,7 +25908,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>135351934</v>
+        <v>135350592</v>
       </c>
       <c r="B228" t="n">
         <v>79452</v>
@@ -25932,14 +25939,14 @@
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>600115</v>
+        <v>600105</v>
       </c>
       <c r="R228" t="n">
-        <v>7331617</v>
+        <v>7331205</v>
       </c>
       <c r="S228" t="n">
         <v>5</v>
@@ -25971,7 +25978,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25981,7 +25988,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25996,12 +26003,12 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -26012,45 +26019,45 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>135361446</v>
+        <v>135350677</v>
       </c>
       <c r="B229" t="n">
-        <v>92795</v>
+        <v>79452</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>600190</v>
+        <v>600100</v>
       </c>
       <c r="R229" t="n">
-        <v>7331349</v>
+        <v>7331204</v>
       </c>
       <c r="S229" t="n">
         <v>5</v>
@@ -26082,7 +26089,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -26092,12 +26099,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC229" t="inlineStr">
-        <is>
-          <t>Ganska nedbruten granlåga</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26112,12 +26114,12 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
@@ -26128,45 +26130,45 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>135361447</v>
+        <v>135351934</v>
       </c>
       <c r="B230" t="n">
-        <v>92795</v>
+        <v>79452</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>918</v>
+        <v>864</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>600184</v>
+        <v>600115</v>
       </c>
       <c r="R230" t="n">
-        <v>7331312</v>
+        <v>7331617</v>
       </c>
       <c r="S230" t="n">
         <v>5</v>
@@ -26198,7 +26200,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -26208,12 +26210,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>Oklart!</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26228,12 +26225,12 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -26244,45 +26241,45 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>135350581</v>
+        <v>135361446</v>
       </c>
       <c r="B231" t="n">
-        <v>91970</v>
+        <v>92795</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>600232</v>
+        <v>600190</v>
       </c>
       <c r="R231" t="n">
-        <v>7331370</v>
+        <v>7331349</v>
       </c>
       <c r="S231" t="n">
         <v>5</v>
@@ -26314,7 +26311,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -26324,7 +26321,12 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Ganska nedbruten granlåga</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26339,12 +26341,12 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
@@ -26355,45 +26357,45 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>135350674</v>
+        <v>135361447</v>
       </c>
       <c r="B232" t="n">
-        <v>91970</v>
+        <v>92795</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>600071</v>
+        <v>600184</v>
       </c>
       <c r="R232" t="n">
-        <v>7331509</v>
+        <v>7331312</v>
       </c>
       <c r="S232" t="n">
         <v>5</v>
@@ -26425,7 +26427,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26435,7 +26437,12 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Oklart!</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26450,12 +26457,12 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
@@ -26466,7 +26473,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>135350740</v>
+        <v>135350581</v>
       </c>
       <c r="B233" t="n">
         <v>91970</v>
@@ -26497,17 +26504,17 @@
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>600074</v>
+        <v>600232</v>
       </c>
       <c r="R233" t="n">
-        <v>7331282</v>
+        <v>7331370</v>
       </c>
       <c r="S233" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -26536,7 +26543,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26546,7 +26553,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26561,12 +26568,12 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
@@ -26577,7 +26584,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>135350763</v>
+        <v>135350674</v>
       </c>
       <c r="B234" t="n">
         <v>91970</v>
@@ -26608,17 +26615,17 @@
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>600167</v>
+        <v>600071</v>
       </c>
       <c r="R234" t="n">
-        <v>7331502</v>
+        <v>7331509</v>
       </c>
       <c r="S234" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -26647,7 +26654,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -26657,7 +26664,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26672,12 +26679,12 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
@@ -26688,7 +26695,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>135354382</v>
+        <v>135350740</v>
       </c>
       <c r="B235" t="n">
         <v>91970</v>
@@ -26719,14 +26726,14 @@
       <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>600205</v>
+        <v>600074</v>
       </c>
       <c r="R235" t="n">
-        <v>7331293</v>
+        <v>7331282</v>
       </c>
       <c r="S235" t="n">
         <v>11</v>
@@ -26758,7 +26765,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -26768,7 +26775,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26783,12 +26790,12 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
@@ -26799,7 +26806,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>135356975</v>
+        <v>135350763</v>
       </c>
       <c r="B236" t="n">
         <v>91970</v>
@@ -26830,17 +26837,17 @@
       <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>600222</v>
+        <v>600167</v>
       </c>
       <c r="R236" t="n">
-        <v>7331371</v>
+        <v>7331502</v>
       </c>
       <c r="S236" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26869,7 +26876,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -26879,7 +26886,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26894,12 +26901,12 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -26910,7 +26917,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>135356977</v>
+        <v>135354382</v>
       </c>
       <c r="B237" t="n">
         <v>91970</v>
@@ -26941,17 +26948,17 @@
       <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>600200</v>
+        <v>600205</v>
       </c>
       <c r="R237" t="n">
-        <v>7331377</v>
+        <v>7331293</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -26980,7 +26987,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -26990,7 +26997,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -27005,12 +27012,12 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
@@ -27021,7 +27028,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>135357066</v>
+        <v>135356975</v>
       </c>
       <c r="B238" t="n">
         <v>91970</v>
@@ -27056,13 +27063,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>600085</v>
+        <v>600222</v>
       </c>
       <c r="R238" t="n">
-        <v>7331505</v>
+        <v>7331371</v>
       </c>
       <c r="S238" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -27091,7 +27098,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -27101,7 +27108,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -27132,7 +27139,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>135357076</v>
+        <v>135356977</v>
       </c>
       <c r="B239" t="n">
         <v>91970</v>
@@ -27167,10 +27174,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>600148</v>
+        <v>600200</v>
       </c>
       <c r="R239" t="n">
-        <v>7331592</v>
+        <v>7331377</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -27202,7 +27209,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -27212,7 +27219,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27243,7 +27250,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>135357445</v>
+        <v>135357066</v>
       </c>
       <c r="B240" t="n">
         <v>91970</v>
@@ -27274,17 +27281,17 @@
       <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>600173</v>
+        <v>600085</v>
       </c>
       <c r="R240" t="n">
-        <v>7331361</v>
+        <v>7331505</v>
       </c>
       <c r="S240" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -27313,7 +27320,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -27323,7 +27330,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27338,12 +27345,12 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
@@ -27354,7 +27361,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>135361445</v>
+        <v>135357076</v>
       </c>
       <c r="B241" t="n">
         <v>91970</v>
@@ -27385,14 +27392,14 @@
       <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
-          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>600190</v>
+        <v>600148</v>
       </c>
       <c r="R241" t="n">
-        <v>7331349</v>
+        <v>7331592</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -27424,7 +27431,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27434,12 +27441,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>Grantubbe</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27454,12 +27456,12 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
@@ -27470,10 +27472,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>135350730</v>
+        <v>135357445</v>
       </c>
       <c r="B242" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27481,37 +27483,37 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>600299</v>
+        <v>600173</v>
       </c>
       <c r="R242" t="n">
-        <v>7331286</v>
+        <v>7331361</v>
       </c>
       <c r="S242" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -27540,7 +27542,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -27550,7 +27552,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27565,12 +27567,12 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
@@ -27581,10 +27583,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>135354295</v>
+        <v>135361445</v>
       </c>
       <c r="B243" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27592,37 +27594,37 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>600320</v>
+        <v>600190</v>
       </c>
       <c r="R243" t="n">
-        <v>7331338</v>
+        <v>7331349</v>
       </c>
       <c r="S243" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -27651,7 +27653,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -27661,7 +27663,12 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>Grantubbe</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27676,12 +27683,12 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
@@ -27692,7 +27699,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>135354297</v>
+        <v>135350730</v>
       </c>
       <c r="B244" t="n">
         <v>91974</v>
@@ -27723,17 +27730,17 @@
       <c r="I244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>600258</v>
+        <v>600299</v>
       </c>
       <c r="R244" t="n">
-        <v>7331367</v>
+        <v>7331286</v>
       </c>
       <c r="S244" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27762,7 +27769,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27772,7 +27779,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27787,12 +27794,12 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
@@ -27803,7 +27810,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>135354322</v>
+        <v>135354295</v>
       </c>
       <c r="B245" t="n">
         <v>91974</v>
@@ -27838,13 +27845,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>600204</v>
+        <v>600320</v>
       </c>
       <c r="R245" t="n">
-        <v>7331293</v>
+        <v>7331338</v>
       </c>
       <c r="S245" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27873,7 +27880,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27883,7 +27890,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27914,7 +27921,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>135354383</v>
+        <v>135354297</v>
       </c>
       <c r="B246" t="n">
         <v>91974</v>
@@ -27945,17 +27952,17 @@
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>600200</v>
+        <v>600258</v>
       </c>
       <c r="R246" t="n">
-        <v>7331295</v>
+        <v>7331367</v>
       </c>
       <c r="S246" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -27984,7 +27991,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -27994,7 +28001,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -28009,12 +28016,12 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
@@ -28025,7 +28032,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>135356976</v>
+        <v>135354322</v>
       </c>
       <c r="B247" t="n">
         <v>91974</v>
@@ -28056,17 +28063,17 @@
       <c r="I247" t="inlineStr"/>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>600205</v>
+        <v>600204</v>
       </c>
       <c r="R247" t="n">
-        <v>7331377</v>
+        <v>7331293</v>
       </c>
       <c r="S247" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -28095,7 +28102,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -28105,7 +28112,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -28120,12 +28127,12 @@
       <c r="AT247" t="inlineStr"/>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
@@ -28136,7 +28143,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>135356983</v>
+        <v>135354383</v>
       </c>
       <c r="B248" t="n">
         <v>91974</v>
@@ -28167,17 +28174,17 @@
       <c r="I248" t="inlineStr"/>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>600207</v>
+        <v>600200</v>
       </c>
       <c r="R248" t="n">
-        <v>7331365</v>
+        <v>7331295</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -28206,7 +28213,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -28216,7 +28223,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28231,12 +28238,12 @@
       <c r="AT248" t="inlineStr"/>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
@@ -28247,7 +28254,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>135357441</v>
+        <v>135356976</v>
       </c>
       <c r="B249" t="n">
         <v>91974</v>
@@ -28278,17 +28285,17 @@
       <c r="I249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>600269</v>
+        <v>600205</v>
       </c>
       <c r="R249" t="n">
-        <v>7331350</v>
+        <v>7331377</v>
       </c>
       <c r="S249" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -28317,7 +28324,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -28327,7 +28334,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD249" t="b">
@@ -28342,12 +28349,12 @@
       <c r="AT249" t="inlineStr"/>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
@@ -28358,45 +28365,45 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>135350675</v>
+        <v>135356983</v>
       </c>
       <c r="B250" t="n">
-        <v>91988</v>
+        <v>91974</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>600082</v>
+        <v>600207</v>
       </c>
       <c r="R250" t="n">
-        <v>7331501</v>
+        <v>7331365</v>
       </c>
       <c r="S250" t="n">
         <v>5</v>
@@ -28428,7 +28435,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28438,7 +28445,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28453,12 +28460,12 @@
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
@@ -28469,10 +28476,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>135356985</v>
+        <v>135357441</v>
       </c>
       <c r="B251" t="n">
-        <v>83222</v>
+        <v>91974</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28480,37 +28487,37 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>600194</v>
+        <v>600269</v>
       </c>
       <c r="R251" t="n">
-        <v>7331360</v>
+        <v>7331350</v>
       </c>
       <c r="S251" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -28539,7 +28546,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -28549,7 +28556,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28564,12 +28571,12 @@
       <c r="AT251" t="inlineStr"/>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
@@ -28580,45 +28587,45 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>135357073</v>
+        <v>135350675</v>
       </c>
       <c r="B252" t="n">
-        <v>83222</v>
+        <v>91988</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>600111</v>
+        <v>600082</v>
       </c>
       <c r="R252" t="n">
-        <v>7331594</v>
+        <v>7331501</v>
       </c>
       <c r="S252" t="n">
         <v>5</v>
@@ -28650,7 +28657,7 @@
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -28660,7 +28667,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD252" t="b">
@@ -28675,12 +28682,12 @@
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
@@ -28691,10 +28698,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135350680</v>
+        <v>135356985</v>
       </c>
       <c r="B253" t="n">
-        <v>83363</v>
+        <v>83222</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28702,34 +28709,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>600100</v>
+        <v>600194</v>
       </c>
       <c r="R253" t="n">
-        <v>7331204</v>
+        <v>7331360</v>
       </c>
       <c r="S253" t="n">
         <v>5</v>
@@ -28761,7 +28768,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28771,7 +28778,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28786,12 +28793,12 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -28802,10 +28809,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135356978</v>
+        <v>135357073</v>
       </c>
       <c r="B254" t="n">
-        <v>83363</v>
+        <v>83222</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28813,21 +28820,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28837,10 +28844,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>600207</v>
+        <v>600111</v>
       </c>
       <c r="R254" t="n">
-        <v>7331365</v>
+        <v>7331594</v>
       </c>
       <c r="S254" t="n">
         <v>5</v>
@@ -28872,7 +28879,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28882,12 +28889,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>Björkhögstubbe</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28918,7 +28920,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>135356987</v>
+        <v>135350680</v>
       </c>
       <c r="B255" t="n">
         <v>83363</v>
@@ -28949,17 +28951,17 @@
       <c r="I255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>600203</v>
+        <v>600100</v>
       </c>
       <c r="R255" t="n">
-        <v>7331379</v>
+        <v>7331204</v>
       </c>
       <c r="S255" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -28988,7 +28990,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -28998,7 +29000,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -29013,12 +29015,12 @@
       <c r="AT255" t="inlineStr"/>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
@@ -29029,7 +29031,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>135356989</v>
+        <v>135356978</v>
       </c>
       <c r="B256" t="n">
         <v>83363</v>
@@ -29064,10 +29066,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>600170</v>
+        <v>600207</v>
       </c>
       <c r="R256" t="n">
-        <v>7331299</v>
+        <v>7331365</v>
       </c>
       <c r="S256" t="n">
         <v>5</v>
@@ -29099,7 +29101,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -29109,7 +29111,12 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -29140,7 +29147,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>135357452</v>
+        <v>135356987</v>
       </c>
       <c r="B257" t="n">
         <v>83363</v>
@@ -29171,17 +29178,17 @@
       <c r="I257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>600068</v>
+        <v>600203</v>
       </c>
       <c r="R257" t="n">
-        <v>7331282</v>
+        <v>7331379</v>
       </c>
       <c r="S257" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -29210,7 +29217,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -29220,7 +29227,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -29235,12 +29242,12 @@
       <c r="AT257" t="inlineStr"/>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
@@ -29251,48 +29258,48 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>135350673</v>
+        <v>135356989</v>
       </c>
       <c r="B258" t="n">
-        <v>92332</v>
+        <v>83363</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1505</v>
+        <v>1467</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>600071</v>
+        <v>600170</v>
       </c>
       <c r="R258" t="n">
-        <v>7331509</v>
+        <v>7331299</v>
       </c>
       <c r="S258" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -29321,7 +29328,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -29331,7 +29338,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29346,12 +29353,12 @@
       <c r="AT258" t="inlineStr"/>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
@@ -29362,32 +29369,32 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>135357450</v>
+        <v>135357452</v>
       </c>
       <c r="B259" t="n">
-        <v>92329</v>
+        <v>83363</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1506</v>
+        <v>1467</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29397,13 +29404,13 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>600139</v>
+        <v>600068</v>
       </c>
       <c r="R259" t="n">
-        <v>7331320</v>
+        <v>7331282</v>
       </c>
       <c r="S259" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -29432,7 +29439,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -29442,7 +29449,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -29473,10 +29480,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>135361448</v>
+        <v>135350673</v>
       </c>
       <c r="B260" t="n">
-        <v>92329</v>
+        <v>92332</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29484,37 +29491,37 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>600187</v>
+        <v>600071</v>
       </c>
       <c r="R260" t="n">
-        <v>7331287</v>
+        <v>7331509</v>
       </c>
       <c r="S260" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -29543,7 +29550,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -29553,12 +29560,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -29573,12 +29575,12 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
@@ -29589,10 +29591,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>135350590</v>
+        <v>135357450</v>
       </c>
       <c r="B261" t="n">
-        <v>92320</v>
+        <v>92329</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29600,37 +29602,37 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>2063</v>
+        <v>1506</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>600137</v>
+        <v>600139</v>
       </c>
       <c r="R261" t="n">
-        <v>7331217</v>
+        <v>7331320</v>
       </c>
       <c r="S261" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -29659,7 +29661,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -29669,7 +29671,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -29684,12 +29686,12 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
@@ -29700,32 +29702,32 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>135361465</v>
+        <v>135361448</v>
       </c>
       <c r="B262" t="n">
-        <v>80489</v>
+        <v>92329</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2081</v>
+        <v>1506</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29735,10 +29737,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>600179</v>
+        <v>600187</v>
       </c>
       <c r="R262" t="n">
-        <v>7331428</v>
+        <v>7331287</v>
       </c>
       <c r="S262" t="n">
         <v>5</v>
@@ -29770,7 +29772,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -29780,7 +29782,12 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29811,48 +29818,48 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>135356973</v>
+        <v>135350590</v>
       </c>
       <c r="B263" t="n">
-        <v>96037</v>
+        <v>92320</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>2387</v>
+        <v>2063</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>600289</v>
+        <v>600137</v>
       </c>
       <c r="R263" t="n">
-        <v>7331332</v>
+        <v>7331217</v>
       </c>
       <c r="S263" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -29881,7 +29888,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -29891,7 +29898,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -29906,12 +29913,12 @@
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
@@ -29922,48 +29929,48 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>135354296</v>
+        <v>135361465</v>
       </c>
       <c r="B264" t="n">
-        <v>92370</v>
+        <v>80489</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4217</v>
+        <v>2081</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>600274</v>
+        <v>600179</v>
       </c>
       <c r="R264" t="n">
-        <v>7331368</v>
+        <v>7331428</v>
       </c>
       <c r="S264" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -29992,7 +29999,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -30002,7 +30009,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30017,12 +30024,12 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
@@ -30033,10 +30040,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>135357067</v>
+        <v>135356973</v>
       </c>
       <c r="B265" t="n">
-        <v>92370</v>
+        <v>96037</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -30044,21 +30051,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4217</v>
+        <v>2387</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -30068,13 +30075,13 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>600086</v>
+        <v>600289</v>
       </c>
       <c r="R265" t="n">
-        <v>7331498</v>
+        <v>7331332</v>
       </c>
       <c r="S265" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -30103,7 +30110,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -30113,12 +30120,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -30149,10 +30151,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>135354381</v>
+        <v>135354296</v>
       </c>
       <c r="B266" t="n">
-        <v>91937</v>
+        <v>92370</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -30160,37 +30162,37 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>600197</v>
+        <v>600274</v>
       </c>
       <c r="R266" t="n">
-        <v>7331329</v>
+        <v>7331368</v>
       </c>
       <c r="S266" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -30219,7 +30221,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -30229,7 +30231,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -30244,12 +30246,12 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
@@ -30260,48 +30262,48 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>135350569</v>
+        <v>135357067</v>
       </c>
       <c r="B267" t="n">
-        <v>79373</v>
+        <v>92370</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>600353</v>
+        <v>600086</v>
       </c>
       <c r="R267" t="n">
-        <v>7331366</v>
+        <v>7331498</v>
       </c>
       <c r="S267" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -30330,7 +30332,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -30340,7 +30342,12 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -30355,12 +30362,12 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
@@ -30371,48 +30378,48 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>135350570</v>
+        <v>135354381</v>
       </c>
       <c r="B268" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>600314</v>
+        <v>600197</v>
       </c>
       <c r="R268" t="n">
-        <v>7331380</v>
+        <v>7331329</v>
       </c>
       <c r="S268" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -30441,7 +30448,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -30451,7 +30458,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -30466,12 +30473,12 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
@@ -30482,7 +30489,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>135350588</v>
+        <v>135350569</v>
       </c>
       <c r="B269" t="n">
         <v>79373</v>
@@ -30517,13 +30524,13 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>600165</v>
+        <v>600353</v>
       </c>
       <c r="R269" t="n">
-        <v>7331257</v>
+        <v>7331366</v>
       </c>
       <c r="S269" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -30552,7 +30559,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -30562,7 +30569,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -30593,7 +30600,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>135351882</v>
+        <v>135350570</v>
       </c>
       <c r="B270" t="n">
         <v>79373</v>
@@ -30624,17 +30631,17 @@
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>600296</v>
+        <v>600314</v>
       </c>
       <c r="R270" t="n">
-        <v>7331306</v>
+        <v>7331380</v>
       </c>
       <c r="S270" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -30663,7 +30670,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -30673,7 +30680,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -30688,12 +30695,12 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
@@ -30704,7 +30711,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>135351891</v>
+        <v>135350588</v>
       </c>
       <c r="B271" t="n">
         <v>79373</v>
@@ -30735,17 +30742,17 @@
       <c r="I271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>600232</v>
+        <v>600165</v>
       </c>
       <c r="R271" t="n">
-        <v>7331370</v>
+        <v>7331257</v>
       </c>
       <c r="S271" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -30774,7 +30781,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -30784,7 +30791,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -30799,12 +30806,12 @@
       <c r="AT271" t="inlineStr"/>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
@@ -30815,7 +30822,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>135351896</v>
+        <v>135351882</v>
       </c>
       <c r="B272" t="n">
         <v>79373</v>
@@ -30850,10 +30857,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>600163</v>
+        <v>600296</v>
       </c>
       <c r="R272" t="n">
-        <v>7331263</v>
+        <v>7331306</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -30885,7 +30892,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -30895,7 +30902,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -30926,7 +30933,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>135351933</v>
+        <v>135351891</v>
       </c>
       <c r="B273" t="n">
         <v>79373</v>
@@ -30961,13 +30968,13 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>600130</v>
+        <v>600232</v>
       </c>
       <c r="R273" t="n">
-        <v>7331606</v>
+        <v>7331370</v>
       </c>
       <c r="S273" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -30996,7 +31003,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -31006,7 +31013,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -31037,7 +31044,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>135356965</v>
+        <v>135351896</v>
       </c>
       <c r="B274" t="n">
         <v>79373</v>
@@ -31068,17 +31075,17 @@
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>600313</v>
+        <v>600163</v>
       </c>
       <c r="R274" t="n">
-        <v>7331354</v>
+        <v>7331263</v>
       </c>
       <c r="S274" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -31107,7 +31114,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -31117,7 +31124,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -31132,12 +31139,12 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
@@ -31148,7 +31155,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>135356986</v>
+        <v>135351933</v>
       </c>
       <c r="B275" t="n">
         <v>79373</v>
@@ -31179,17 +31186,17 @@
       <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>600192</v>
+        <v>600130</v>
       </c>
       <c r="R275" t="n">
-        <v>7331349</v>
+        <v>7331606</v>
       </c>
       <c r="S275" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -31218,7 +31225,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -31228,7 +31235,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -31243,12 +31250,12 @@
       <c r="AT275" t="inlineStr"/>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
@@ -31259,7 +31266,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>135357069</v>
+        <v>135356965</v>
       </c>
       <c r="B276" t="n">
         <v>79373</v>
@@ -31294,13 +31301,13 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>600085</v>
+        <v>600313</v>
       </c>
       <c r="R276" t="n">
-        <v>7331514</v>
+        <v>7331354</v>
       </c>
       <c r="S276" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -31329,7 +31336,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -31339,7 +31346,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -31370,7 +31377,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>135357071</v>
+        <v>135356986</v>
       </c>
       <c r="B277" t="n">
         <v>79373</v>
@@ -31405,10 +31412,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>600083</v>
+        <v>600192</v>
       </c>
       <c r="R277" t="n">
-        <v>7331533</v>
+        <v>7331349</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -31440,7 +31447,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -31450,7 +31457,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -31481,7 +31488,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>135357722</v>
+        <v>135357069</v>
       </c>
       <c r="B278" t="n">
         <v>79373</v>
@@ -31510,19 +31517,16 @@
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>600176</v>
+        <v>600085</v>
       </c>
       <c r="R278" t="n">
-        <v>7331284</v>
+        <v>7331514</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -31554,7 +31558,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -31564,7 +31568,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -31573,19 +31577,18 @@
       <c r="AE278" t="b">
         <v>0</v>
       </c>
-      <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="b">
         <v>0</v>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
@@ -31596,32 +31599,32 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>135356979</v>
+        <v>135357071</v>
       </c>
       <c r="B279" t="n">
-        <v>75340</v>
+        <v>79373</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -31631,10 +31634,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>600207</v>
+        <v>600083</v>
       </c>
       <c r="R279" t="n">
-        <v>7331365</v>
+        <v>7331533</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -31666,7 +31669,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -31676,7 +31679,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -31707,45 +31710,48 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>135350587</v>
+        <v>135357722</v>
       </c>
       <c r="B280" t="n">
-        <v>83341</v>
+        <v>79373</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>600187</v>
+        <v>600176</v>
       </c>
       <c r="R280" t="n">
-        <v>7331296</v>
+        <v>7331284</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -31777,7 +31783,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -31787,7 +31793,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -31796,18 +31802,19 @@
       <c r="AE280" t="b">
         <v>0</v>
       </c>
+      <c r="AF280" t="inlineStr"/>
       <c r="AG280" t="b">
         <v>0</v>
       </c>
       <c r="AT280" t="inlineStr"/>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
@@ -31818,10 +31825,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>135356993</v>
+        <v>135356979</v>
       </c>
       <c r="B281" t="n">
-        <v>83341</v>
+        <v>75340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31829,21 +31836,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -31853,10 +31860,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>600066</v>
+        <v>600207</v>
       </c>
       <c r="R281" t="n">
-        <v>7331231</v>
+        <v>7331365</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -31888,7 +31895,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -31898,7 +31905,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -31929,7 +31936,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>135357451</v>
+        <v>135350587</v>
       </c>
       <c r="B282" t="n">
         <v>83341</v>
@@ -31960,17 +31967,17 @@
       <c r="I282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>600065</v>
+        <v>600187</v>
       </c>
       <c r="R282" t="n">
-        <v>7331283</v>
+        <v>7331296</v>
       </c>
       <c r="S282" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -31999,7 +32006,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -32009,7 +32016,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -32024,12 +32031,12 @@
       <c r="AT282" t="inlineStr"/>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
@@ -32040,48 +32047,48 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>135350572</v>
+        <v>135356993</v>
       </c>
       <c r="B283" t="n">
-        <v>83358</v>
+        <v>83341</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>600311</v>
+        <v>600066</v>
       </c>
       <c r="R283" t="n">
-        <v>7331348</v>
+        <v>7331231</v>
       </c>
       <c r="S283" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -32110,7 +32117,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -32120,7 +32127,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -32135,12 +32142,12 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
@@ -32151,48 +32158,48 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>135350580</v>
+        <v>135357451</v>
       </c>
       <c r="B284" t="n">
-        <v>83358</v>
+        <v>83341</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>600229</v>
+        <v>600065</v>
       </c>
       <c r="R284" t="n">
-        <v>7331364</v>
+        <v>7331283</v>
       </c>
       <c r="S284" t="n">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -32221,7 +32228,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -32231,7 +32238,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -32246,12 +32253,12 @@
       <c r="AT284" t="inlineStr"/>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
@@ -32262,7 +32269,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>135351877</v>
+        <v>135350572</v>
       </c>
       <c r="B285" t="n">
         <v>83358</v>
@@ -32293,17 +32300,17 @@
       <c r="I285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>600358</v>
+        <v>600311</v>
       </c>
       <c r="R285" t="n">
-        <v>7331345</v>
+        <v>7331348</v>
       </c>
       <c r="S285" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -32332,7 +32339,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -32342,7 +32349,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -32357,12 +32364,12 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
@@ -32373,7 +32380,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>135354294</v>
+        <v>135350580</v>
       </c>
       <c r="B286" t="n">
         <v>83358</v>
@@ -32404,14 +32411,14 @@
       <c r="I286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>600351</v>
+        <v>600229</v>
       </c>
       <c r="R286" t="n">
-        <v>7331356</v>
+        <v>7331364</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -32443,7 +32450,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -32453,7 +32460,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -32468,12 +32475,12 @@
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
@@ -32484,7 +32491,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>135354298</v>
+        <v>135351877</v>
       </c>
       <c r="B287" t="n">
         <v>83358</v>
@@ -32515,17 +32522,17 @@
       <c r="I287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>600143</v>
+        <v>600358</v>
       </c>
       <c r="R287" t="n">
-        <v>7331397</v>
+        <v>7331345</v>
       </c>
       <c r="S287" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -32554,7 +32561,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -32564,7 +32571,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -32579,12 +32586,12 @@
       <c r="AT287" t="inlineStr"/>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
@@ -32595,7 +32602,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>135356964</v>
+        <v>135354294</v>
       </c>
       <c r="B288" t="n">
         <v>83358</v>
@@ -32626,14 +32633,14 @@
       <c r="I288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>600312</v>
+        <v>600351</v>
       </c>
       <c r="R288" t="n">
-        <v>7331352</v>
+        <v>7331356</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -32665,7 +32672,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -32675,7 +32682,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -32690,12 +32697,12 @@
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -32706,7 +32713,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>135356969</v>
+        <v>135354298</v>
       </c>
       <c r="B289" t="n">
         <v>83358</v>
@@ -32737,17 +32744,17 @@
       <c r="I289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>600307</v>
+        <v>600143</v>
       </c>
       <c r="R289" t="n">
-        <v>7331359</v>
+        <v>7331397</v>
       </c>
       <c r="S289" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -32776,7 +32783,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -32786,7 +32793,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -32801,12 +32808,12 @@
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
@@ -32817,7 +32824,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>135357070</v>
+        <v>135356964</v>
       </c>
       <c r="B290" t="n">
         <v>83358</v>
@@ -32852,13 +32859,13 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>600081</v>
+        <v>600312</v>
       </c>
       <c r="R290" t="n">
-        <v>7331525</v>
+        <v>7331352</v>
       </c>
       <c r="S290" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -32887,7 +32894,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -32897,7 +32904,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -32928,7 +32935,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>135357077</v>
+        <v>135356969</v>
       </c>
       <c r="B291" t="n">
         <v>83358</v>
@@ -32963,13 +32970,13 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>600368</v>
+        <v>600307</v>
       </c>
       <c r="R291" t="n">
-        <v>7331322</v>
+        <v>7331359</v>
       </c>
       <c r="S291" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -32998,7 +33005,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -33008,7 +33015,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -33039,7 +33046,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>135357444</v>
+        <v>135357070</v>
       </c>
       <c r="B292" t="n">
         <v>83358</v>
@@ -33070,17 +33077,17 @@
       <c r="I292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>600198</v>
+        <v>600081</v>
       </c>
       <c r="R292" t="n">
-        <v>7331357</v>
+        <v>7331525</v>
       </c>
       <c r="S292" t="n">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -33109,7 +33116,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -33119,7 +33126,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -33134,12 +33141,12 @@
       <c r="AT292" t="inlineStr"/>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr">
@@ -33150,7 +33157,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>135357486</v>
+        <v>135357077</v>
       </c>
       <c r="B293" t="n">
         <v>83358</v>
@@ -33181,17 +33188,17 @@
       <c r="I293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>600111</v>
+        <v>600368</v>
       </c>
       <c r="R293" t="n">
-        <v>7331482</v>
+        <v>7331322</v>
       </c>
       <c r="S293" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -33220,7 +33227,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -33230,7 +33237,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -33245,12 +33252,12 @@
       <c r="AT293" t="inlineStr"/>
       <c r="AW293" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr">
@@ -33261,10 +33268,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>135357447</v>
+        <v>135357444</v>
       </c>
       <c r="B294" t="n">
-        <v>80488</v>
+        <v>83358</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33272,21 +33279,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -33296,13 +33303,13 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>600173</v>
+        <v>600198</v>
       </c>
       <c r="R294" t="n">
-        <v>7331345</v>
+        <v>7331357</v>
       </c>
       <c r="S294" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -33331,7 +33338,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -33341,12 +33348,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC294" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -33377,10 +33379,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>135361464</v>
+        <v>135357486</v>
       </c>
       <c r="B295" t="n">
-        <v>80488</v>
+        <v>83358</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -33388,37 +33390,37 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
         <is>
-          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>600109</v>
+        <v>600111</v>
       </c>
       <c r="R295" t="n">
-        <v>7331546</v>
+        <v>7331482</v>
       </c>
       <c r="S295" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -33447,7 +33449,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -33457,7 +33459,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -33472,12 +33474,12 @@
       <c r="AT295" t="inlineStr"/>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
@@ -33488,48 +33490,48 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>135350593</v>
+        <v>135357447</v>
       </c>
       <c r="B296" t="n">
-        <v>80493</v>
+        <v>80488</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>600068</v>
+        <v>600173</v>
       </c>
       <c r="R296" t="n">
-        <v>7331214</v>
+        <v>7331345</v>
       </c>
       <c r="S296" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -33558,7 +33560,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -33568,7 +33570,12 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC296" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -33583,12 +33590,12 @@
       <c r="AT296" t="inlineStr"/>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
@@ -33599,48 +33606,48 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>135356991</v>
+        <v>135361464</v>
       </c>
       <c r="B297" t="n">
-        <v>80493</v>
+        <v>80488</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>600066</v>
+        <v>600109</v>
       </c>
       <c r="R297" t="n">
-        <v>7331234</v>
+        <v>7331546</v>
       </c>
       <c r="S297" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
@@ -33669,7 +33676,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -33679,7 +33686,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -33694,12 +33701,12 @@
       <c r="AT297" t="inlineStr"/>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
@@ -33710,10 +33717,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>135357721</v>
+        <v>135350593</v>
       </c>
       <c r="B298" t="n">
-        <v>80500</v>
+        <v>80493</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33721,37 +33728,37 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>600199</v>
+        <v>600068</v>
       </c>
       <c r="R298" t="n">
-        <v>7331404</v>
+        <v>7331214</v>
       </c>
       <c r="S298" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -33780,7 +33787,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -33790,7 +33797,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -33805,12 +33812,12 @@
       <c r="AT298" t="inlineStr"/>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
@@ -33821,53 +33828,48 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>135350576</v>
+        <v>135356991</v>
       </c>
       <c r="B299" t="n">
-        <v>57975</v>
+        <v>80493</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>600274</v>
+        <v>600066</v>
       </c>
       <c r="R299" t="n">
-        <v>7331368</v>
+        <v>7331234</v>
       </c>
       <c r="S299" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
@@ -33896,7 +33898,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -33906,7 +33908,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -33921,12 +33923,12 @@
       <c r="AT299" t="inlineStr"/>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
@@ -33937,53 +33939,48 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>135350583</v>
+        <v>135357721</v>
       </c>
       <c r="B300" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
-      <c r="M300" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>600166</v>
+        <v>600199</v>
       </c>
       <c r="R300" t="n">
-        <v>7331334</v>
+        <v>7331404</v>
       </c>
       <c r="S300" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="T300" t="inlineStr">
         <is>
@@ -34012,7 +34009,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -34022,7 +34019,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -34037,12 +34034,12 @@
       <c r="AT300" t="inlineStr"/>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
@@ -34053,7 +34050,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>135350764</v>
+        <v>135350576</v>
       </c>
       <c r="B301" t="n">
         <v>57975</v>
@@ -34082,16 +34079,21 @@
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>600272</v>
+        <v>600274</v>
       </c>
       <c r="R301" t="n">
-        <v>7331401</v>
+        <v>7331368</v>
       </c>
       <c r="S301" t="n">
         <v>6</v>
@@ -34123,7 +34125,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -34133,12 +34135,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC301" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -34153,12 +34150,12 @@
       <c r="AT301" t="inlineStr"/>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
@@ -34169,7 +34166,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>135354320</v>
+        <v>135350583</v>
       </c>
       <c r="B302" t="n">
         <v>57975</v>
@@ -34198,19 +34195,24 @@
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>600173</v>
+        <v>600166</v>
       </c>
       <c r="R302" t="n">
-        <v>7331326</v>
+        <v>7331334</v>
       </c>
       <c r="S302" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -34239,7 +34241,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -34249,12 +34251,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC302" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -34269,12 +34266,12 @@
       <c r="AT302" t="inlineStr"/>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
@@ -34285,7 +34282,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>135357488</v>
+        <v>135350764</v>
       </c>
       <c r="B303" t="n">
         <v>57975</v>
@@ -34314,27 +34311,19 @@
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>600078</v>
+        <v>600272</v>
       </c>
       <c r="R303" t="n">
-        <v>7331554</v>
+        <v>7331401</v>
       </c>
       <c r="S303" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -34363,7 +34352,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -34373,12 +34362,12 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
         <is>
-          <t>Gammalt bohål i gran angripen av granticka som verkar stämma med måtten för den tretåiga hackspettens bohål</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -34393,12 +34382,12 @@
       <c r="AT303" t="inlineStr"/>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
@@ -34409,10 +34398,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>135350578</v>
+        <v>135354320</v>
       </c>
       <c r="B304" t="n">
-        <v>58079</v>
+        <v>57975</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -34420,16 +34409,16 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -34440,17 +34429,17 @@
       <c r="I304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>600263</v>
+        <v>600173</v>
       </c>
       <c r="R304" t="n">
-        <v>7331376</v>
+        <v>7331326</v>
       </c>
       <c r="S304" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -34479,7 +34468,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -34489,7 +34478,12 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC304" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -34504,12 +34498,12 @@
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
@@ -34520,10 +34514,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>135354424</v>
+        <v>135357488</v>
       </c>
       <c r="B305" t="n">
-        <v>58079</v>
+        <v>57975</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34531,16 +34525,16 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -34549,19 +34543,27 @@
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>600223</v>
+        <v>600078</v>
       </c>
       <c r="R305" t="n">
-        <v>7331526</v>
+        <v>7331554</v>
       </c>
       <c r="S305" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -34590,7 +34592,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -34600,7 +34602,12 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i gran angripen av granticka som verkar stämma med måtten för den tretåiga hackspettens bohål</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -34615,12 +34622,12 @@
       <c r="AT305" t="inlineStr"/>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
@@ -34631,7 +34638,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>135356970</v>
+        <v>135350578</v>
       </c>
       <c r="B306" t="n">
         <v>58079</v>
@@ -34662,17 +34669,17 @@
       <c r="I306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>600313</v>
+        <v>600263</v>
       </c>
       <c r="R306" t="n">
-        <v>7331351</v>
+        <v>7331376</v>
       </c>
       <c r="S306" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -34701,7 +34708,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -34711,7 +34718,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -34726,12 +34733,12 @@
       <c r="AT306" t="inlineStr"/>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
@@ -34742,7 +34749,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>135357424</v>
+        <v>135354424</v>
       </c>
       <c r="B307" t="n">
         <v>58079</v>
@@ -34773,17 +34780,17 @@
       <c r="I307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>600144</v>
+        <v>600223</v>
       </c>
       <c r="R307" t="n">
-        <v>7331309</v>
+        <v>7331526</v>
       </c>
       <c r="S307" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -34812,7 +34819,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -34822,7 +34829,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -34837,12 +34844,12 @@
       <c r="AT307" t="inlineStr"/>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
@@ -34853,48 +34860,48 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>135354385</v>
+        <v>135356970</v>
       </c>
       <c r="B308" t="n">
-        <v>92661</v>
+        <v>58079</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>106596</v>
+        <v>103031</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Nordlig parasitporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>600167</v>
+        <v>600313</v>
       </c>
       <c r="R308" t="n">
-        <v>7331292</v>
+        <v>7331351</v>
       </c>
       <c r="S308" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -34923,7 +34930,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -34933,7 +34940,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -34948,12 +34955,12 @@
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
@@ -34964,48 +34971,48 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>135354316</v>
+        <v>135357424</v>
       </c>
       <c r="B309" t="n">
-        <v>99112</v>
+        <v>58079</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>600064</v>
+        <v>600144</v>
       </c>
       <c r="R309" t="n">
-        <v>7331520</v>
+        <v>7331309</v>
       </c>
       <c r="S309" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -35034,7 +35041,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -35044,7 +35051,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -35059,12 +35066,12 @@
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
@@ -35075,48 +35082,48 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>135356990</v>
+        <v>135354385</v>
       </c>
       <c r="B310" t="n">
-        <v>99112</v>
+        <v>92661</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>219790</v>
+        <v>106596</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>600178</v>
+        <v>600167</v>
       </c>
       <c r="R310" t="n">
-        <v>7331297</v>
+        <v>7331292</v>
       </c>
       <c r="S310" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -35145,7 +35152,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -35155,7 +35162,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -35170,12 +35177,12 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
@@ -35186,7 +35193,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>135357428</v>
+        <v>135354316</v>
       </c>
       <c r="B311" t="n">
         <v>99112</v>
@@ -35217,17 +35224,17 @@
       <c r="I311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>600147</v>
+        <v>600064</v>
       </c>
       <c r="R311" t="n">
-        <v>7331298</v>
+        <v>7331520</v>
       </c>
       <c r="S311" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -35256,7 +35263,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -35266,7 +35273,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -35281,12 +35288,12 @@
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
@@ -35297,7 +35304,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>135357723</v>
+        <v>135356990</v>
       </c>
       <c r="B312" t="n">
         <v>99112</v>
@@ -35328,17 +35335,17 @@
       <c r="I312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>600154</v>
+        <v>600178</v>
       </c>
       <c r="R312" t="n">
-        <v>7331294</v>
+        <v>7331297</v>
       </c>
       <c r="S312" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -35367,7 +35374,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -35377,7 +35384,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -35392,12 +35399,12 @@
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
@@ -35408,10 +35415,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>135357413</v>
+        <v>135357428</v>
       </c>
       <c r="B313" t="n">
-        <v>99094</v>
+        <v>99112</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -35419,21 +35426,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
@@ -35443,13 +35450,13 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>600302</v>
+        <v>600147</v>
       </c>
       <c r="R313" t="n">
-        <v>7331340</v>
+        <v>7331298</v>
       </c>
       <c r="S313" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -35478,7 +35485,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -35488,7 +35495,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -35519,10 +35526,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>135351879</v>
+        <v>135357723</v>
       </c>
       <c r="B314" t="n">
-        <v>98219</v>
+        <v>99112</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -35530,37 +35537,37 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>219815</v>
+        <v>219790</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>600306</v>
+        <v>600154</v>
       </c>
       <c r="R314" t="n">
-        <v>7331319</v>
+        <v>7331294</v>
       </c>
       <c r="S314" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -35589,7 +35596,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -35599,7 +35606,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -35614,12 +35621,12 @@
       <c r="AT314" t="inlineStr"/>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
@@ -35630,10 +35637,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>135350571</v>
+        <v>135357413</v>
       </c>
       <c r="B315" t="n">
-        <v>108205</v>
+        <v>99094</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35641,37 +35648,37 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>220083</v>
+        <v>219795</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>600308</v>
+        <v>600302</v>
       </c>
       <c r="R315" t="n">
-        <v>7331355</v>
+        <v>7331340</v>
       </c>
       <c r="S315" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
@@ -35700,7 +35707,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -35710,7 +35717,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -35725,12 +35732,12 @@
       <c r="AT315" t="inlineStr"/>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
@@ -35741,10 +35748,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>135357421</v>
+        <v>135351879</v>
       </c>
       <c r="B316" t="n">
-        <v>99099</v>
+        <v>98219</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35752,37 +35759,37 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>220093</v>
+        <v>219815</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
       <c r="P316" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>600182</v>
+        <v>600306</v>
       </c>
       <c r="R316" t="n">
-        <v>7331307</v>
+        <v>7331319</v>
       </c>
       <c r="S316" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T316" t="inlineStr">
         <is>
@@ -35811,7 +35818,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -35821,7 +35828,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -35836,12 +35843,12 @@
       <c r="AT316" t="inlineStr"/>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
@@ -35852,10 +35859,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>135356968</v>
+        <v>135350571</v>
       </c>
       <c r="B317" t="n">
-        <v>108274</v>
+        <v>108205</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -35863,37 +35870,37 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>600309</v>
+        <v>600308</v>
       </c>
       <c r="R317" t="n">
-        <v>7331352</v>
+        <v>7331355</v>
       </c>
       <c r="S317" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -35922,7 +35929,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -35932,7 +35939,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -35947,12 +35954,12 @@
       <c r="AT317" t="inlineStr"/>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
@@ -35963,10 +35970,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>135357440</v>
+        <v>135357421</v>
       </c>
       <c r="B318" t="n">
-        <v>109924</v>
+        <v>99099</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -35974,21 +35981,21 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>221184</v>
+        <v>220093</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
@@ -35998,13 +36005,13 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>600294</v>
+        <v>600182</v>
       </c>
       <c r="R318" t="n">
-        <v>7331371</v>
+        <v>7331307</v>
       </c>
       <c r="S318" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -36033,7 +36040,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -36043,7 +36050,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -36058,12 +36065,12 @@
       <c r="AT318" t="inlineStr"/>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
@@ -36074,48 +36081,48 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>135354425</v>
+        <v>135356968</v>
       </c>
       <c r="B319" t="n">
-        <v>102541</v>
+        <v>108274</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>221343</v>
+        <v>220102</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>600233</v>
+        <v>600309</v>
       </c>
       <c r="R319" t="n">
-        <v>7331537</v>
+        <v>7331352</v>
       </c>
       <c r="S319" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -36144,7 +36151,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -36154,7 +36161,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -36163,19 +36170,18 @@
       <c r="AE319" t="b">
         <v>0</v>
       </c>
-      <c r="AF319" t="inlineStr"/>
       <c r="AG319" t="b">
         <v>0</v>
       </c>
       <c r="AT319" t="inlineStr"/>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
@@ -36186,10 +36192,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>135351883</v>
+        <v>135357440</v>
       </c>
       <c r="B320" t="n">
-        <v>106309</v>
+        <v>109924</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -36197,16 +36203,16 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>221725</v>
+        <v>221184</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -36217,17 +36223,17 @@
       <c r="I320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>600318</v>
+        <v>600294</v>
       </c>
       <c r="R320" t="n">
-        <v>7331322</v>
+        <v>7331371</v>
       </c>
       <c r="S320" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T320" t="inlineStr">
         <is>
@@ -36256,7 +36262,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -36266,7 +36272,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -36281,12 +36287,12 @@
       <c r="AT320" t="inlineStr"/>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
@@ -36297,48 +36303,48 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>135351890</v>
+        <v>135354425</v>
       </c>
       <c r="B321" t="n">
-        <v>106309</v>
+        <v>102541</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>221725</v>
+        <v>221343</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q321" t="n">
         <v>600233</v>
       </c>
       <c r="R321" t="n">
-        <v>7331385</v>
+        <v>7331537</v>
       </c>
       <c r="S321" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -36367,7 +36373,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -36377,7 +36383,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -36386,18 +36392,19 @@
       <c r="AE321" t="b">
         <v>0</v>
       </c>
+      <c r="AF321" t="inlineStr"/>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
@@ -36408,7 +36415,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>135351895</v>
+        <v>135351883</v>
       </c>
       <c r="B322" t="n">
         <v>106309</v>
@@ -36443,10 +36450,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>600190</v>
+        <v>600318</v>
       </c>
       <c r="R322" t="n">
-        <v>7331355</v>
+        <v>7331322</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -36478,7 +36485,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -36488,7 +36495,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -36519,7 +36526,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>135357411</v>
+        <v>135351890</v>
       </c>
       <c r="B323" t="n">
         <v>106309</v>
@@ -36550,17 +36557,17 @@
       <c r="I323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>600334</v>
+        <v>600233</v>
       </c>
       <c r="R323" t="n">
-        <v>7331370</v>
+        <v>7331385</v>
       </c>
       <c r="S323" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -36589,7 +36596,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -36599,7 +36606,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -36614,12 +36621,12 @@
       <c r="AT323" t="inlineStr"/>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
@@ -36630,7 +36637,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>135357417</v>
+        <v>135351895</v>
       </c>
       <c r="B324" t="n">
         <v>106309</v>
@@ -36661,17 +36668,17 @@
       <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>600250</v>
+        <v>600190</v>
       </c>
       <c r="R324" t="n">
-        <v>7331298</v>
+        <v>7331355</v>
       </c>
       <c r="S324" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -36700,7 +36707,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -36710,7 +36717,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -36725,12 +36732,12 @@
       <c r="AT324" t="inlineStr"/>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -36741,7 +36748,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>135357426</v>
+        <v>135357411</v>
       </c>
       <c r="B325" t="n">
         <v>106309</v>
@@ -36776,13 +36783,13 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>600130</v>
+        <v>600334</v>
       </c>
       <c r="R325" t="n">
-        <v>7331303</v>
+        <v>7331370</v>
       </c>
       <c r="S325" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -36811,7 +36818,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -36821,7 +36828,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -36852,7 +36859,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>135357429</v>
+        <v>135357417</v>
       </c>
       <c r="B326" t="n">
         <v>106309</v>
@@ -36887,13 +36894,13 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>600104</v>
+        <v>600250</v>
       </c>
       <c r="R326" t="n">
-        <v>7331449</v>
+        <v>7331298</v>
       </c>
       <c r="S326" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -36922,7 +36929,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -36932,7 +36939,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD326" t="b">
@@ -36963,10 +36970,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>135351878</v>
+        <v>135357426</v>
       </c>
       <c r="B327" t="n">
-        <v>99217</v>
+        <v>106309</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36974,37 +36981,37 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>600337</v>
+        <v>600130</v>
       </c>
       <c r="R327" t="n">
-        <v>7331349</v>
+        <v>7331303</v>
       </c>
       <c r="S327" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -37033,7 +37040,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -37043,7 +37050,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -37058,12 +37065,12 @@
       <c r="AT327" t="inlineStr"/>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
@@ -37074,10 +37081,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>135351888</v>
+        <v>135357429</v>
       </c>
       <c r="B328" t="n">
-        <v>99217</v>
+        <v>106309</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -37085,37 +37092,37 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>600264</v>
+        <v>600104</v>
       </c>
       <c r="R328" t="n">
-        <v>7331324</v>
+        <v>7331449</v>
       </c>
       <c r="S328" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -37144,7 +37151,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -37154,7 +37161,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD328" t="b">
@@ -37169,12 +37176,12 @@
       <c r="AT328" t="inlineStr"/>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
@@ -37185,7 +37192,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>135356971</v>
+        <v>135351878</v>
       </c>
       <c r="B329" t="n">
         <v>99217</v>
@@ -37216,17 +37223,17 @@
       <c r="I329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>600311</v>
+        <v>600337</v>
       </c>
       <c r="R329" t="n">
-        <v>7331344</v>
+        <v>7331349</v>
       </c>
       <c r="S329" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -37255,7 +37262,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -37265,7 +37272,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -37280,12 +37287,12 @@
       <c r="AT329" t="inlineStr"/>
       <c r="AW329" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
@@ -37296,7 +37303,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>135357078</v>
+        <v>135351888</v>
       </c>
       <c r="B330" t="n">
         <v>99217</v>
@@ -37327,14 +37334,14 @@
       <c r="I330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>600368</v>
+        <v>600264</v>
       </c>
       <c r="R330" t="n">
-        <v>7331322</v>
+        <v>7331324</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -37366,7 +37373,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -37376,7 +37383,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -37391,12 +37398,12 @@
       <c r="AT330" t="inlineStr"/>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
@@ -37407,7 +37414,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>135357410</v>
+        <v>135356971</v>
       </c>
       <c r="B331" t="n">
         <v>99217</v>
@@ -37438,17 +37445,17 @@
       <c r="I331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>600354</v>
+        <v>600311</v>
       </c>
       <c r="R331" t="n">
-        <v>7331358</v>
+        <v>7331344</v>
       </c>
       <c r="S331" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -37477,7 +37484,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -37487,7 +37494,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -37502,12 +37509,12 @@
       <c r="AT331" t="inlineStr"/>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr">
@@ -37518,7 +37525,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>135357422</v>
+        <v>135357078</v>
       </c>
       <c r="B332" t="n">
         <v>99217</v>
@@ -37549,17 +37556,17 @@
       <c r="I332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>600175</v>
+        <v>600368</v>
       </c>
       <c r="R332" t="n">
-        <v>7331319</v>
+        <v>7331322</v>
       </c>
       <c r="S332" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -37588,7 +37595,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -37598,7 +37605,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -37613,12 +37620,12 @@
       <c r="AT332" t="inlineStr"/>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
@@ -37629,10 +37636,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>135357415</v>
+        <v>135357410</v>
       </c>
       <c r="B333" t="n">
-        <v>104707</v>
+        <v>99217</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -37640,21 +37647,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
@@ -37664,13 +37671,13 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>600265</v>
+        <v>600354</v>
       </c>
       <c r="R333" t="n">
-        <v>7331310</v>
+        <v>7331358</v>
       </c>
       <c r="S333" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -37699,7 +37706,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -37709,7 +37716,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -37740,10 +37747,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>135357416</v>
+        <v>135357422</v>
       </c>
       <c r="B334" t="n">
-        <v>104707</v>
+        <v>99217</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -37751,21 +37758,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
@@ -37775,13 +37782,13 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>600258</v>
+        <v>600175</v>
       </c>
       <c r="R334" t="n">
-        <v>7331287</v>
+        <v>7331319</v>
       </c>
       <c r="S334" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -37810,7 +37817,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -37820,7 +37827,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -37851,7 +37858,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>135357427</v>
+        <v>135357415</v>
       </c>
       <c r="B335" t="n">
         <v>104707</v>
@@ -37886,13 +37893,13 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>600156</v>
+        <v>600265</v>
       </c>
       <c r="R335" t="n">
-        <v>7331306</v>
+        <v>7331310</v>
       </c>
       <c r="S335" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -37921,7 +37928,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -37931,7 +37938,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -37962,10 +37969,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>135357412</v>
+        <v>135357416</v>
       </c>
       <c r="B336" t="n">
-        <v>102871</v>
+        <v>104707</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -37973,16 +37980,16 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>223037</v>
+        <v>222412</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -37997,13 +38004,13 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>600334</v>
+        <v>600258</v>
       </c>
       <c r="R336" t="n">
-        <v>7331370</v>
+        <v>7331287</v>
       </c>
       <c r="S336" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -38032,7 +38039,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -38042,7 +38049,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -38073,10 +38080,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>135351880</v>
+        <v>135357427</v>
       </c>
       <c r="B337" t="n">
-        <v>99001</v>
+        <v>104707</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -38084,16 +38091,16 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>223049</v>
+        <v>222412</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -38104,17 +38111,17 @@
       <c r="I337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>600310</v>
+        <v>600156</v>
       </c>
       <c r="R337" t="n">
-        <v>7331313</v>
+        <v>7331306</v>
       </c>
       <c r="S337" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -38143,7 +38150,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -38153,7 +38160,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -38168,12 +38175,12 @@
       <c r="AT337" t="inlineStr"/>
       <c r="AW337" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
@@ -38184,10 +38191,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>135357418</v>
+        <v>135357412</v>
       </c>
       <c r="B338" t="n">
-        <v>99001</v>
+        <v>102871</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -38195,16 +38202,16 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>223049</v>
+        <v>223037</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -38219,13 +38226,13 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>600187</v>
+        <v>600334</v>
       </c>
       <c r="R338" t="n">
-        <v>7331321</v>
+        <v>7331370</v>
       </c>
       <c r="S338" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -38254,7 +38261,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -38264,7 +38271,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -38295,7 +38302,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>135357423</v>
+        <v>135351880</v>
       </c>
       <c r="B339" t="n">
         <v>99001</v>
@@ -38326,17 +38333,17 @@
       <c r="I339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>600172</v>
+        <v>600310</v>
       </c>
       <c r="R339" t="n">
-        <v>7331318</v>
+        <v>7331313</v>
       </c>
       <c r="S339" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -38365,7 +38372,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -38375,7 +38382,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -38390,12 +38397,12 @@
       <c r="AT339" t="inlineStr"/>
       <c r="AW339" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
@@ -38406,10 +38413,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>135356967</v>
+        <v>135357418</v>
       </c>
       <c r="B340" t="n">
-        <v>105771</v>
+        <v>99001</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -38417,33 +38424,37 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>224074</v>
+        <v>223049</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Nordlundarv</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Stellaria nemorum subsp. nemorum</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr"/>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>600310</v>
+        <v>600187</v>
       </c>
       <c r="R340" t="n">
-        <v>7331362</v>
+        <v>7331321</v>
       </c>
       <c r="S340" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -38472,7 +38483,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -38482,7 +38493,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -38497,12 +38508,12 @@
       <c r="AT340" t="inlineStr"/>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
@@ -38513,10 +38524,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>135351885</v>
+        <v>135357423</v>
       </c>
       <c r="B341" t="n">
-        <v>101293</v>
+        <v>99001</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -38524,37 +38535,37 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>224885</v>
+        <v>223049</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>600266</v>
+        <v>600172</v>
       </c>
       <c r="R341" t="n">
-        <v>7331350</v>
+        <v>7331318</v>
       </c>
       <c r="S341" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -38583,7 +38594,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -38593,7 +38604,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -38608,12 +38619,12 @@
       <c r="AT341" t="inlineStr"/>
       <c r="AW341" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr">
@@ -38624,10 +38635,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>135356966</v>
+        <v>135356967</v>
       </c>
       <c r="B342" t="n">
-        <v>101293</v>
+        <v>105771</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -38635,23 +38646,19 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>224885</v>
+        <v>224074</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Nordlundarv</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
+          <t>Stellaria nemorum subsp. nemorum</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
         <is>
@@ -38665,7 +38672,7 @@
         <v>7331362</v>
       </c>
       <c r="S342" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -38735,48 +38742,48 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>135350568</v>
+        <v>135351885</v>
       </c>
       <c r="B343" t="n">
-        <v>78382</v>
+        <v>101293</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>228579</v>
+        <v>224885</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>600361</v>
+        <v>600266</v>
       </c>
       <c r="R343" t="n">
-        <v>7331368</v>
+        <v>7331350</v>
       </c>
       <c r="S343" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -38805,7 +38812,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -38815,7 +38822,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -38830,12 +38837,12 @@
       <c r="AT343" t="inlineStr"/>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr">
@@ -38846,45 +38853,45 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>135350582</v>
+        <v>135356966</v>
       </c>
       <c r="B344" t="n">
-        <v>78382</v>
+        <v>101293</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>228579</v>
+        <v>224885</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
       <c r="P344" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>600208</v>
+        <v>600310</v>
       </c>
       <c r="R344" t="n">
-        <v>7331396</v>
+        <v>7331362</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -38916,7 +38923,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -38926,7 +38933,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD344" t="b">
@@ -38941,15 +38948,237 @@
       <c r="AT344" t="inlineStr"/>
       <c r="AW344" t="inlineStr">
         <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX344" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY344" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>135350568</v>
+      </c>
+      <c r="B345" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr"/>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q345" t="n">
+        <v>600361</v>
+      </c>
+      <c r="R345" t="n">
+        <v>7331368</v>
+      </c>
+      <c r="S345" t="n">
+        <v>14</v>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD345" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE345" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG345" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT345" t="inlineStr"/>
+      <c r="AW345" t="inlineStr">
+        <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AX344" t="inlineStr">
+      <c r="AX345" t="inlineStr">
         <is>
           <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
-      <c r="AY344" t="inlineStr">
+      <c r="AY345" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>135350582</v>
+      </c>
+      <c r="B346" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr"/>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q346" t="n">
+        <v>600208</v>
+      </c>
+      <c r="R346" t="n">
+        <v>7331396</v>
+      </c>
+      <c r="S346" t="n">
+        <v>5</v>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB346" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD346" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE346" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG346" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT346" t="inlineStr"/>
+      <c r="AW346" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX346" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY346" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY358"/>
+  <dimension ref="A1:AY359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31492,48 +31492,48 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>135350569</v>
+        <v>135357072</v>
       </c>
       <c r="B278" t="n">
-        <v>79373</v>
+        <v>91803</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6425</v>
+        <v>6020</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>600353</v>
+        <v>600083</v>
       </c>
       <c r="R278" t="n">
-        <v>7331366</v>
+        <v>7331559</v>
       </c>
       <c r="S278" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -31572,7 +31572,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -31581,18 +31581,24 @@
       <c r="AE278" t="b">
         <v>0</v>
       </c>
+      <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="b">
         <v>0</v>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
@@ -31603,7 +31609,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>135350570</v>
+        <v>135350569</v>
       </c>
       <c r="B279" t="n">
         <v>79373</v>
@@ -31638,13 +31644,13 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>600314</v>
+        <v>600353</v>
       </c>
       <c r="R279" t="n">
-        <v>7331380</v>
+        <v>7331366</v>
       </c>
       <c r="S279" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -31673,7 +31679,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -31683,7 +31689,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -31714,7 +31720,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>135350588</v>
+        <v>135350570</v>
       </c>
       <c r="B280" t="n">
         <v>79373</v>
@@ -31749,13 +31755,13 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>600165</v>
+        <v>600314</v>
       </c>
       <c r="R280" t="n">
-        <v>7331257</v>
+        <v>7331380</v>
       </c>
       <c r="S280" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -31784,7 +31790,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -31794,7 +31800,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -31825,7 +31831,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>135351882</v>
+        <v>135350588</v>
       </c>
       <c r="B281" t="n">
         <v>79373</v>
@@ -31856,17 +31862,17 @@
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>600296</v>
+        <v>600165</v>
       </c>
       <c r="R281" t="n">
-        <v>7331306</v>
+        <v>7331257</v>
       </c>
       <c r="S281" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -31895,7 +31901,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -31905,7 +31911,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -31920,12 +31926,12 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
@@ -31936,7 +31942,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>135351891</v>
+        <v>135351882</v>
       </c>
       <c r="B282" t="n">
         <v>79373</v>
@@ -31971,10 +31977,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>600232</v>
+        <v>600296</v>
       </c>
       <c r="R282" t="n">
-        <v>7331370</v>
+        <v>7331306</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -32006,7 +32012,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -32016,7 +32022,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -32047,7 +32053,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>135351896</v>
+        <v>135351891</v>
       </c>
       <c r="B283" t="n">
         <v>79373</v>
@@ -32082,10 +32088,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>600163</v>
+        <v>600232</v>
       </c>
       <c r="R283" t="n">
-        <v>7331263</v>
+        <v>7331370</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -32117,7 +32123,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -32127,7 +32133,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -32158,7 +32164,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>135351933</v>
+        <v>135351896</v>
       </c>
       <c r="B284" t="n">
         <v>79373</v>
@@ -32193,13 +32199,13 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>600130</v>
+        <v>600163</v>
       </c>
       <c r="R284" t="n">
-        <v>7331606</v>
+        <v>7331263</v>
       </c>
       <c r="S284" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -32228,7 +32234,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -32238,7 +32244,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -32269,7 +32275,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>135356965</v>
+        <v>135351933</v>
       </c>
       <c r="B285" t="n">
         <v>79373</v>
@@ -32300,17 +32306,17 @@
       <c r="I285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>600313</v>
+        <v>600130</v>
       </c>
       <c r="R285" t="n">
-        <v>7331354</v>
+        <v>7331606</v>
       </c>
       <c r="S285" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -32339,7 +32345,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -32349,7 +32355,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -32364,12 +32370,12 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
@@ -32380,7 +32386,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>135356986</v>
+        <v>135356965</v>
       </c>
       <c r="B286" t="n">
         <v>79373</v>
@@ -32415,13 +32421,13 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>600192</v>
+        <v>600313</v>
       </c>
       <c r="R286" t="n">
-        <v>7331349</v>
+        <v>7331354</v>
       </c>
       <c r="S286" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -32450,7 +32456,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -32460,7 +32466,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -32491,7 +32497,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>135357069</v>
+        <v>135356986</v>
       </c>
       <c r="B287" t="n">
         <v>79373</v>
@@ -32526,10 +32532,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>600085</v>
+        <v>600192</v>
       </c>
       <c r="R287" t="n">
-        <v>7331514</v>
+        <v>7331349</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -32561,7 +32567,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -32571,7 +32577,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -32602,7 +32608,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>135357071</v>
+        <v>135357069</v>
       </c>
       <c r="B288" t="n">
         <v>79373</v>
@@ -32637,10 +32643,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>600083</v>
+        <v>600085</v>
       </c>
       <c r="R288" t="n">
-        <v>7331533</v>
+        <v>7331514</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -32672,7 +32678,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -32682,7 +32688,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -32713,7 +32719,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>135357722</v>
+        <v>135357071</v>
       </c>
       <c r="B289" t="n">
         <v>79373</v>
@@ -32742,19 +32748,16 @@
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
-      <c r="N289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>600176</v>
+        <v>600083</v>
       </c>
       <c r="R289" t="n">
-        <v>7331284</v>
+        <v>7331533</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -32786,7 +32789,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -32796,7 +32799,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -32805,19 +32808,18 @@
       <c r="AE289" t="b">
         <v>0</v>
       </c>
-      <c r="AF289" t="inlineStr"/>
       <c r="AG289" t="b">
         <v>0</v>
       </c>
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
@@ -32828,45 +32830,48 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>135356979</v>
+        <v>135357722</v>
       </c>
       <c r="B290" t="n">
-        <v>75340</v>
+        <v>79373</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>600207</v>
+        <v>600176</v>
       </c>
       <c r="R290" t="n">
-        <v>7331365</v>
+        <v>7331284</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -32898,7 +32903,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -32908,7 +32913,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -32917,18 +32922,19 @@
       <c r="AE290" t="b">
         <v>0</v>
       </c>
+      <c r="AF290" t="inlineStr"/>
       <c r="AG290" t="b">
         <v>0</v>
       </c>
       <c r="AT290" t="inlineStr"/>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
@@ -32939,10 +32945,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>135350587</v>
+        <v>135356979</v>
       </c>
       <c r="B291" t="n">
-        <v>83341</v>
+        <v>75340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32950,34 +32956,34 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>600187</v>
+        <v>600207</v>
       </c>
       <c r="R291" t="n">
-        <v>7331296</v>
+        <v>7331365</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -33009,7 +33015,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -33019,7 +33025,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -33034,12 +33040,12 @@
       <c r="AT291" t="inlineStr"/>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
@@ -33050,7 +33056,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>135356993</v>
+        <v>135350587</v>
       </c>
       <c r="B292" t="n">
         <v>83341</v>
@@ -33081,14 +33087,14 @@
       <c r="I292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>600066</v>
+        <v>600187</v>
       </c>
       <c r="R292" t="n">
-        <v>7331231</v>
+        <v>7331296</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -33120,7 +33126,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -33130,7 +33136,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -33145,12 +33151,12 @@
       <c r="AT292" t="inlineStr"/>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr">
@@ -33161,7 +33167,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>135357451</v>
+        <v>135356993</v>
       </c>
       <c r="B293" t="n">
         <v>83341</v>
@@ -33192,17 +33198,17 @@
       <c r="I293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>600065</v>
+        <v>600066</v>
       </c>
       <c r="R293" t="n">
-        <v>7331283</v>
+        <v>7331231</v>
       </c>
       <c r="S293" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -33231,7 +33237,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -33241,7 +33247,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -33256,12 +33262,12 @@
       <c r="AT293" t="inlineStr"/>
       <c r="AW293" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr">
@@ -33272,48 +33278,48 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>135350572</v>
+        <v>135357451</v>
       </c>
       <c r="B294" t="n">
-        <v>83358</v>
+        <v>83341</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>600311</v>
+        <v>600065</v>
       </c>
       <c r="R294" t="n">
-        <v>7331348</v>
+        <v>7331283</v>
       </c>
       <c r="S294" t="n">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -33342,7 +33348,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -33352,7 +33358,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -33367,12 +33373,12 @@
       <c r="AT294" t="inlineStr"/>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">
@@ -33383,7 +33389,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>135350580</v>
+        <v>135350572</v>
       </c>
       <c r="B295" t="n">
         <v>83358</v>
@@ -33418,13 +33424,13 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>600229</v>
+        <v>600311</v>
       </c>
       <c r="R295" t="n">
-        <v>7331364</v>
+        <v>7331348</v>
       </c>
       <c r="S295" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -33453,7 +33459,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -33463,7 +33469,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -33494,7 +33500,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>135351877</v>
+        <v>135350580</v>
       </c>
       <c r="B296" t="n">
         <v>83358</v>
@@ -33525,17 +33531,17 @@
       <c r="I296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>600358</v>
+        <v>600229</v>
       </c>
       <c r="R296" t="n">
-        <v>7331345</v>
+        <v>7331364</v>
       </c>
       <c r="S296" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -33564,7 +33570,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -33574,7 +33580,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -33589,12 +33595,12 @@
       <c r="AT296" t="inlineStr"/>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
@@ -33605,7 +33611,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>135354294</v>
+        <v>135351877</v>
       </c>
       <c r="B297" t="n">
         <v>83358</v>
@@ -33636,17 +33642,17 @@
       <c r="I297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>600351</v>
+        <v>600358</v>
       </c>
       <c r="R297" t="n">
-        <v>7331356</v>
+        <v>7331345</v>
       </c>
       <c r="S297" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
@@ -33700,12 +33706,12 @@
       <c r="AT297" t="inlineStr"/>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
@@ -33716,7 +33722,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>135354298</v>
+        <v>135354294</v>
       </c>
       <c r="B298" t="n">
         <v>83358</v>
@@ -33751,10 +33757,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>600143</v>
+        <v>600351</v>
       </c>
       <c r="R298" t="n">
-        <v>7331397</v>
+        <v>7331356</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -33786,7 +33792,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -33796,7 +33802,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -33827,7 +33833,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>135356964</v>
+        <v>135354298</v>
       </c>
       <c r="B299" t="n">
         <v>83358</v>
@@ -33858,14 +33864,14 @@
       <c r="I299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>600312</v>
+        <v>600143</v>
       </c>
       <c r="R299" t="n">
-        <v>7331352</v>
+        <v>7331397</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -33897,7 +33903,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -33907,7 +33913,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -33922,12 +33928,12 @@
       <c r="AT299" t="inlineStr"/>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
@@ -33938,7 +33944,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>135356969</v>
+        <v>135356964</v>
       </c>
       <c r="B300" t="n">
         <v>83358</v>
@@ -33973,13 +33979,13 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>600307</v>
+        <v>600312</v>
       </c>
       <c r="R300" t="n">
-        <v>7331359</v>
+        <v>7331352</v>
       </c>
       <c r="S300" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T300" t="inlineStr">
         <is>
@@ -34008,7 +34014,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -34018,7 +34024,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -34049,7 +34055,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>135357070</v>
+        <v>135356969</v>
       </c>
       <c r="B301" t="n">
         <v>83358</v>
@@ -34084,13 +34090,13 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>600081</v>
+        <v>600307</v>
       </c>
       <c r="R301" t="n">
-        <v>7331525</v>
+        <v>7331359</v>
       </c>
       <c r="S301" t="n">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -34119,7 +34125,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -34129,7 +34135,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -34160,7 +34166,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>135357077</v>
+        <v>135357070</v>
       </c>
       <c r="B302" t="n">
         <v>83358</v>
@@ -34195,13 +34201,13 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>600368</v>
+        <v>600081</v>
       </c>
       <c r="R302" t="n">
-        <v>7331322</v>
+        <v>7331525</v>
       </c>
       <c r="S302" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -34230,7 +34236,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -34240,7 +34246,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -34271,7 +34277,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>135357444</v>
+        <v>135357077</v>
       </c>
       <c r="B303" t="n">
         <v>83358</v>
@@ -34302,17 +34308,17 @@
       <c r="I303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>600198</v>
+        <v>600368</v>
       </c>
       <c r="R303" t="n">
-        <v>7331357</v>
+        <v>7331322</v>
       </c>
       <c r="S303" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -34341,7 +34347,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -34351,7 +34357,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -34366,12 +34372,12 @@
       <c r="AT303" t="inlineStr"/>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
@@ -34382,7 +34388,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>135357486</v>
+        <v>135357444</v>
       </c>
       <c r="B304" t="n">
         <v>83358</v>
@@ -34417,13 +34423,13 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>600111</v>
+        <v>600198</v>
       </c>
       <c r="R304" t="n">
-        <v>7331482</v>
+        <v>7331357</v>
       </c>
       <c r="S304" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -34452,7 +34458,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -34462,7 +34468,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -34493,10 +34499,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>135357447</v>
+        <v>135357486</v>
       </c>
       <c r="B305" t="n">
-        <v>80488</v>
+        <v>83358</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -34504,21 +34510,21 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -34528,13 +34534,13 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>600173</v>
+        <v>600111</v>
       </c>
       <c r="R305" t="n">
-        <v>7331345</v>
+        <v>7331482</v>
       </c>
       <c r="S305" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -34563,7 +34569,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -34573,12 +34579,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC305" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -34609,7 +34610,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>135361464</v>
+        <v>135357447</v>
       </c>
       <c r="B306" t="n">
         <v>80488</v>
@@ -34640,17 +34641,17 @@
       <c r="I306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
-          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>600109</v>
+        <v>600173</v>
       </c>
       <c r="R306" t="n">
-        <v>7331546</v>
+        <v>7331345</v>
       </c>
       <c r="S306" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -34679,7 +34680,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -34689,7 +34690,12 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC306" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -34704,12 +34710,12 @@
       <c r="AT306" t="inlineStr"/>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Moa Turid Lövdahl</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
@@ -34720,48 +34726,48 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>135350593</v>
+        <v>135361464</v>
       </c>
       <c r="B307" t="n">
-        <v>80493</v>
+        <v>80488</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>600068</v>
+        <v>600109</v>
       </c>
       <c r="R307" t="n">
-        <v>7331214</v>
+        <v>7331546</v>
       </c>
       <c r="S307" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -34790,7 +34796,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -34800,7 +34806,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -34815,12 +34821,12 @@
       <c r="AT307" t="inlineStr"/>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Moa Turid Lövdahl</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
@@ -34831,7 +34837,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>135356991</v>
+        <v>135350593</v>
       </c>
       <c r="B308" t="n">
         <v>80493</v>
@@ -34862,17 +34868,17 @@
       <c r="I308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>600066</v>
+        <v>600068</v>
       </c>
       <c r="R308" t="n">
-        <v>7331234</v>
+        <v>7331214</v>
       </c>
       <c r="S308" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -34901,7 +34907,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -34911,7 +34917,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -34926,12 +34932,12 @@
       <c r="AT308" t="inlineStr"/>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
@@ -34942,10 +34948,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>135357721</v>
+        <v>135356991</v>
       </c>
       <c r="B309" t="n">
-        <v>80500</v>
+        <v>80493</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -34953,37 +34959,37 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>600199</v>
+        <v>600066</v>
       </c>
       <c r="R309" t="n">
-        <v>7331404</v>
+        <v>7331234</v>
       </c>
       <c r="S309" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -35012,7 +35018,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -35022,7 +35028,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -35037,12 +35043,12 @@
       <c r="AT309" t="inlineStr"/>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
@@ -35053,53 +35059,48 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>135350576</v>
+        <v>135357721</v>
       </c>
       <c r="B310" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
-      <c r="M310" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>600274</v>
+        <v>600199</v>
       </c>
       <c r="R310" t="n">
-        <v>7331368</v>
+        <v>7331404</v>
       </c>
       <c r="S310" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -35128,7 +35129,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -35138,7 +35139,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD310" t="b">
@@ -35153,12 +35154,12 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
@@ -35169,7 +35170,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>135350583</v>
+        <v>135350576</v>
       </c>
       <c r="B311" t="n">
         <v>57975</v>
@@ -35209,13 +35210,13 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>600166</v>
+        <v>600274</v>
       </c>
       <c r="R311" t="n">
-        <v>7331334</v>
+        <v>7331368</v>
       </c>
       <c r="S311" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -35244,7 +35245,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -35254,7 +35255,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD311" t="b">
@@ -35285,7 +35286,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>135350764</v>
+        <v>135350583</v>
       </c>
       <c r="B312" t="n">
         <v>57975</v>
@@ -35314,19 +35315,24 @@
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>600272</v>
+        <v>600166</v>
       </c>
       <c r="R312" t="n">
-        <v>7331401</v>
+        <v>7331334</v>
       </c>
       <c r="S312" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -35355,7 +35361,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -35365,12 +35371,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC312" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -35385,12 +35386,12 @@
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
@@ -35401,7 +35402,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>135354320</v>
+        <v>135350764</v>
       </c>
       <c r="B313" t="n">
         <v>57975</v>
@@ -35432,17 +35433,17 @@
       <c r="I313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>600173</v>
+        <v>600272</v>
       </c>
       <c r="R313" t="n">
-        <v>7331326</v>
+        <v>7331401</v>
       </c>
       <c r="S313" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -35471,7 +35472,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -35481,12 +35482,12 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -35501,12 +35502,12 @@
       <c r="AT313" t="inlineStr"/>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
@@ -35517,7 +35518,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>135357488</v>
+        <v>135354320</v>
       </c>
       <c r="B314" t="n">
         <v>57975</v>
@@ -35546,27 +35547,19 @@
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>600078</v>
+        <v>600173</v>
       </c>
       <c r="R314" t="n">
-        <v>7331554</v>
+        <v>7331326</v>
       </c>
       <c r="S314" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -35595,7 +35588,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -35605,12 +35598,12 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
         <is>
-          <t>Gammalt bohål i gran angripen av granticka som verkar stämma med måtten för den tretåiga hackspettens bohål</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -35625,12 +35618,12 @@
       <c r="AT314" t="inlineStr"/>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
@@ -35641,7 +35634,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>135363067</v>
+        <v>135357488</v>
       </c>
       <c r="B315" t="n">
         <v>57975</v>
@@ -35670,24 +35663,27 @@
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
           <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>600163</v>
+        <v>600078</v>
       </c>
       <c r="R315" t="n">
-        <v>7331326</v>
+        <v>7331554</v>
       </c>
       <c r="S315" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
@@ -35716,7 +35712,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -35726,12 +35722,12 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gammalt bohål i gran angripen av granticka som verkar stämma med måtten för den tretåiga hackspettens bohål</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -35746,12 +35742,12 @@
       <c r="AT315" t="inlineStr"/>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Amanda Wiker Briceño</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>Amanda Wiker Briceño</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
@@ -35762,10 +35758,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>135350578</v>
+        <v>135363067</v>
       </c>
       <c r="B316" t="n">
-        <v>58079</v>
+        <v>57975</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -35773,16 +35769,16 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -35791,19 +35787,24 @@
         </is>
       </c>
       <c r="I316" t="inlineStr"/>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>600263</v>
+        <v>600163</v>
       </c>
       <c r="R316" t="n">
-        <v>7331376</v>
+        <v>7331326</v>
       </c>
       <c r="S316" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T316" t="inlineStr">
         <is>
@@ -35832,7 +35833,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -35842,7 +35843,12 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -35857,12 +35863,12 @@
       <c r="AT316" t="inlineStr"/>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Amanda Wiker Briceño</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Amanda Wiker Briceño</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
@@ -35873,7 +35879,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>135354424</v>
+        <v>135350578</v>
       </c>
       <c r="B317" t="n">
         <v>58079</v>
@@ -35904,17 +35910,17 @@
       <c r="I317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>600223</v>
+        <v>600263</v>
       </c>
       <c r="R317" t="n">
-        <v>7331526</v>
+        <v>7331376</v>
       </c>
       <c r="S317" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -35943,7 +35949,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -35953,7 +35959,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -35968,12 +35974,12 @@
       <c r="AT317" t="inlineStr"/>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
@@ -35984,7 +35990,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>135356970</v>
+        <v>135354424</v>
       </c>
       <c r="B318" t="n">
         <v>58079</v>
@@ -36015,17 +36021,17 @@
       <c r="I318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>600313</v>
+        <v>600223</v>
       </c>
       <c r="R318" t="n">
-        <v>7331351</v>
+        <v>7331526</v>
       </c>
       <c r="S318" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -36054,7 +36060,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -36064,7 +36070,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -36079,12 +36085,12 @@
       <c r="AT318" t="inlineStr"/>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
@@ -36095,7 +36101,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>135357424</v>
+        <v>135356970</v>
       </c>
       <c r="B319" t="n">
         <v>58079</v>
@@ -36126,17 +36132,17 @@
       <c r="I319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>600144</v>
+        <v>600313</v>
       </c>
       <c r="R319" t="n">
-        <v>7331309</v>
+        <v>7331351</v>
       </c>
       <c r="S319" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -36165,7 +36171,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -36175,7 +36181,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -36190,12 +36196,12 @@
       <c r="AT319" t="inlineStr"/>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
@@ -36206,48 +36212,48 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>135354385</v>
+        <v>135357424</v>
       </c>
       <c r="B320" t="n">
-        <v>92661</v>
+        <v>58079</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>106596</v>
+        <v>103031</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Nordlig parasitporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>600167</v>
+        <v>600144</v>
       </c>
       <c r="R320" t="n">
-        <v>7331292</v>
+        <v>7331309</v>
       </c>
       <c r="S320" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="T320" t="inlineStr">
         <is>
@@ -36276,7 +36282,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -36286,7 +36292,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -36301,12 +36307,12 @@
       <c r="AT320" t="inlineStr"/>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
@@ -36317,48 +36323,48 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>135363079</v>
+        <v>135354385</v>
       </c>
       <c r="B321" t="n">
-        <v>58839</v>
+        <v>92661</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>208249</v>
+        <v>106596</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>600184</v>
+        <v>600167</v>
       </c>
       <c r="R321" t="n">
-        <v>7331550</v>
+        <v>7331292</v>
       </c>
       <c r="S321" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -36387,7 +36393,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -36397,7 +36403,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -36412,12 +36418,12 @@
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Amanda Wiker Briceño</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Amanda Wiker Briceño</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
@@ -36428,10 +36434,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>135354316</v>
+        <v>135363079</v>
       </c>
       <c r="B322" t="n">
-        <v>99112</v>
+        <v>58839</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -36439,37 +36445,37 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>600064</v>
+        <v>600184</v>
       </c>
       <c r="R322" t="n">
-        <v>7331520</v>
+        <v>7331550</v>
       </c>
       <c r="S322" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -36498,7 +36504,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -36508,7 +36514,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -36523,12 +36529,12 @@
       <c r="AT322" t="inlineStr"/>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Amanda Wiker Briceño</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Amanda Wiker Briceño</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
@@ -36539,7 +36545,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>135356990</v>
+        <v>135354316</v>
       </c>
       <c r="B323" t="n">
         <v>99112</v>
@@ -36570,17 +36576,17 @@
       <c r="I323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>600178</v>
+        <v>600064</v>
       </c>
       <c r="R323" t="n">
-        <v>7331297</v>
+        <v>7331520</v>
       </c>
       <c r="S323" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -36609,7 +36615,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -36619,7 +36625,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -36634,12 +36640,12 @@
       <c r="AT323" t="inlineStr"/>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
@@ -36650,7 +36656,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>135357428</v>
+        <v>135356990</v>
       </c>
       <c r="B324" t="n">
         <v>99112</v>
@@ -36681,17 +36687,17 @@
       <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>600147</v>
+        <v>600178</v>
       </c>
       <c r="R324" t="n">
-        <v>7331298</v>
+        <v>7331297</v>
       </c>
       <c r="S324" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -36720,7 +36726,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -36730,7 +36736,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -36745,12 +36751,12 @@
       <c r="AT324" t="inlineStr"/>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -36761,7 +36767,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>135357723</v>
+        <v>135357428</v>
       </c>
       <c r="B325" t="n">
         <v>99112</v>
@@ -36792,17 +36798,17 @@
       <c r="I325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>600154</v>
+        <v>600147</v>
       </c>
       <c r="R325" t="n">
-        <v>7331294</v>
+        <v>7331298</v>
       </c>
       <c r="S325" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -36831,7 +36837,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -36841,7 +36847,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -36856,12 +36862,12 @@
       <c r="AT325" t="inlineStr"/>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>Laura Dobrandt</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
@@ -36872,7 +36878,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>135363068</v>
+        <v>135357723</v>
       </c>
       <c r="B326" t="n">
         <v>99112</v>
@@ -36903,14 +36909,14 @@
       <c r="I326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>600153</v>
+        <v>600154</v>
       </c>
       <c r="R326" t="n">
-        <v>7331289</v>
+        <v>7331294</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -36942,7 +36948,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -36952,7 +36958,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD326" t="b">
@@ -36967,12 +36973,12 @@
       <c r="AT326" t="inlineStr"/>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>Amanda Wiker Briceño</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>Amanda Wiker Briceño</t>
+          <t>Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr">
@@ -36983,10 +36989,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>135357413</v>
+        <v>135363068</v>
       </c>
       <c r="B327" t="n">
-        <v>99094</v>
+        <v>99112</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36994,21 +37000,21 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
@@ -37018,13 +37024,13 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>600302</v>
+        <v>600153</v>
       </c>
       <c r="R327" t="n">
-        <v>7331340</v>
+        <v>7331289</v>
       </c>
       <c r="S327" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -37053,7 +37059,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -37063,7 +37069,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -37078,12 +37084,12 @@
       <c r="AT327" t="inlineStr"/>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Amanda Wiker Briceño</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Amanda Wiker Briceño</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
@@ -37094,10 +37100,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>135351879</v>
+        <v>135357413</v>
       </c>
       <c r="B328" t="n">
-        <v>98219</v>
+        <v>99094</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -37105,34 +37111,34 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>219815</v>
+        <v>219795</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>600306</v>
+        <v>600302</v>
       </c>
       <c r="R328" t="n">
-        <v>7331319</v>
+        <v>7331340</v>
       </c>
       <c r="S328" t="n">
         <v>7</v>
@@ -37164,7 +37170,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -37174,7 +37180,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD328" t="b">
@@ -37189,12 +37195,12 @@
       <c r="AT328" t="inlineStr"/>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
@@ -37205,10 +37211,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>135350571</v>
+        <v>135351879</v>
       </c>
       <c r="B329" t="n">
-        <v>108205</v>
+        <v>98219</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -37216,37 +37222,37 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>220083</v>
+        <v>219815</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>600308</v>
+        <v>600306</v>
       </c>
       <c r="R329" t="n">
-        <v>7331355</v>
+        <v>7331319</v>
       </c>
       <c r="S329" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -37275,7 +37281,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -37285,7 +37291,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -37300,12 +37306,12 @@
       <c r="AT329" t="inlineStr"/>
       <c r="AW329" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
@@ -37316,10 +37322,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>135357421</v>
+        <v>135350571</v>
       </c>
       <c r="B330" t="n">
-        <v>99099</v>
+        <v>108205</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -37327,37 +37333,37 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>220093</v>
+        <v>220083</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>600182</v>
+        <v>600308</v>
       </c>
       <c r="R330" t="n">
-        <v>7331307</v>
+        <v>7331355</v>
       </c>
       <c r="S330" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -37386,7 +37392,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -37396,7 +37402,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -37411,12 +37417,12 @@
       <c r="AT330" t="inlineStr"/>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
@@ -37427,10 +37433,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>135356968</v>
+        <v>135357421</v>
       </c>
       <c r="B331" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -37438,37 +37444,37 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>600309</v>
+        <v>600182</v>
       </c>
       <c r="R331" t="n">
-        <v>7331352</v>
+        <v>7331307</v>
       </c>
       <c r="S331" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -37497,7 +37503,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -37507,7 +37513,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -37522,12 +37528,12 @@
       <c r="AT331" t="inlineStr"/>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr">
@@ -37538,10 +37544,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>135357440</v>
+        <v>135356968</v>
       </c>
       <c r="B332" t="n">
-        <v>109924</v>
+        <v>108274</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -37549,37 +37555,37 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>221184</v>
+        <v>220102</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>600294</v>
+        <v>600309</v>
       </c>
       <c r="R332" t="n">
-        <v>7331371</v>
+        <v>7331352</v>
       </c>
       <c r="S332" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -37608,7 +37614,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -37618,7 +37624,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -37633,12 +37639,12 @@
       <c r="AT332" t="inlineStr"/>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
@@ -37649,48 +37655,48 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>135354425</v>
+        <v>135357440</v>
       </c>
       <c r="B333" t="n">
-        <v>102541</v>
+        <v>109924</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>221343</v>
+        <v>221184</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>600233</v>
+        <v>600294</v>
       </c>
       <c r="R333" t="n">
-        <v>7331537</v>
+        <v>7331371</v>
       </c>
       <c r="S333" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -37719,7 +37725,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -37729,7 +37735,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -37738,19 +37744,18 @@
       <c r="AE333" t="b">
         <v>0</v>
       </c>
-      <c r="AF333" t="inlineStr"/>
       <c r="AG333" t="b">
         <v>0</v>
       </c>
       <c r="AT333" t="inlineStr"/>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr">
@@ -37761,48 +37766,48 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>135351883</v>
+        <v>135354425</v>
       </c>
       <c r="B334" t="n">
-        <v>106309</v>
+        <v>102541</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>221725</v>
+        <v>221343</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>600318</v>
+        <v>600233</v>
       </c>
       <c r="R334" t="n">
-        <v>7331322</v>
+        <v>7331537</v>
       </c>
       <c r="S334" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -37831,7 +37836,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -37841,7 +37846,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -37850,18 +37855,19 @@
       <c r="AE334" t="b">
         <v>0</v>
       </c>
+      <c r="AF334" t="inlineStr"/>
       <c r="AG334" t="b">
         <v>0</v>
       </c>
       <c r="AT334" t="inlineStr"/>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr">
@@ -37872,7 +37878,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>135351890</v>
+        <v>135351883</v>
       </c>
       <c r="B335" t="n">
         <v>106309</v>
@@ -37907,13 +37913,13 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>600233</v>
+        <v>600318</v>
       </c>
       <c r="R335" t="n">
-        <v>7331385</v>
+        <v>7331322</v>
       </c>
       <c r="S335" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -37942,7 +37948,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -37952,7 +37958,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -37983,7 +37989,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>135351895</v>
+        <v>135351890</v>
       </c>
       <c r="B336" t="n">
         <v>106309</v>
@@ -38018,13 +38024,13 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>600190</v>
+        <v>600233</v>
       </c>
       <c r="R336" t="n">
-        <v>7331355</v>
+        <v>7331385</v>
       </c>
       <c r="S336" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -38053,7 +38059,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -38063,7 +38069,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -38094,7 +38100,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>135357411</v>
+        <v>135351895</v>
       </c>
       <c r="B337" t="n">
         <v>106309</v>
@@ -38125,17 +38131,17 @@
       <c r="I337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>600334</v>
+        <v>600190</v>
       </c>
       <c r="R337" t="n">
-        <v>7331370</v>
+        <v>7331355</v>
       </c>
       <c r="S337" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -38164,7 +38170,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -38174,7 +38180,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -38189,12 +38195,12 @@
       <c r="AT337" t="inlineStr"/>
       <c r="AW337" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
@@ -38205,7 +38211,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>135357417</v>
+        <v>135357411</v>
       </c>
       <c r="B338" t="n">
         <v>106309</v>
@@ -38240,13 +38246,13 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>600250</v>
+        <v>600334</v>
       </c>
       <c r="R338" t="n">
-        <v>7331298</v>
+        <v>7331370</v>
       </c>
       <c r="S338" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -38275,7 +38281,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -38285,7 +38291,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -38316,7 +38322,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>135357426</v>
+        <v>135357417</v>
       </c>
       <c r="B339" t="n">
         <v>106309</v>
@@ -38351,13 +38357,13 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>600130</v>
+        <v>600250</v>
       </c>
       <c r="R339" t="n">
-        <v>7331303</v>
+        <v>7331298</v>
       </c>
       <c r="S339" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -38386,7 +38392,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -38396,7 +38402,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -38427,7 +38433,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>135357429</v>
+        <v>135357426</v>
       </c>
       <c r="B340" t="n">
         <v>106309</v>
@@ -38462,13 +38468,13 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>600104</v>
+        <v>600130</v>
       </c>
       <c r="R340" t="n">
-        <v>7331449</v>
+        <v>7331303</v>
       </c>
       <c r="S340" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -38497,7 +38503,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -38507,7 +38513,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -38538,10 +38544,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>135351878</v>
+        <v>135357429</v>
       </c>
       <c r="B341" t="n">
-        <v>99217</v>
+        <v>106309</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -38549,37 +38555,37 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>600337</v>
+        <v>600104</v>
       </c>
       <c r="R341" t="n">
-        <v>7331349</v>
+        <v>7331449</v>
       </c>
       <c r="S341" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -38608,7 +38614,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -38618,7 +38624,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD341" t="b">
@@ -38633,12 +38639,12 @@
       <c r="AT341" t="inlineStr"/>
       <c r="AW341" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr">
@@ -38649,7 +38655,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>135351888</v>
+        <v>135351878</v>
       </c>
       <c r="B342" t="n">
         <v>99217</v>
@@ -38684,13 +38690,13 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>600264</v>
+        <v>600337</v>
       </c>
       <c r="R342" t="n">
-        <v>7331324</v>
+        <v>7331349</v>
       </c>
       <c r="S342" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -38719,7 +38725,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -38729,7 +38735,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD342" t="b">
@@ -38760,7 +38766,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>135356971</v>
+        <v>135351888</v>
       </c>
       <c r="B343" t="n">
         <v>99217</v>
@@ -38791,17 +38797,17 @@
       <c r="I343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>600311</v>
+        <v>600264</v>
       </c>
       <c r="R343" t="n">
-        <v>7331344</v>
+        <v>7331324</v>
       </c>
       <c r="S343" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -38830,7 +38836,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -38840,7 +38846,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD343" t="b">
@@ -38855,12 +38861,12 @@
       <c r="AT343" t="inlineStr"/>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr">
@@ -38871,7 +38877,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>135357078</v>
+        <v>135356971</v>
       </c>
       <c r="B344" t="n">
         <v>99217</v>
@@ -38906,13 +38912,13 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>600368</v>
+        <v>600311</v>
       </c>
       <c r="R344" t="n">
-        <v>7331322</v>
+        <v>7331344</v>
       </c>
       <c r="S344" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T344" t="inlineStr">
         <is>
@@ -38941,7 +38947,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -38951,7 +38957,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD344" t="b">
@@ -38982,7 +38988,7 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>135357410</v>
+        <v>135357078</v>
       </c>
       <c r="B345" t="n">
         <v>99217</v>
@@ -39013,14 +39019,14 @@
       <c r="I345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>600354</v>
+        <v>600368</v>
       </c>
       <c r="R345" t="n">
-        <v>7331358</v>
+        <v>7331322</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -39052,7 +39058,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -39062,7 +39068,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD345" t="b">
@@ -39077,12 +39083,12 @@
       <c r="AT345" t="inlineStr"/>
       <c r="AW345" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr">
@@ -39093,7 +39099,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>135357422</v>
+        <v>135357410</v>
       </c>
       <c r="B346" t="n">
         <v>99217</v>
@@ -39128,13 +39134,13 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>600175</v>
+        <v>600354</v>
       </c>
       <c r="R346" t="n">
-        <v>7331319</v>
+        <v>7331358</v>
       </c>
       <c r="S346" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -39163,7 +39169,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -39173,7 +39179,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD346" t="b">
@@ -39204,10 +39210,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>135357415</v>
+        <v>135357422</v>
       </c>
       <c r="B347" t="n">
-        <v>104707</v>
+        <v>99217</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -39215,21 +39221,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
@@ -39239,13 +39245,13 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>600265</v>
+        <v>600175</v>
       </c>
       <c r="R347" t="n">
-        <v>7331310</v>
+        <v>7331319</v>
       </c>
       <c r="S347" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -39274,7 +39280,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -39284,7 +39290,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD347" t="b">
@@ -39315,7 +39321,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>135357416</v>
+        <v>135357415</v>
       </c>
       <c r="B348" t="n">
         <v>104707</v>
@@ -39350,13 +39356,13 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>600258</v>
+        <v>600265</v>
       </c>
       <c r="R348" t="n">
-        <v>7331287</v>
+        <v>7331310</v>
       </c>
       <c r="S348" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -39385,7 +39391,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -39395,7 +39401,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD348" t="b">
@@ -39426,7 +39432,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>135357427</v>
+        <v>135357416</v>
       </c>
       <c r="B349" t="n">
         <v>104707</v>
@@ -39461,13 +39467,13 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>600156</v>
+        <v>600258</v>
       </c>
       <c r="R349" t="n">
-        <v>7331306</v>
+        <v>7331287</v>
       </c>
       <c r="S349" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T349" t="inlineStr">
         <is>
@@ -39496,7 +39502,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -39506,7 +39512,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD349" t="b">
@@ -39537,10 +39543,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>135357412</v>
+        <v>135357427</v>
       </c>
       <c r="B350" t="n">
-        <v>102871</v>
+        <v>104707</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -39548,16 +39554,16 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>223037</v>
+        <v>222412</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -39572,13 +39578,13 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>600334</v>
+        <v>600156</v>
       </c>
       <c r="R350" t="n">
-        <v>7331370</v>
+        <v>7331306</v>
       </c>
       <c r="S350" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -39607,7 +39613,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -39617,7 +39623,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD350" t="b">
@@ -39648,10 +39654,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>135351880</v>
+        <v>135357412</v>
       </c>
       <c r="B351" t="n">
-        <v>99001</v>
+        <v>102871</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -39659,16 +39665,16 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>223049</v>
+        <v>223037</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -39679,17 +39685,17 @@
       <c r="I351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>600310</v>
+        <v>600334</v>
       </c>
       <c r="R351" t="n">
-        <v>7331313</v>
+        <v>7331370</v>
       </c>
       <c r="S351" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -39718,7 +39724,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -39728,7 +39734,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD351" t="b">
@@ -39743,12 +39749,12 @@
       <c r="AT351" t="inlineStr"/>
       <c r="AW351" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr">
@@ -39759,7 +39765,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>135357418</v>
+        <v>135351880</v>
       </c>
       <c r="B352" t="n">
         <v>99001</v>
@@ -39790,17 +39796,17 @@
       <c r="I352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>600187</v>
+        <v>600310</v>
       </c>
       <c r="R352" t="n">
-        <v>7331321</v>
+        <v>7331313</v>
       </c>
       <c r="S352" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -39829,7 +39835,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -39839,7 +39845,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD352" t="b">
@@ -39854,12 +39860,12 @@
       <c r="AT352" t="inlineStr"/>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr">
@@ -39870,7 +39876,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>135357423</v>
+        <v>135357418</v>
       </c>
       <c r="B353" t="n">
         <v>99001</v>
@@ -39905,13 +39911,13 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>600172</v>
+        <v>600187</v>
       </c>
       <c r="R353" t="n">
-        <v>7331318</v>
+        <v>7331321</v>
       </c>
       <c r="S353" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -39940,7 +39946,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -39950,7 +39956,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD353" t="b">
@@ -39981,10 +39987,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>135356967</v>
+        <v>135357423</v>
       </c>
       <c r="B354" t="n">
-        <v>105771</v>
+        <v>99001</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -39992,33 +39998,37 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>224074</v>
+        <v>223049</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Nordlundarv</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Stellaria nemorum subsp. nemorum</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr"/>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>600310</v>
+        <v>600172</v>
       </c>
       <c r="R354" t="n">
-        <v>7331362</v>
+        <v>7331318</v>
       </c>
       <c r="S354" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -40047,7 +40057,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -40057,7 +40067,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD354" t="b">
@@ -40072,12 +40082,12 @@
       <c r="AT354" t="inlineStr"/>
       <c r="AW354" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Agne  Jonsson</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr">
@@ -40088,10 +40098,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>135351885</v>
+        <v>135356967</v>
       </c>
       <c r="B355" t="n">
-        <v>101293</v>
+        <v>105771</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -40099,37 +40109,33 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>224885</v>
+        <v>224074</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Nordlundarv</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
+          <t>Stellaria nemorum subsp. nemorum</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>600266</v>
+        <v>600310</v>
       </c>
       <c r="R355" t="n">
-        <v>7331350</v>
+        <v>7331362</v>
       </c>
       <c r="S355" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -40158,7 +40164,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -40168,7 +40174,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD355" t="b">
@@ -40183,12 +40189,12 @@
       <c r="AT355" t="inlineStr"/>
       <c r="AW355" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr">
@@ -40199,7 +40205,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>135356966</v>
+        <v>135351885</v>
       </c>
       <c r="B356" t="n">
         <v>101293</v>
@@ -40230,17 +40236,17 @@
       <c r="I356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>600310</v>
+        <v>600266</v>
       </c>
       <c r="R356" t="n">
-        <v>7331362</v>
+        <v>7331350</v>
       </c>
       <c r="S356" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -40269,7 +40275,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -40279,7 +40285,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD356" t="b">
@@ -40294,12 +40300,12 @@
       <c r="AT356" t="inlineStr"/>
       <c r="AW356" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
@@ -40310,48 +40316,48 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>135350568</v>
+        <v>135356966</v>
       </c>
       <c r="B357" t="n">
-        <v>78382</v>
+        <v>101293</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>228579</v>
+        <v>224885</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I357" t="inlineStr"/>
       <c r="P357" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>600361</v>
+        <v>600310</v>
       </c>
       <c r="R357" t="n">
-        <v>7331368</v>
+        <v>7331362</v>
       </c>
       <c r="S357" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -40380,7 +40386,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -40390,7 +40396,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD357" t="b">
@@ -40405,12 +40411,12 @@
       <c r="AT357" t="inlineStr"/>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
@@ -40421,7 +40427,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>135350582</v>
+        <v>135350568</v>
       </c>
       <c r="B358" t="n">
         <v>78382</v>
@@ -40456,13 +40462,13 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>600208</v>
+        <v>600361</v>
       </c>
       <c r="R358" t="n">
-        <v>7331396</v>
+        <v>7331368</v>
       </c>
       <c r="S358" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T358" t="inlineStr">
         <is>
@@ -40491,7 +40497,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -40501,7 +40507,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD358" t="b">
@@ -40525,6 +40531,117 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>135350582</v>
+      </c>
+      <c r="B359" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr"/>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q359" t="n">
+        <v>600208</v>
+      </c>
+      <c r="R359" t="n">
+        <v>7331396</v>
+      </c>
+      <c r="S359" t="n">
+        <v>5</v>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD359" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE359" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG359" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT359" t="inlineStr"/>
+      <c r="AW359" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX359" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY359" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -22268,7 +22268,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>135383950</v>
+        <v>135383954</v>
       </c>
       <c r="B196" t="n">
         <v>101293</v>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -22348,7 +22348,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22357,6 +22357,7 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -26480,7 +26480,7 @@
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
@@ -28280,7 +28280,7 @@
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
@@ -29080,7 +29080,7 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
@@ -31871,7 +31871,7 @@
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
@@ -32209,7 +32209,7 @@
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
@@ -32432,7 +32432,7 @@
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -32766,7 +32766,7 @@
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
@@ -32877,7 +32877,7 @@
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
@@ -33543,7 +33543,7 @@
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
@@ -33764,7 +33764,7 @@
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
@@ -34541,7 +34541,7 @@
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
@@ -34652,7 +34652,7 @@
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
@@ -34763,7 +34763,7 @@
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
@@ -34879,7 +34879,7 @@
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
@@ -35767,7 +35767,7 @@
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
@@ -36655,7 +36655,7 @@
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -36766,7 +36766,7 @@
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
@@ -38118,7 +38118,7 @@
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
@@ -38557,12 +38557,12 @@
       <c r="AT341" t="inlineStr"/>
       <c r="AW341" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr">
@@ -39223,12 +39223,12 @@
       <c r="AT347" t="inlineStr"/>
       <c r="AW347" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr">
@@ -39886,7 +39886,7 @@
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr">
@@ -39997,7 +39997,7 @@
       </c>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr">
@@ -40219,7 +40219,7 @@
       </c>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
@@ -40668,7 +40668,7 @@
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
@@ -41006,7 +41006,7 @@
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
@@ -41450,7 +41450,7 @@
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
@@ -42116,7 +42116,7 @@
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
@@ -42449,7 +42449,7 @@
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
@@ -42782,12 +42782,12 @@
       <c r="AT379" t="inlineStr"/>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
@@ -43004,7 +43004,7 @@
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr">
@@ -43226,7 +43226,7 @@
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
@@ -43337,7 +43337,7 @@
       </c>
       <c r="AX384" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY384" t="inlineStr">
@@ -43448,7 +43448,7 @@
       </c>
       <c r="AX385" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY385" t="inlineStr">
@@ -43670,7 +43670,7 @@
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr">
@@ -43781,7 +43781,7 @@
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr">
@@ -43892,7 +43892,7 @@
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr">
@@ -44003,7 +44003,7 @@
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY390" t="inlineStr">
@@ -44447,7 +44447,7 @@
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr">
@@ -44558,7 +44558,7 @@
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr">
@@ -44780,7 +44780,7 @@
       </c>
       <c r="AX397" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY397" t="inlineStr">
@@ -45336,7 +45336,7 @@
       </c>
       <c r="AX402" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY402" t="inlineStr">
@@ -45447,7 +45447,7 @@
       </c>
       <c r="AX403" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY403" t="inlineStr">
@@ -45558,7 +45558,7 @@
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr">
@@ -45669,7 +45669,7 @@
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr">
@@ -45780,7 +45780,7 @@
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr">
@@ -46114,7 +46114,7 @@
       </c>
       <c r="AX409" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY409" t="inlineStr">
@@ -46225,7 +46225,7 @@
       </c>
       <c r="AX410" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY410" t="inlineStr">
@@ -46336,7 +46336,7 @@
       </c>
       <c r="AX411" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY411" t="inlineStr">
@@ -46447,7 +46447,7 @@
       </c>
       <c r="AX412" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY412" t="inlineStr">
@@ -46891,7 +46891,7 @@
       </c>
       <c r="AX416" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY416" t="inlineStr">
@@ -47002,7 +47002,7 @@
       </c>
       <c r="AX417" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY417" t="inlineStr">
@@ -47113,7 +47113,7 @@
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr">
@@ -47224,7 +47224,7 @@
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr">
@@ -47673,7 +47673,7 @@
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr">
@@ -47895,7 +47895,7 @@
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr">
@@ -48117,7 +48117,7 @@
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
@@ -48228,7 +48228,7 @@
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr">
@@ -48450,7 +48450,7 @@
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr">
@@ -48783,7 +48783,7 @@
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
@@ -48894,7 +48894,7 @@
       </c>
       <c r="AX434" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY434" t="inlineStr">
@@ -49005,7 +49005,7 @@
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
@@ -49116,7 +49116,7 @@
       </c>
       <c r="AX436" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY436" t="inlineStr">
@@ -50670,7 +50670,7 @@
       </c>
       <c r="AX450" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY450" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AX451" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY451" t="inlineStr">
@@ -51119,7 +51119,7 @@
       </c>
       <c r="AX454" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY454" t="inlineStr">
@@ -51346,7 +51346,7 @@
       </c>
       <c r="AX456" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY456" t="inlineStr">
@@ -51573,7 +51573,7 @@
       </c>
       <c r="AX458" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY458" t="inlineStr">
@@ -51689,7 +51689,7 @@
       </c>
       <c r="AX459" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY459" t="inlineStr">
@@ -51805,7 +51805,7 @@
       </c>
       <c r="AX460" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY460" t="inlineStr">
@@ -52162,7 +52162,7 @@
       </c>
       <c r="AX463" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY463" t="inlineStr">
@@ -52283,7 +52283,7 @@
       </c>
       <c r="AX464" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY464" t="inlineStr">
@@ -52524,7 +52524,7 @@
       </c>
       <c r="AX466" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY466" t="inlineStr">
@@ -53079,7 +53079,7 @@
       </c>
       <c r="AX471" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY471" t="inlineStr">
@@ -53296,12 +53296,12 @@
       <c r="AT473" t="inlineStr"/>
       <c r="AW473" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX473" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY473" t="inlineStr">
@@ -53745,7 +53745,7 @@
       </c>
       <c r="AX477" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY477" t="inlineStr">
@@ -53856,7 +53856,7 @@
       </c>
       <c r="AX478" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY478" t="inlineStr">
@@ -54751,7 +54751,7 @@
       </c>
       <c r="AX486" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY486" t="inlineStr">
@@ -54862,7 +54862,7 @@
       </c>
       <c r="AX487" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY487" t="inlineStr">
@@ -54973,7 +54973,7 @@
       </c>
       <c r="AX488" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY488" t="inlineStr">
@@ -55533,7 +55533,7 @@
       </c>
       <c r="AX493" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY493" t="inlineStr">
@@ -56088,7 +56088,7 @@
       </c>
       <c r="AX498" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY498" t="inlineStr">
@@ -56199,7 +56199,7 @@
       </c>
       <c r="AX499" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY499" t="inlineStr">
@@ -56310,7 +56310,7 @@
       </c>
       <c r="AX500" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY500" t="inlineStr">
@@ -56875,7 +56875,7 @@
       </c>
       <c r="AX505" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY505" t="inlineStr">
@@ -56986,7 +56986,7 @@
       </c>
       <c r="AX506" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY506" t="inlineStr">
@@ -57874,7 +57874,7 @@
       </c>
       <c r="AX514" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY514" t="inlineStr">
@@ -58878,7 +58878,7 @@
       </c>
       <c r="AX523" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY523" t="inlineStr">
@@ -58989,7 +58989,7 @@
       </c>
       <c r="AX524" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY524" t="inlineStr">
@@ -59544,7 +59544,7 @@
       </c>
       <c r="AX529" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY529" t="inlineStr">
@@ -59993,7 +59993,7 @@
       </c>
       <c r="AX533" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY533" t="inlineStr">
@@ -60104,7 +60104,7 @@
       </c>
       <c r="AX534" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY534" t="inlineStr">
@@ -60215,7 +60215,7 @@
       </c>
       <c r="AX535" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY535" t="inlineStr">
@@ -60442,7 +60442,7 @@
       </c>
       <c r="AX537" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY537" t="inlineStr">
@@ -61452,7 +61452,7 @@
       </c>
       <c r="AX546" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY546" t="inlineStr">
@@ -61563,7 +61563,7 @@
       </c>
       <c r="AX547" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY547" t="inlineStr">
@@ -61674,7 +61674,7 @@
       </c>
       <c r="AX548" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY548" t="inlineStr">
@@ -62899,7 +62899,7 @@
       </c>
       <c r="AX559" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY559" t="inlineStr">
@@ -63121,7 +63121,7 @@
       </c>
       <c r="AX561" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY561" t="inlineStr">
@@ -63232,7 +63232,7 @@
       </c>
       <c r="AX562" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY562" t="inlineStr">
@@ -63343,7 +63343,7 @@
       </c>
       <c r="AX563" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY563" t="inlineStr">
@@ -64231,7 +64231,7 @@
       </c>
       <c r="AX571" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY571" t="inlineStr">
@@ -64342,7 +64342,7 @@
       </c>
       <c r="AX572" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY572" t="inlineStr">
@@ -64458,7 +64458,7 @@
       </c>
       <c r="AX573" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY573" t="inlineStr">
@@ -64680,7 +64680,7 @@
       </c>
       <c r="AX575" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY575" t="inlineStr">
@@ -65018,7 +65018,7 @@
       </c>
       <c r="AX578" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY578" t="inlineStr">
@@ -65134,7 +65134,7 @@
       </c>
       <c r="AX579" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY579" t="inlineStr">
@@ -65490,7 +65490,7 @@
       </c>
       <c r="AX582" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY582" t="inlineStr">
@@ -65722,7 +65722,7 @@
       </c>
       <c r="AX584" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY584" t="inlineStr">
@@ -66050,12 +66050,12 @@
       <c r="AT587" t="inlineStr"/>
       <c r="AW587" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX587" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY587" t="inlineStr">
@@ -66605,12 +66605,12 @@
       <c r="AT592" t="inlineStr"/>
       <c r="AW592" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX592" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY592" t="inlineStr">
@@ -66938,12 +66938,12 @@
       <c r="AT595" t="inlineStr"/>
       <c r="AW595" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX595" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY595" t="inlineStr">
@@ -67165,7 +67165,7 @@
       </c>
       <c r="AX597" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY597" t="inlineStr">
@@ -67271,12 +67271,12 @@
       <c r="AT598" t="inlineStr"/>
       <c r="AW598" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX598" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY598" t="inlineStr">
@@ -67498,7 +67498,7 @@
       </c>
       <c r="AX600" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY600" t="inlineStr">
@@ -68049,12 +68049,12 @@
       <c r="AT605" t="inlineStr"/>
       <c r="AW605" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX605" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY605" t="inlineStr">
@@ -68160,12 +68160,12 @@
       <c r="AT606" t="inlineStr"/>
       <c r="AW606" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX606" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY606" t="inlineStr">
@@ -68271,12 +68271,12 @@
       <c r="AT607" t="inlineStr"/>
       <c r="AW607" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX607" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY607" t="inlineStr">
@@ -68382,12 +68382,12 @@
       <c r="AT608" t="inlineStr"/>
       <c r="AW608" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX608" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY608" t="inlineStr">
@@ -68937,12 +68937,12 @@
       <c r="AT613" t="inlineStr"/>
       <c r="AW613" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX613" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY613" t="inlineStr">
@@ -69048,12 +69048,12 @@
       <c r="AT614" t="inlineStr"/>
       <c r="AW614" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX614" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY614" t="inlineStr">
@@ -69159,12 +69159,12 @@
       <c r="AT615" t="inlineStr"/>
       <c r="AW615" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX615" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY615" t="inlineStr">
@@ -69270,12 +69270,12 @@
       <c r="AT616" t="inlineStr"/>
       <c r="AW616" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX616" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY616" t="inlineStr">
@@ -69381,12 +69381,12 @@
       <c r="AT617" t="inlineStr"/>
       <c r="AW617" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX617" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY617" t="inlineStr">
@@ -69603,12 +69603,12 @@
       <c r="AT619" t="inlineStr"/>
       <c r="AW619" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX619" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY619" t="inlineStr">
@@ -69825,12 +69825,12 @@
       <c r="AT621" t="inlineStr"/>
       <c r="AW621" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX621" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY621" t="inlineStr">
@@ -69936,12 +69936,12 @@
       <c r="AT622" t="inlineStr"/>
       <c r="AW622" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AX622" t="inlineStr">
         <is>
-          <t>Agne  Jonsson</t>
+          <t>Agne Jonsson</t>
         </is>
       </c>
       <c r="AY622" t="inlineStr">
@@ -70381,7 +70381,7 @@
       </c>
       <c r="AX626" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY626" t="inlineStr">
@@ -70492,7 +70492,7 @@
       </c>
       <c r="AX627" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY627" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -33446,7 +33446,7 @@
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
@@ -36338,7 +36338,7 @@
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
@@ -37564,7 +37564,7 @@
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
@@ -41683,7 +41683,7 @@
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
@@ -42016,7 +42016,7 @@
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
@@ -42465,7 +42465,7 @@
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
@@ -42803,7 +42803,7 @@
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
@@ -44246,7 +44246,7 @@
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr">
@@ -56548,7 +56548,7 @@
       </c>
       <c r="AX502" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY502" t="inlineStr">
@@ -57996,7 +57996,7 @@
       </c>
       <c r="AX515" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY515" t="inlineStr">
@@ -62239,7 +62239,7 @@
       </c>
       <c r="AX553" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY553" t="inlineStr">
@@ -65029,7 +65029,7 @@
       </c>
       <c r="AX578" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY578" t="inlineStr">
@@ -67519,7 +67519,7 @@
       </c>
       <c r="AX600" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY600" t="inlineStr">
@@ -72289,7 +72289,7 @@
       </c>
       <c r="AX643" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY643" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135384331</v>
+        <v>135382760</v>
       </c>
       <c r="B2" t="n">
         <v>91924</v>
@@ -704,19 +704,22 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598540</v>
+        <v>598539</v>
       </c>
       <c r="R2" t="n">
-        <v>7331137</v>
+        <v>7331139</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,18 +767,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,48 +790,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135382413</v>
+        <v>135384331</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>91924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>306</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598444</v>
+        <v>598540</v>
       </c>
       <c r="R3" t="n">
-        <v>7331025</v>
+        <v>7331137</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,48 +901,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135384288</v>
+        <v>135382413</v>
       </c>
       <c r="B4" t="n">
-        <v>89354</v>
+        <v>83343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598430</v>
+        <v>598444</v>
       </c>
       <c r="R4" t="n">
-        <v>7331083</v>
+        <v>7331025</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Nr7</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,12 +996,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1013,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135379254</v>
+        <v>135384288</v>
       </c>
       <c r="B5" t="n">
-        <v>92245</v>
+        <v>89354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +1023,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598419</v>
+        <v>598430</v>
       </c>
       <c r="R5" t="n">
-        <v>7331061</v>
+        <v>7331083</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1083,7 +1082,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1093,7 +1092,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Nr7</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,12 +1112,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1124,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135379255</v>
+        <v>135379254</v>
       </c>
       <c r="B6" t="n">
         <v>92245</v>
@@ -1159,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598417</v>
+        <v>598419</v>
       </c>
       <c r="R6" t="n">
-        <v>7331147</v>
+        <v>7331061</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1194,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1239,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135382735</v>
+        <v>135379255</v>
       </c>
       <c r="B7" t="n">
         <v>92245</v>
@@ -1266,17 +1270,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598429</v>
+        <v>598417</v>
       </c>
       <c r="R7" t="n">
-        <v>7330875</v>
+        <v>7331147</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,12 +1334,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1346,7 +1350,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135382750</v>
+        <v>135382735</v>
       </c>
       <c r="B8" t="n">
         <v>92245</v>
@@ -1381,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598403</v>
+        <v>598429</v>
       </c>
       <c r="R8" t="n">
-        <v>7330993</v>
+        <v>7330875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,7 +1461,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135382772</v>
+        <v>135382750</v>
       </c>
       <c r="B9" t="n">
         <v>92245</v>
@@ -1492,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598422</v>
+        <v>598403</v>
       </c>
       <c r="R9" t="n">
-        <v>7331095</v>
+        <v>7330993</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1541,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,7 +1572,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135383974</v>
+        <v>135382772</v>
       </c>
       <c r="B10" t="n">
         <v>92245</v>
@@ -1599,14 +1603,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598448</v>
+        <v>598422</v>
       </c>
       <c r="R10" t="n">
-        <v>7331109</v>
+        <v>7331095</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1642,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,12 +1667,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1679,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135384144</v>
+        <v>135383974</v>
       </c>
       <c r="B11" t="n">
         <v>92245</v>
@@ -1710,14 +1714,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598419</v>
+        <v>598448</v>
       </c>
       <c r="R11" t="n">
-        <v>7331086</v>
+        <v>7331109</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,12 +1778,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1790,7 +1794,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135384270</v>
+        <v>135384144</v>
       </c>
       <c r="B12" t="n">
         <v>92245</v>
@@ -1821,14 +1825,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598392</v>
+        <v>598419</v>
       </c>
       <c r="R12" t="n">
-        <v>7330995</v>
+        <v>7331086</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,12 +1889,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1901,7 +1905,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135384286</v>
+        <v>135384270</v>
       </c>
       <c r="B13" t="n">
         <v>92245</v>
@@ -1936,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598436</v>
+        <v>598392</v>
       </c>
       <c r="R13" t="n">
-        <v>7331076</v>
+        <v>7330995</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,7 +1975,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1981,7 +1985,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,7 +2016,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135385128</v>
+        <v>135384286</v>
       </c>
       <c r="B14" t="n">
         <v>92245</v>
@@ -2043,17 +2047,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598458</v>
+        <v>598436</v>
       </c>
       <c r="R14" t="n">
-        <v>7331086</v>
+        <v>7331076</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,7 +2086,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2092,7 +2096,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,12 +2111,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2123,10 +2127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135357040</v>
+        <v>135385128</v>
       </c>
       <c r="B15" t="n">
-        <v>79452</v>
+        <v>92245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,34 +2138,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598489</v>
+        <v>598458</v>
       </c>
       <c r="R15" t="n">
-        <v>7331104</v>
+        <v>7331086</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2188,22 +2192,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,12 +2222,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2234,7 +2238,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135382042</v>
+        <v>135357040</v>
       </c>
       <c r="B16" t="n">
         <v>79452</v>
@@ -2265,17 +2269,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598455</v>
+        <v>598489</v>
       </c>
       <c r="R16" t="n">
-        <v>7331156</v>
+        <v>7331104</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2299,22 +2303,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,19 +2327,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2346,7 +2349,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135383991</v>
+        <v>135382042</v>
       </c>
       <c r="B17" t="n">
         <v>79452</v>
@@ -2377,17 +2380,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598390</v>
+        <v>598455</v>
       </c>
       <c r="R17" t="n">
-        <v>7330796</v>
+        <v>7331156</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2416,7 +2419,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2426,7 +2429,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,18 +2438,19 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2457,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135379238</v>
+        <v>135383991</v>
       </c>
       <c r="B18" t="n">
-        <v>91970</v>
+        <v>79452</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,37 +2472,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598450</v>
+        <v>598390</v>
       </c>
       <c r="R18" t="n">
-        <v>7330930</v>
+        <v>7330796</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2527,7 +2531,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,7 +2541,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2552,12 +2556,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2568,7 +2572,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135379243</v>
+        <v>135379238</v>
       </c>
       <c r="B19" t="n">
         <v>91970</v>
@@ -2606,10 +2610,10 @@
         <v>598450</v>
       </c>
       <c r="R19" t="n">
-        <v>7331038</v>
+        <v>7330930</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2638,7 +2642,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2648,7 +2652,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135379248</v>
+        <v>135379243</v>
       </c>
       <c r="B20" t="n">
         <v>91970</v>
@@ -2714,13 +2718,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598423</v>
+        <v>598450</v>
       </c>
       <c r="R20" t="n">
-        <v>7331046</v>
+        <v>7331038</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2749,7 +2753,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2759,7 +2763,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,7 +2794,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135379249</v>
+        <v>135379248</v>
       </c>
       <c r="B21" t="n">
         <v>91970</v>
@@ -2825,13 +2829,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598410</v>
+        <v>598423</v>
       </c>
       <c r="R21" t="n">
-        <v>7331047</v>
+        <v>7331046</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2860,7 +2864,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2870,7 +2874,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2901,7 +2905,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135379252</v>
+        <v>135379249</v>
       </c>
       <c r="B22" t="n">
         <v>91970</v>
@@ -2936,13 +2940,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598424</v>
+        <v>598410</v>
       </c>
       <c r="R22" t="n">
-        <v>7331046</v>
+        <v>7331047</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2971,7 +2975,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2981,7 +2985,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3012,7 +3016,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135382411</v>
+        <v>135379252</v>
       </c>
       <c r="B23" t="n">
         <v>91970</v>
@@ -3047,13 +3051,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>598411</v>
+        <v>598424</v>
       </c>
       <c r="R23" t="n">
-        <v>7331051</v>
+        <v>7331046</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3082,7 +3086,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3092,7 +3096,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3107,12 +3111,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3123,7 +3127,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135382725</v>
+        <v>135382411</v>
       </c>
       <c r="B24" t="n">
         <v>91970</v>
@@ -3154,17 +3158,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>598409</v>
+        <v>598411</v>
       </c>
       <c r="R24" t="n">
-        <v>7330832</v>
+        <v>7331051</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3193,7 +3197,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3203,7 +3207,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,12 +3222,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3234,7 +3238,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135382733</v>
+        <v>135382725</v>
       </c>
       <c r="B25" t="n">
         <v>91970</v>
@@ -3269,10 +3273,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>598471</v>
+        <v>598409</v>
       </c>
       <c r="R25" t="n">
-        <v>7330884</v>
+        <v>7330832</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3304,7 +3308,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3314,7 +3318,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3345,7 +3349,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135383965</v>
+        <v>135382733</v>
       </c>
       <c r="B26" t="n">
         <v>91970</v>
@@ -3376,14 +3380,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>598424</v>
+        <v>598471</v>
       </c>
       <c r="R26" t="n">
-        <v>7331042</v>
+        <v>7330884</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3415,7 +3419,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3425,7 +3429,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3440,12 +3444,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3456,7 +3460,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135384150</v>
+        <v>135383965</v>
       </c>
       <c r="B27" t="n">
         <v>91970</v>
@@ -3487,14 +3491,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>598523</v>
+        <v>598424</v>
       </c>
       <c r="R27" t="n">
-        <v>7331149</v>
+        <v>7331042</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,7 +3530,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3536,7 +3540,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3551,12 +3555,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3567,7 +3571,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135385952</v>
+        <v>135384150</v>
       </c>
       <c r="B28" t="n">
         <v>91970</v>
@@ -3598,14 +3602,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>598463</v>
+        <v>598523</v>
       </c>
       <c r="R28" t="n">
-        <v>7330966</v>
+        <v>7331149</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3662,12 +3666,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3678,7 +3682,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135385965</v>
+        <v>135385952</v>
       </c>
       <c r="B29" t="n">
         <v>91970</v>
@@ -3713,10 +3717,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>598445</v>
+        <v>598463</v>
       </c>
       <c r="R29" t="n">
-        <v>7331066</v>
+        <v>7330966</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3752,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3758,7 +3762,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3789,7 +3793,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135385966</v>
+        <v>135385965</v>
       </c>
       <c r="B30" t="n">
         <v>91970</v>
@@ -3824,10 +3828,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>598510</v>
+        <v>598445</v>
       </c>
       <c r="R30" t="n">
-        <v>7331106</v>
+        <v>7331066</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3859,7 +3863,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3869,7 +3873,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3900,7 +3904,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135385973</v>
+        <v>135385966</v>
       </c>
       <c r="B31" t="n">
         <v>91970</v>
@@ -3935,10 +3939,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>598583</v>
+        <v>598510</v>
       </c>
       <c r="R31" t="n">
-        <v>7331166</v>
+        <v>7331106</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3970,7 +3974,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3980,7 +3984,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4011,10 +4015,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135379246</v>
+        <v>135385973</v>
       </c>
       <c r="B32" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4022,37 +4026,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>598450</v>
+        <v>598583</v>
       </c>
       <c r="R32" t="n">
-        <v>7331038</v>
+        <v>7331166</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4081,7 +4085,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4091,7 +4095,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4106,12 +4110,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4122,7 +4126,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135382064</v>
+        <v>135379246</v>
       </c>
       <c r="B33" t="n">
         <v>91974</v>
@@ -4153,17 +4157,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>598519</v>
+        <v>598450</v>
       </c>
       <c r="R33" t="n">
-        <v>7331136</v>
+        <v>7331038</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4192,7 +4196,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4202,7 +4206,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4217,12 +4221,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maja Rancic</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4233,7 +4237,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135382736</v>
+        <v>135382064</v>
       </c>
       <c r="B34" t="n">
         <v>91974</v>
@@ -4264,17 +4268,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>598429</v>
+        <v>598519</v>
       </c>
       <c r="R34" t="n">
-        <v>7330875</v>
+        <v>7331136</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4303,7 +4307,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4313,7 +4317,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4328,12 +4332,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4344,7 +4348,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135383967</v>
+        <v>135382736</v>
       </c>
       <c r="B35" t="n">
         <v>91974</v>
@@ -4375,14 +4379,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>598514</v>
+        <v>598429</v>
       </c>
       <c r="R35" t="n">
-        <v>7331131</v>
+        <v>7330875</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4414,7 +4418,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4424,7 +4428,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4439,12 +4443,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4455,7 +4459,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135384131</v>
+        <v>135383967</v>
       </c>
       <c r="B36" t="n">
         <v>91974</v>
@@ -4486,14 +4490,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>598446</v>
+        <v>598514</v>
       </c>
       <c r="R36" t="n">
-        <v>7330836</v>
+        <v>7331131</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4525,7 +4529,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4535,7 +4539,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4550,12 +4554,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4566,7 +4570,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135384136</v>
+        <v>135384131</v>
       </c>
       <c r="B37" t="n">
         <v>91974</v>
@@ -4601,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>598401</v>
+        <v>598446</v>
       </c>
       <c r="R37" t="n">
-        <v>7330867</v>
+        <v>7330836</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4636,7 +4640,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4646,7 +4650,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4677,7 +4681,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135384146</v>
+        <v>135384136</v>
       </c>
       <c r="B38" t="n">
         <v>91974</v>
@@ -4712,10 +4716,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>598419</v>
+        <v>598401</v>
       </c>
       <c r="R38" t="n">
-        <v>7331081</v>
+        <v>7330867</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4747,7 +4751,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4757,7 +4761,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4788,7 +4792,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135384153</v>
+        <v>135384146</v>
       </c>
       <c r="B39" t="n">
         <v>91974</v>
@@ -4823,10 +4827,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>598535</v>
+        <v>598419</v>
       </c>
       <c r="R39" t="n">
-        <v>7331145</v>
+        <v>7331081</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4858,7 +4862,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4868,7 +4872,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4899,7 +4903,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135384272</v>
+        <v>135384153</v>
       </c>
       <c r="B40" t="n">
         <v>91974</v>
@@ -4930,14 +4934,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>598392</v>
+        <v>598535</v>
       </c>
       <c r="R40" t="n">
-        <v>7330995</v>
+        <v>7331145</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4969,7 +4973,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4979,7 +4983,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4994,12 +4998,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5010,7 +5014,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135385129</v>
+        <v>135384272</v>
       </c>
       <c r="B41" t="n">
         <v>91974</v>
@@ -5041,17 +5045,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>598508</v>
+        <v>598392</v>
       </c>
       <c r="R41" t="n">
-        <v>7331136</v>
+        <v>7330995</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5080,7 +5084,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5090,7 +5094,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5105,12 +5109,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5121,48 +5125,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135386007</v>
+        <v>135385129</v>
       </c>
       <c r="B42" t="n">
-        <v>91988</v>
+        <v>91974</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>598635</v>
+        <v>598508</v>
       </c>
       <c r="R42" t="n">
-        <v>7330799</v>
+        <v>7331136</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5191,7 +5195,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5201,7 +5205,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5216,12 +5220,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5232,48 +5236,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135379250</v>
+        <v>135386007</v>
       </c>
       <c r="B43" t="n">
-        <v>92406</v>
+        <v>91988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>598412</v>
+        <v>598635</v>
       </c>
       <c r="R43" t="n">
-        <v>7331049</v>
+        <v>7330799</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5302,7 +5306,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5312,7 +5316,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5327,12 +5331,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5343,7 +5347,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135382403</v>
+        <v>135379250</v>
       </c>
       <c r="B44" t="n">
         <v>92406</v>
@@ -5378,13 +5382,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>598423</v>
+        <v>598412</v>
       </c>
       <c r="R44" t="n">
-        <v>7330967</v>
+        <v>7331049</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5423,7 +5427,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5438,12 +5442,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5454,7 +5458,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135383973</v>
+        <v>135382403</v>
       </c>
       <c r="B45" t="n">
         <v>92406</v>
@@ -5485,17 +5489,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>598446</v>
+        <v>598423</v>
       </c>
       <c r="R45" t="n">
-        <v>7331122</v>
+        <v>7330967</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5524,7 +5528,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5534,7 +5538,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5549,12 +5553,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5565,7 +5569,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135385127</v>
+        <v>135383973</v>
       </c>
       <c r="B46" t="n">
         <v>92406</v>
@@ -5596,17 +5600,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>598457</v>
+        <v>598446</v>
       </c>
       <c r="R46" t="n">
-        <v>7331085</v>
+        <v>7331122</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5635,7 +5639,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5645,7 +5649,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5660,12 +5664,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5676,10 +5680,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135383992</v>
+        <v>135385127</v>
       </c>
       <c r="B47" t="n">
-        <v>83222</v>
+        <v>92406</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5687,37 +5691,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>598387</v>
+        <v>598457</v>
       </c>
       <c r="R47" t="n">
-        <v>7330791</v>
+        <v>7331085</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5746,7 +5750,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5756,7 +5760,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5765,19 +5769,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5788,10 +5791,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135382399</v>
+        <v>135383992</v>
       </c>
       <c r="B48" t="n">
-        <v>83363</v>
+        <v>83222</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5799,37 +5802,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>598470</v>
+        <v>598387</v>
       </c>
       <c r="R48" t="n">
-        <v>7330873</v>
+        <v>7330791</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5858,7 +5861,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5868,7 +5871,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5877,18 +5880,19 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5899,7 +5903,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135382407</v>
+        <v>135382399</v>
       </c>
       <c r="B49" t="n">
         <v>83363</v>
@@ -5934,10 +5938,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>598370</v>
+        <v>598470</v>
       </c>
       <c r="R49" t="n">
-        <v>7330983</v>
+        <v>7330873</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5969,7 +5973,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5979,7 +5983,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6010,32 +6014,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135379247</v>
+        <v>135382407</v>
       </c>
       <c r="B50" t="n">
-        <v>92332</v>
+        <v>83363</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1505</v>
+        <v>1467</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6045,13 +6049,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>598445</v>
+        <v>598370</v>
       </c>
       <c r="R50" t="n">
-        <v>7331042</v>
+        <v>7330983</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6080,7 +6084,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6090,7 +6094,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6099,19 +6103,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6122,10 +6125,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135357049</v>
+        <v>135379247</v>
       </c>
       <c r="B51" t="n">
-        <v>92329</v>
+        <v>92332</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6133,37 +6136,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>598581</v>
+        <v>598445</v>
       </c>
       <c r="R51" t="n">
-        <v>7330973</v>
+        <v>7331042</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6187,22 +6190,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6211,18 +6214,19 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6233,7 +6237,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135357050</v>
+        <v>135357049</v>
       </c>
       <c r="B52" t="n">
         <v>92329</v>
@@ -6271,10 +6275,10 @@
         <v>598581</v>
       </c>
       <c r="R52" t="n">
-        <v>7330972</v>
+        <v>7330973</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6303,7 +6307,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6313,7 +6317,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6344,7 +6348,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135384148</v>
+        <v>135357050</v>
       </c>
       <c r="B53" t="n">
         <v>92329</v>
@@ -6375,17 +6379,17 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>598523</v>
+        <v>598581</v>
       </c>
       <c r="R53" t="n">
-        <v>7331149</v>
+        <v>7330972</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6409,22 +6413,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6439,12 +6443,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6455,7 +6459,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135385971</v>
+        <v>135384148</v>
       </c>
       <c r="B54" t="n">
         <v>92329</v>
@@ -6486,14 +6490,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>598568</v>
+        <v>598523</v>
       </c>
       <c r="R54" t="n">
-        <v>7331169</v>
+        <v>7331149</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6525,7 +6529,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6535,7 +6539,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6550,12 +6554,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6566,10 +6570,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135387640</v>
+        <v>135385971</v>
       </c>
       <c r="B55" t="n">
-        <v>92318</v>
+        <v>92329</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6577,21 +6581,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2062</v>
+        <v>1506</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6601,13 +6605,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>598398</v>
+        <v>598568</v>
       </c>
       <c r="R55" t="n">
-        <v>7331002</v>
+        <v>7331169</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6636,7 +6640,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6646,7 +6650,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6661,12 +6665,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6677,10 +6681,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135382727</v>
+        <v>135387640</v>
       </c>
       <c r="B56" t="n">
-        <v>92320</v>
+        <v>92318</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6688,16 +6692,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6708,17 +6712,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>598440</v>
+        <v>598398</v>
       </c>
       <c r="R56" t="n">
-        <v>7330835</v>
+        <v>7331002</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6747,7 +6751,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6757,7 +6761,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6772,12 +6776,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6788,7 +6792,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135382741</v>
+        <v>135382727</v>
       </c>
       <c r="B57" t="n">
         <v>92320</v>
@@ -6823,10 +6827,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>598413</v>
+        <v>598440</v>
       </c>
       <c r="R57" t="n">
-        <v>7330907</v>
+        <v>7330835</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6858,7 +6862,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6868,7 +6872,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6899,7 +6903,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135382757</v>
+        <v>135382741</v>
       </c>
       <c r="B58" t="n">
         <v>92320</v>
@@ -6934,10 +6938,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>598418</v>
+        <v>598413</v>
       </c>
       <c r="R58" t="n">
-        <v>7331075</v>
+        <v>7330907</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6969,7 +6973,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6979,7 +6983,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7010,7 +7014,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135385962</v>
+        <v>135382757</v>
       </c>
       <c r="B59" t="n">
         <v>92320</v>
@@ -7041,14 +7045,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>598513</v>
+        <v>598418</v>
       </c>
       <c r="R59" t="n">
-        <v>7330984</v>
+        <v>7331075</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7080,7 +7084,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7090,7 +7094,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7105,12 +7109,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7121,10 +7125,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135382999</v>
+        <v>135385962</v>
       </c>
       <c r="B60" t="n">
-        <v>92326</v>
+        <v>92320</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7132,37 +7136,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kilporing</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Skeletocutis kuehneri</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>A.David</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>598481</v>
+        <v>598513</v>
       </c>
       <c r="R60" t="n">
-        <v>7331157</v>
+        <v>7330984</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7192,14 +7193,19 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På döda violtickor/under bark med döda violtickor. Ser ut som och luktar tydligt skeletocutie</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7208,19 +7214,18 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7231,45 +7236,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135382745</v>
+        <v>135382999</v>
       </c>
       <c r="B61" t="n">
-        <v>80489</v>
+        <v>92326</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>2064</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>598376</v>
+        <v>598481</v>
       </c>
       <c r="R61" t="n">
-        <v>7330983</v>
+        <v>7331157</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7299,19 +7307,14 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:51</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På döda violtickor/under bark med döda violtickor. Ser ut som och luktar tydligt skeletocutie</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7320,6 +7323,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7342,48 +7346,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135380608</v>
+        <v>135382745</v>
       </c>
       <c r="B62" t="n">
-        <v>96410</v>
+        <v>80489</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2812</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>598484</v>
+        <v>598376</v>
       </c>
       <c r="R62" t="n">
-        <v>7331166</v>
+        <v>7330983</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7407,22 +7411,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7437,12 +7441,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7453,7 +7457,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135382742</v>
+        <v>135380608</v>
       </c>
       <c r="B63" t="n">
         <v>96410</v>
@@ -7484,17 +7488,17 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>598360</v>
+        <v>598484</v>
       </c>
       <c r="R63" t="n">
-        <v>7330971</v>
+        <v>7331166</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7518,22 +7522,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7548,12 +7552,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7564,7 +7568,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135382748</v>
+        <v>135382742</v>
       </c>
       <c r="B64" t="n">
         <v>96410</v>
@@ -7599,10 +7603,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>598376</v>
+        <v>598360</v>
       </c>
       <c r="R64" t="n">
-        <v>7330983</v>
+        <v>7330971</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7634,7 +7638,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7644,7 +7648,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7675,7 +7679,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135382753</v>
+        <v>135382748</v>
       </c>
       <c r="B65" t="n">
         <v>96410</v>
@@ -7710,10 +7714,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>598403</v>
+        <v>598376</v>
       </c>
       <c r="R65" t="n">
-        <v>7331036</v>
+        <v>7330983</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7745,7 +7749,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7755,7 +7759,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7786,7 +7790,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135382767</v>
+        <v>135382753</v>
       </c>
       <c r="B66" t="n">
         <v>96410</v>
@@ -7821,10 +7825,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>598435</v>
+        <v>598403</v>
       </c>
       <c r="R66" t="n">
-        <v>7331156</v>
+        <v>7331036</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7856,7 +7860,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7866,7 +7870,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7897,7 +7901,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135382773</v>
+        <v>135382767</v>
       </c>
       <c r="B67" t="n">
         <v>96410</v>
@@ -7932,10 +7936,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>598422</v>
+        <v>598435</v>
       </c>
       <c r="R67" t="n">
-        <v>7331095</v>
+        <v>7331156</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7967,7 +7971,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7977,7 +7981,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8008,7 +8012,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135382778</v>
+        <v>135382773</v>
       </c>
       <c r="B68" t="n">
         <v>96410</v>
@@ -8043,10 +8047,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>598335</v>
+        <v>598422</v>
       </c>
       <c r="R68" t="n">
-        <v>7330956</v>
+        <v>7331095</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8078,7 +8082,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8088,7 +8092,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8119,7 +8123,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135383981</v>
+        <v>135382778</v>
       </c>
       <c r="B69" t="n">
         <v>96410</v>
@@ -8150,14 +8154,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>598337</v>
+        <v>598335</v>
       </c>
       <c r="R69" t="n">
-        <v>7330968</v>
+        <v>7330956</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8189,7 +8193,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8199,7 +8203,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8214,12 +8218,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8230,10 +8234,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135383962</v>
+        <v>135383981</v>
       </c>
       <c r="B70" t="n">
-        <v>92370</v>
+        <v>96410</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8241,21 +8245,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4217</v>
+        <v>2812</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8265,10 +8269,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>598525</v>
+        <v>598337</v>
       </c>
       <c r="R70" t="n">
-        <v>7331166</v>
+        <v>7330968</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8300,7 +8304,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8310,7 +8314,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8341,45 +8345,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135382760</v>
+        <v>135383962</v>
       </c>
       <c r="B71" t="n">
-        <v>93324</v>
+        <v>92370</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6164</v>
+        <v>4217</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Filttagging</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odontia ferruginea</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>598539</v>
+        <v>598525</v>
       </c>
       <c r="R71" t="n">
-        <v>7331139</v>
+        <v>7331166</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8411,7 +8415,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8421,33 +8425,27 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Förmodligen stjärntagging, men ska mikras, Fanns bara korta "taggar" överallt</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På döda violtickor/under bark med döda violtickor. Ser ut som och luktar tydligt skeletocutie</t>
+          <t>På döda violtickor/under bark med döda violtickor. Ser ut som och luktar tydligt skeletocutis</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -33444,7 +33444,7 @@
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
@@ -36336,7 +36336,7 @@
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
@@ -37562,7 +37562,7 @@
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
@@ -41681,7 +41681,7 @@
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
@@ -42463,7 +42463,7 @@
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
@@ -42801,7 +42801,7 @@
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
@@ -44244,7 +44244,7 @@
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr">
@@ -56546,7 +56546,7 @@
       </c>
       <c r="AX502" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY502" t="inlineStr">
@@ -57994,7 +57994,7 @@
       </c>
       <c r="AX515" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY515" t="inlineStr">
@@ -62237,7 +62237,7 @@
       </c>
       <c r="AX553" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY553" t="inlineStr">
@@ -65027,7 +65027,7 @@
       </c>
       <c r="AX578" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY578" t="inlineStr">
@@ -67517,7 +67517,7 @@
       </c>
       <c r="AX600" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY600" t="inlineStr">
@@ -72287,7 +72287,7 @@
       </c>
       <c r="AX643" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY643" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -12588,7 +12588,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Elin Kannerby, Petra Wikström, Helen Sterner, Christina Boyd, per-erik mukka, Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Elin Kannerby, Christina Boyd, Helen Sterner, Petra Wikström, per-erik mukka, Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -24487,7 +24487,7 @@
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Elin Kannerby, Petra Wikström, Helen Sterner, Christina Boyd, per-erik mukka, Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
@@ -34450,7 +34450,7 @@
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
@@ -35448,7 +35448,7 @@
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
@@ -39005,7 +39005,7 @@
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
+          <t>Elin Kannerby, Anton Lundberg, Petra Wikström, Helen Sterner, Christina Boyd, per-erik mukka, Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr">
@@ -54319,7 +54319,7 @@
       </c>
       <c r="AX482" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY482" t="inlineStr">
@@ -58670,7 +58670,7 @@
       </c>
       <c r="AX521" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY521" t="inlineStr">
@@ -63247,7 +63247,7 @@
       </c>
       <c r="AX562" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY562" t="inlineStr">
@@ -63358,7 +63358,7 @@
       </c>
       <c r="AX563" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY563" t="inlineStr">
@@ -65138,7 +65138,7 @@
       </c>
       <c r="AX579" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY579" t="inlineStr">
@@ -68960,7 +68960,7 @@
       </c>
       <c r="AX613" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY613" t="inlineStr">
@@ -72176,7 +72176,7 @@
       </c>
       <c r="AX642" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY642" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -12588,7 +12588,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Petra Wikström, Helen Sterner, Christina Boyd, per-erik mukka, Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Helen Sterner, Petra Wikström, per-erik mukka, Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -24487,7 +24487,7 @@
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Petra Wikström, Helen Sterner, Christina Boyd, per-erik mukka, Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
@@ -34450,7 +34450,7 @@
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
@@ -35448,7 +35448,7 @@
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
@@ -39005,7 +39005,7 @@
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Anton Lundberg, Petra Wikström, Helen Sterner, Christina Boyd, per-erik mukka, Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby, Anton Lundberg, Alva Dahlqvist Cederstrand, per-erik mukka, Christina Boyd, Helen Sterner, Petra Wikström</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr">
@@ -54319,7 +54319,7 @@
       </c>
       <c r="AX482" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY482" t="inlineStr">
@@ -58670,7 +58670,7 @@
       </c>
       <c r="AX521" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY521" t="inlineStr">
@@ -63247,7 +63247,7 @@
       </c>
       <c r="AX562" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY562" t="inlineStr">
@@ -63358,7 +63358,7 @@
       </c>
       <c r="AX563" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY563" t="inlineStr">
@@ -65138,7 +65138,7 @@
       </c>
       <c r="AX579" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY579" t="inlineStr">
@@ -68960,7 +68960,7 @@
       </c>
       <c r="AX613" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY613" t="inlineStr">
@@ -72176,7 +72176,7 @@
       </c>
       <c r="AX642" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY642" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY643"/>
+  <dimension ref="A1:AZ643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382760</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384331</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382413</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384288</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379254</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379255</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1458,6 +1493,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382735</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1569,6 +1609,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382750</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382772</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1791,6 +1841,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383974</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1902,6 +1957,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384144</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2013,6 +2073,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384270</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2124,6 +2189,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384286</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2235,6 +2305,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385128</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2346,6 +2421,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357040</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2458,6 +2538,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382042</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2569,6 +2654,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383991</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2680,6 +2770,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379238</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2791,6 +2886,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379243</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2902,6 +3002,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379248</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3013,6 +3118,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379249</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3124,6 +3234,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379252</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3235,6 +3350,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382411</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3346,6 +3466,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382725</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3457,6 +3582,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382733</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3568,6 +3698,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383965</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3679,6 +3814,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384150</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3790,6 +3930,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385952</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3901,6 +4046,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385965</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4012,6 +4162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385966</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4123,6 +4278,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385973</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4234,6 +4394,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379246</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4345,6 +4510,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382064</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4456,6 +4626,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382736</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4567,6 +4742,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383967</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4678,6 +4858,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384131</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4789,6 +4974,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384136</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4900,6 +5090,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384146</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5011,6 +5206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384153</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5122,6 +5322,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384272</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5233,6 +5438,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385129</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5344,6 +5554,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135386007</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5455,6 +5670,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379250</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5566,6 +5786,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382403</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5677,6 +5902,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383973</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5788,6 +6018,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385127</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5900,6 +6135,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383992</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6011,6 +6251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382399</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6122,6 +6367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382407</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6234,6 +6484,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379247</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6345,6 +6600,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357049</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6456,6 +6716,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357050</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6567,6 +6832,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384148</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6678,6 +6948,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385971</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6789,6 +7064,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135387640</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6900,6 +7180,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382727</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7011,6 +7296,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382741</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7122,6 +7412,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382757</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7231,6 +7526,11 @@
       <c r="AY60" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385962</t>
         </is>
       </c>
     </row>
@@ -7343,6 +7643,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382999</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7454,6 +7759,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382745</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7565,6 +7875,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380608</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7676,6 +7991,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382742</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7787,6 +8107,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382748</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7898,6 +8223,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382753</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8009,6 +8339,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382767</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8120,6 +8455,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382773</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8231,6 +8571,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382778</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8342,6 +8687,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383981</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8453,6 +8803,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383962</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8564,6 +8919,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357046</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8675,6 +9035,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382034</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8791,6 +9156,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382036</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8902,6 +9272,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382400</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9013,6 +9388,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382417</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9124,6 +9504,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382419</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9235,6 +9620,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382466</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9346,6 +9736,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382731</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9457,6 +9852,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384252</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9568,6 +9968,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384261</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9679,6 +10084,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384285</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9790,6 +10200,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385123</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9901,6 +10316,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385124</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10012,6 +10432,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382396</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10123,6 +10548,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385120</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10234,6 +10664,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382391</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10345,6 +10780,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385941</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10456,6 +10896,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382746</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10567,6 +11012,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382749</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10678,6 +11128,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382463</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10789,6 +11244,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382752</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10900,6 +11360,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382774</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11011,6 +11476,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382751</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11122,6 +11592,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382775</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11233,6 +11708,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382039</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11344,6 +11824,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382040</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11455,6 +11940,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382747</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11566,6 +12056,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384138</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11690,6 +12185,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384126</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11814,6 +12314,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384141</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11930,6 +12435,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385126</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12041,6 +12551,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383964</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12152,6 +12667,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357038</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12263,6 +12783,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383994</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12374,6 +12899,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384128</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12485,6 +13015,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385940</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12596,6 +13131,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385968</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12707,6 +13247,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385976</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12818,6 +13363,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385960</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12929,6 +13479,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385977</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13040,6 +13595,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382393</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13151,6 +13711,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357039</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13262,6 +13827,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385959</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13373,6 +13943,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385969</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13484,6 +14059,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358340</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13595,6 +14175,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382723</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13706,6 +14291,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382739</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13817,6 +14407,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383976</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13928,6 +14523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385944</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14039,6 +14639,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382410</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14150,6 +14755,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382412</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14261,6 +14871,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384266</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14372,6 +14987,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384268</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14483,6 +15103,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384279</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14594,6 +15219,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384281</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14705,6 +15335,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384330</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14816,6 +15451,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385947</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14927,6 +15567,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385957</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15038,6 +15683,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382032</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15149,6 +15799,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384249</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15260,6 +15915,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384258</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15371,6 +16031,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357042</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15482,6 +16147,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357048</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15593,6 +16263,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379237</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15704,6 +16379,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382041</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15815,6 +16495,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382721</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15926,6 +16611,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382730</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16037,6 +16727,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382770</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16148,6 +16843,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384251</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16259,6 +16959,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384256</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16370,6 +17075,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384278</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16481,6 +17191,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384291</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16592,6 +17307,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357041</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16703,6 +17423,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382744</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16814,6 +17539,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382754</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16925,6 +17655,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385964</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17036,6 +17771,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385967</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17147,6 +17887,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135386008</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17258,6 +18003,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383990</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17367,6 +18117,11 @@
       <c r="AY151" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385954</t>
         </is>
       </c>
     </row>
@@ -17484,6 +18239,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385951</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17595,6 +18355,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385942</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17706,6 +18471,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382724</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17817,6 +18587,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383978</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17928,6 +18703,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385955</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18039,6 +18819,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385946</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18150,6 +18935,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382758</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18261,6 +19051,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385950</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18370,6 +19165,11 @@
       <c r="AY160" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385958</t>
         </is>
       </c>
     </row>
@@ -18484,6 +19284,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135389393</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18595,6 +19400,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357037</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18706,6 +19516,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382722</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18817,6 +19632,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382737</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18928,6 +19748,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382743</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19039,6 +19864,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382755</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19150,6 +19980,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382759</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19261,6 +20096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382768</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19372,6 +20212,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382777</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19483,6 +20328,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383977</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19594,6 +20444,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383986</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19705,6 +20560,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383995</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19816,6 +20676,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384133</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19927,6 +20792,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382053</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20038,6 +20908,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383947</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20150,6 +21025,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382043</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20261,6 +21141,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357031</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20372,6 +21257,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357033</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20483,6 +21373,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357035</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20594,6 +21489,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379257</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20705,6 +21605,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382440</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20816,6 +21721,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382442</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20927,6 +21837,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382445</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21038,6 +21953,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382448</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21149,6 +22069,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382763</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21260,6 +22185,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383940</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21371,6 +22301,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385134</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21482,6 +22417,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385983</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21593,6 +22533,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379260</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21704,6 +22649,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382055</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21815,6 +22765,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384325</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21926,6 +22881,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382762</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22037,6 +22997,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383937</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22148,6 +23113,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385132</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22259,6 +23229,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382428</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22370,6 +23345,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384158</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22481,6 +23461,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385985</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22592,6 +23577,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135386085</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22703,6 +23693,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382420</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22814,6 +23809,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385133</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22925,6 +23925,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357030</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23036,6 +24041,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382057</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23147,6 +24157,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382438</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23258,6 +24273,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382446</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23369,6 +24389,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382765</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23481,6 +24506,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382436</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23592,6 +24622,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382434</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23703,6 +24738,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383960</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23814,6 +24854,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384155</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23925,6 +24970,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385135</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24036,6 +25086,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385979</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24147,6 +25202,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382060</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24258,6 +25318,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382062</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24384,6 +25449,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385130</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24495,6 +25565,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385980</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24611,6 +25686,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384316</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24730,6 +25810,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382766</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24841,6 +25926,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382435</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24952,6 +26042,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383970</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25063,6 +26158,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384332</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25174,6 +26274,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384318</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25285,6 +26390,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383932</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25396,6 +26506,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384295</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25507,6 +26622,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384309</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25618,6 +26738,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384311</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25729,6 +26854,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384327</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25840,6 +26970,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384312</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25951,6 +27086,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384322</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26062,6 +27202,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382050</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26173,6 +27318,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382761</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26284,6 +27434,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384302</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26395,6 +27550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384304</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26506,6 +27666,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384323</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26617,6 +27782,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384329</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26728,6 +27898,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383955</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26839,6 +28014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383961</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26950,6 +28130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383936</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27061,6 +28246,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383957</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27172,6 +28362,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382764</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27283,6 +28478,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383934</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27394,6 +28594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383942</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27506,6 +28711,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383954</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27617,6 +28827,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383958</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27728,6 +28943,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383969</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27839,6 +29059,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380606</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27950,6 +29175,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357457</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28061,6 +29291,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354306</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28172,6 +29407,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351913</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28283,6 +29523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135386003</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28394,6 +29639,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350748</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28505,6 +29755,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354307</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28616,6 +29871,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383923</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28732,6 +29992,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357008</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28848,6 +30113,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383921</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28962,6 +30232,11 @@
       <c r="AY255" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383924</t>
         </is>
       </c>
     </row>
@@ -29084,6 +30359,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383916</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29195,6 +30475,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353579</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29306,6 +30591,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357007</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29417,6 +30707,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357057</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29528,6 +30823,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357059</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29639,6 +30939,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380605</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29750,6 +31055,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350615</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29861,6 +31171,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351914</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29972,6 +31287,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354305</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -30083,6 +31403,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382457</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -30194,6 +31519,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382453</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -30305,6 +31635,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382455</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -30414,6 +31749,11 @@
       <c r="AY268" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385141</t>
         </is>
       </c>
     </row>
@@ -30550,6 +31890,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135386004</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30661,6 +32006,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357458</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30772,6 +32122,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363071</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30883,6 +32238,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382456</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30994,6 +32354,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383919</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -31105,6 +32470,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135386001</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -31216,6 +32586,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135386002</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -31332,6 +32707,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353578</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -31448,6 +32828,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351912</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -31564,6 +32949,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357727</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31675,6 +33065,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382451</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31786,6 +33181,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382462</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31897,6 +33297,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379281</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -32008,6 +33413,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351911</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -32119,6 +33529,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383925</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -32230,6 +33645,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353582</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -32341,6 +33761,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358339</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -32452,6 +33877,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379275</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -32563,6 +33993,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353577</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32674,6 +34109,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353581</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32785,6 +34225,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357058</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32896,6 +34341,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383915</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -33007,6 +34457,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353580</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -33118,6 +34573,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358334</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -33230,6 +34690,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358336</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -33341,6 +34806,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358338</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -33452,6 +34922,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350617</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -33563,6 +35038,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357009</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33679,6 +35159,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361457</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -33790,6 +35275,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350633</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -33902,6 +35392,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351916</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -34013,6 +35508,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357469</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -34124,6 +35624,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357024</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -34235,6 +35740,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350626</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -34347,6 +35857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357468</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -34458,6 +35973,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350629</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -34569,6 +36089,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350753</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -34680,6 +36205,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379266</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -34791,6 +36321,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379272</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -34902,6 +36437,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385139</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -35013,6 +36553,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354411</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -35124,6 +36669,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363074</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -35233,6 +36783,11 @@
       <c r="AY311" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350627</t>
         </is>
       </c>
     </row>
@@ -35345,6 +36900,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361715</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -35456,6 +37016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350628</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -35567,6 +37132,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350755</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -35678,6 +37248,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351919</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -35789,6 +37364,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357023</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -35900,6 +37480,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382450</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -36011,6 +37596,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385136</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -36122,6 +37712,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350625</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -36233,6 +37828,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351917</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -36344,6 +37944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350623</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -36455,6 +38060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357459</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -36566,6 +38176,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357463</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -36682,6 +38297,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357467</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -36793,6 +38413,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379269</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -36904,6 +38529,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383930</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -37015,6 +38645,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385988</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -37126,6 +38761,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385990</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -37237,6 +38877,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385992</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -37348,6 +38993,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385993</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -37459,6 +39109,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385996</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -37570,6 +39225,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350624</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -37681,6 +39341,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354309</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -37792,6 +39457,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363072</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -37903,6 +39573,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383929</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -38014,6 +39689,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385987</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -38125,6 +39805,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385989</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -38236,6 +39921,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385997</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -38347,6 +40037,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385999</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -38458,6 +40153,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350620</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -38569,6 +40269,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350622</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -38680,6 +40385,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385986</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -38791,6 +40501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385991</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -38902,6 +40617,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385994</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -39013,6 +40733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385995</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -39124,6 +40849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385998</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -39240,6 +40970,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350752</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -39356,6 +41091,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350754</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -39472,6 +41212,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357018</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -39588,6 +41333,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354310</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -39699,6 +41449,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354407</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -39810,6 +41565,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357020</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -39921,6 +41681,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357464</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -40032,6 +41797,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357021</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -40143,6 +41913,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357016</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -40254,6 +42029,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383931</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -40365,6 +42145,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357437</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -40476,6 +42261,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357465</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -40587,6 +42377,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382449</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -40698,6 +42493,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357026</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -40809,6 +42609,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357013</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -40920,6 +42725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357015</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -41031,6 +42841,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357435</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -41142,6 +42957,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379271</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -41249,6 +43069,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357019</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -41356,6 +43181,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357028</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -41467,6 +43297,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354408</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -41578,6 +43413,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357014</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -41689,6 +43529,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350632</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -41800,6 +43645,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350608</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -41911,6 +43761,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380604</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -42022,6 +43877,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350612</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -42138,6 +43998,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361453</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -42249,6 +44114,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363070</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -42360,6 +44230,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380603</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -42471,6 +44346,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350613</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -42582,6 +44462,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354304</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -42698,6 +44583,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361454</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -42809,6 +44699,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350604</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -42920,6 +44815,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351906</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -43031,6 +44931,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351907</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -43142,6 +45047,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354303</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -43253,6 +45163,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350607</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -43364,6 +45279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350745</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -43475,6 +45395,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357004</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -43586,6 +45511,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357726</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -43697,6 +45627,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351909</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -43808,6 +45743,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357006</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -43919,6 +45859,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350609</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -44030,6 +45975,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350743</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -44141,6 +46091,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351905</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -44252,6 +46207,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350611</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -44368,6 +46328,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350746</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -44479,6 +46444,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357725</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -44590,6 +46560,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357432</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -44701,6 +46676,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357005</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -44807,6 +46787,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350610</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -44918,6 +46903,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380601</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -45029,6 +47019,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350655</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -45140,6 +47135,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357454</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -45251,6 +47251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350666</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -45362,6 +47367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380602</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -45473,6 +47483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350644</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -45584,6 +47599,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350649</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -45695,6 +47715,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350658</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -45806,6 +47831,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350665</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -45917,6 +47947,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350758</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -46028,6 +48063,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350760</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -46139,6 +48179,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354420</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -46250,6 +48295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357478</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -46361,6 +48411,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357482</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -46472,6 +48527,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361459</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -46583,6 +48643,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350653</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -46694,6 +48759,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351898</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -46805,6 +48875,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351904</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -46916,6 +48991,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351922</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -47027,6 +49107,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357002</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -47139,6 +49224,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357476</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -47250,6 +49340,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350651</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -47361,6 +49456,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350659</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -47472,6 +49572,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350663</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -47583,6 +49688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350672</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -47694,6 +49804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350757</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -47805,6 +49920,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356998</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -47917,6 +50037,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357474</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -48028,6 +50153,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350643</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -48139,6 +50269,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350646</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -48250,6 +50385,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350650</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -48361,6 +50501,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351926</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -48472,6 +50617,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354300</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -48583,6 +50733,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357064</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -48694,6 +50849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357473</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -48805,6 +50965,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357480</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -48916,6 +51081,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350654</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -49027,6 +51197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350657</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -49138,6 +51313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356995</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -49254,6 +51434,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354312</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -49365,6 +51550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361460</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -49476,6 +51666,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350647</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -49587,6 +51782,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363069</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -49698,6 +51898,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350669</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -49809,6 +52014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356997</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -49920,6 +52130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350645</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -50031,6 +52246,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350648</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -50142,6 +52362,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350759</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -50253,6 +52478,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350600</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -50364,6 +52594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361462</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -50475,6 +52710,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351925</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -50586,6 +52826,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350638</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -50697,6 +52942,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350642</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -50808,6 +53058,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350656</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -50919,6 +53174,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350664</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -51030,6 +53290,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351901</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -51141,6 +53406,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351902</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -51252,6 +53522,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351903</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -51363,6 +53638,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351921</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -51474,6 +53754,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354393</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -51585,6 +53870,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356996</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -51696,6 +53986,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357000</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -51807,6 +54102,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357061</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -51918,6 +54218,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357062</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -52029,6 +54334,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ462" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361450</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -52140,6 +54450,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ463" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361458</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -52251,6 +54566,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ464" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354311</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -52362,6 +54682,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ465" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357060</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -52473,6 +54798,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ466" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350652</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -52584,6 +54914,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ467" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350671</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -52700,6 +55035,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ468" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361452</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -52811,6 +55151,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ469" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363076</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -52922,6 +55267,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ470" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350606</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -53038,6 +55388,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ471" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361461</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -53149,6 +55504,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350598</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -53260,6 +55620,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354314</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -53376,6 +55741,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ474" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350599</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -53492,6 +55862,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350667</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -53608,6 +55983,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350670</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -53722,6 +56102,11 @@
       <c r="AY477" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350744</t>
         </is>
       </c>
     </row>
@@ -53844,6 +56229,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ478" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357063</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -53965,6 +56355,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ479" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357477</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -54086,6 +56481,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ480" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357483</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -54207,6 +56607,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ481" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363075</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -54327,6 +56732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ482" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350635</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -54438,6 +56848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ483" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363077</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -54549,6 +56964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ484" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354302</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -54660,6 +57080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ485" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354390</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -54771,6 +57196,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ486" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354391</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -54882,6 +57312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ487" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350637</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -54993,6 +57428,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ488" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354389</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -55104,6 +57544,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ489" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357431</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -55215,6 +57660,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ490" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351924</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -55326,6 +57776,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ491" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357001</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -55437,6 +57892,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ492" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361463</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -55548,6 +58008,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ493" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350605</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -55659,6 +58124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ494" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350641</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -55770,6 +58240,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ495" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351935</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -55881,6 +58356,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ496" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350728</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -55992,6 +58472,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ497" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354377</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -56103,6 +58588,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ498" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354423</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -56214,6 +58704,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ499" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361466</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -56331,6 +58826,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ500" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356982</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -56443,6 +58943,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ501" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356988</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -56554,6 +59059,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ502" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350579</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -56665,6 +59175,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ503" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350596</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -56776,6 +59291,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ504" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350679</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -56887,6 +59407,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ505" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356980</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -56998,6 +59523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ506" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357075</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -57109,6 +59639,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ507" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380600</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -57220,6 +59755,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ508" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361449</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -57336,6 +59876,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ509" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350594</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -57447,6 +59992,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ510" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351897</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -57558,6 +60108,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ511" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351929</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -57669,6 +60224,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ512" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354318</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -57780,6 +60340,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ513" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357068</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -57891,6 +60456,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ514" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350575</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -58002,6 +60572,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ515" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350592</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -58113,6 +60688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ516" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350677</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -58224,6 +60804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ517" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351934</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -58335,6 +60920,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ518" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380595</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -58451,6 +61041,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ519" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361446</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -58567,6 +61162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ520" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361447</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -58678,6 +61278,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ521" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350581</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -58789,6 +61394,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ522" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350674</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -58900,6 +61510,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ523" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350740</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -59011,6 +61626,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ524" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350763</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -59122,6 +61742,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ525" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354382</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -59233,6 +61858,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ526" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356975</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -59344,6 +61974,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ527" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356977</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -59455,6 +62090,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ528" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357066</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -59566,6 +62206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ529" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357076</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -59677,6 +62322,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ530" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357445</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -59793,6 +62443,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ531" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361445</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -59904,6 +62559,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ532" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350730</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -60015,6 +62675,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ533" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354295</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -60126,6 +62791,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ534" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354297</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -60237,6 +62907,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ535" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354322</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -60348,6 +63023,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ536" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354383</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -60459,6 +63139,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ537" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356976</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -60570,6 +63255,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ538" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356983</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -60681,6 +63371,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ539" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357441</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -60792,6 +63487,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ540" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350675</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -60903,6 +63603,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ541" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356985</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -61014,6 +63719,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ542" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357073</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -61125,6 +63835,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ543" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363066</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -61236,6 +63951,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ544" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363078</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -61347,6 +64067,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ545" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350680</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -61463,6 +64188,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ546" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356978</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -61574,6 +64304,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ547" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356987</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -61685,6 +64420,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ548" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356989</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -61796,6 +64536,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ549" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357452</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -61907,6 +64652,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ550" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350673</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -62018,6 +64768,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ551" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357450</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -62134,6 +64889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ552" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361448</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -62245,6 +65005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ553" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350590</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -62356,6 +65121,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ554" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361465</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -62467,6 +65237,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ555" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356973</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -62578,6 +65353,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ556" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380594</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -62689,6 +65469,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ557" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380599</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -62800,6 +65585,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ558" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354296</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -62916,6 +65706,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ559" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357067</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -63027,6 +65822,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ560" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354381</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -63144,6 +65944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ561" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357072</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -63255,6 +66060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ562" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350569</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -63366,6 +66176,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ563" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350570</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -63477,6 +66292,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ564" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350588</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -63588,6 +66408,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ565" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351882</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -63699,6 +66524,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ566" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351891</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -63810,6 +66640,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ567" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351896</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -63921,6 +66756,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ568" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351933</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -64032,6 +66872,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ569" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356965</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -64143,6 +66988,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ570" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356986</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -64254,6 +67104,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ571" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357069</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -64363,6 +67218,11 @@
       <c r="AY572" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ572" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357071</t>
         </is>
       </c>
     </row>
@@ -64480,6 +67340,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ573" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357722</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -64591,6 +67456,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ574" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356979</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -64702,6 +67572,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ575" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350587</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -64813,6 +67688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ576" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356993</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -64924,6 +67804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ577" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357451</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -65035,6 +67920,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ578" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350572</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -65146,6 +68036,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ579" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350580</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -65257,6 +68152,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ580" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351877</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -65368,6 +68268,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ581" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354294</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -65479,6 +68384,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ582" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354298</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -65590,6 +68500,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ583" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356964</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -65701,6 +68616,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ584" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356969</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -65812,6 +68732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ585" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357070</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -65923,6 +68848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ586" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357077</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -66034,6 +68964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ587" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357444</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -66145,6 +69080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ588" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357486</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -66261,6 +69201,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ589" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357447</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -66372,6 +69317,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ590" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361464</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -66483,6 +69433,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ591" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350593</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -66594,6 +69549,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ592" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356991</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -66705,6 +69665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ593" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357721</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -66821,6 +69786,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ594" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350576</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -66937,6 +69907,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ595" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350583</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -67053,6 +70028,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ596" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350764</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -67169,6 +70149,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ597" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354320</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -67293,6 +70278,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ598" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357488</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -67414,6 +70404,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ599" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363067</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -67525,6 +70520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ600" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350578</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -67636,6 +70636,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ601" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354424</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -67747,6 +70752,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ602" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356970</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -67858,6 +70868,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ603" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357424</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -67969,6 +70984,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ604" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354385</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -68080,6 +71100,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ605" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363079</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -68191,6 +71216,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ606" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354316</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -68302,6 +71332,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ607" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356990</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -68413,6 +71448,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ608" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357428</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -68524,6 +71564,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ609" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357723</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -68635,6 +71680,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ610" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135363068</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -68746,6 +71796,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ611" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357413</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -68857,6 +71912,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ612" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351879</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -68968,6 +72028,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ613" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350571</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -69079,6 +72144,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ614" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357421</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -69190,6 +72260,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ615" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356968</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -69301,6 +72376,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ616" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357440</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -69413,6 +72493,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ617" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354425</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -69524,6 +72609,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ618" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351883</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -69635,6 +72725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ619" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351890</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -69746,6 +72841,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ620" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351895</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -69857,6 +72957,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ621" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357411</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -69968,6 +73073,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ622" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357417</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -70079,6 +73189,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ623" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357426</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -70190,6 +73305,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ624" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357429</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -70301,6 +73421,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ625" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351878</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -70412,6 +73537,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ626" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351888</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -70523,6 +73653,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ627" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356971</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -70634,6 +73769,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ628" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357078</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -70745,6 +73885,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ629" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357410</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -70856,6 +74001,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ630" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357422</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -70967,6 +74117,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ631" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357415</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -71078,6 +74233,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ632" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357416</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -71189,6 +74349,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ633" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357427</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -71300,6 +74465,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ634" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135380596</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -71411,6 +74581,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ635" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357412</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -71522,6 +74697,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ636" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351880</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -71633,6 +74813,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ637" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357418</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -71744,6 +74929,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ638" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357423</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -71851,6 +75041,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ639" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356967</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -71962,6 +75157,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ640" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351885</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -72073,6 +75273,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ641" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356966</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -72184,6 +75389,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ642" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350568</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -72295,8 +75505,657 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ643" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350582</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ540" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ541" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ542" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ543" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ544" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ545" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ546" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ547" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ548" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ549" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ550" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ551" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ552" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ553" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ554" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ555" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ556" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ557" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ558" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ559" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ560" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ561" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ562" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ563" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ564" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ565" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ566" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ567" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ568" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ569" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ570" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ571" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ572" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ573" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ574" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ575" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ576" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ577" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ578" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ579" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ580" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ581" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ582" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ583" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ584" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ585" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ586" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ587" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ588" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ589" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ590" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ591" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ592" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ593" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ594" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ595" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ596" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ597" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ598" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ599" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ600" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ601" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ602" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ603" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ604" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ605" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ606" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ607" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ608" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ609" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ610" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ611" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ612" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ613" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ614" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ615" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ616" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ617" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ618" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ619" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ620" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ621" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ622" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ623" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ624" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ625" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ626" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ627" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ628" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ629" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ630" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ631" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ632" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ633" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ634" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ635" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ636" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ637" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ638" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ639" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ640" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ641" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ642" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ643" r:id="rId642"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -36777,7 +36777,7 @@
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
@@ -43637,7 +43637,7 @@
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Elin Kannerby, Marie Persson, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
@@ -45155,7 +45155,7 @@
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
@@ -51890,7 +51890,7 @@
       </c>
       <c r="AX441" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño</t>
         </is>
       </c>
       <c r="AY441" t="inlineStr">
@@ -52818,7 +52818,7 @@
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
@@ -59167,7 +59167,7 @@
       </c>
       <c r="AX503" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY503" t="inlineStr">
@@ -67564,7 +67564,7 @@
       </c>
       <c r="AX575" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY575" t="inlineStr">
@@ -69778,7 +69778,7 @@
       </c>
       <c r="AX594" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY594" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135382760</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>135384331</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135382413</v>
       </c>
       <c r="B4" t="n">
-        <v>83343</v>
+        <v>83383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>135384288</v>
       </c>
       <c r="B5" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135379254</v>
       </c>
       <c r="B6" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135379255</v>
       </c>
       <c r="B7" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135382735</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>135382750</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>135382772</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>135383974</v>
       </c>
       <c r="B11" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>135384144</v>
       </c>
       <c r="B12" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>135384270</v>
       </c>
       <c r="B13" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>135384286</v>
       </c>
       <c r="B14" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>135385128</v>
       </c>
       <c r="B15" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>135357040</v>
       </c>
       <c r="B16" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>135382042</v>
       </c>
       <c r="B17" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135383991</v>
       </c>
       <c r="B18" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>135379238</v>
       </c>
       <c r="B19" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135379243</v>
       </c>
       <c r="B20" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135379248</v>
       </c>
       <c r="B21" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135379249</v>
       </c>
       <c r="B22" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135379252</v>
       </c>
       <c r="B23" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>135382411</v>
       </c>
       <c r="B24" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>135382725</v>
       </c>
       <c r="B25" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135382733</v>
       </c>
       <c r="B26" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>135383965</v>
       </c>
       <c r="B27" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>135384150</v>
       </c>
       <c r="B28" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>135385952</v>
       </c>
       <c r="B29" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>135385965</v>
       </c>
       <c r="B30" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>135385966</v>
       </c>
       <c r="B31" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>135385973</v>
       </c>
       <c r="B32" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>135379246</v>
       </c>
       <c r="B33" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>135382064</v>
       </c>
       <c r="B34" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135382736</v>
       </c>
       <c r="B35" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>135383967</v>
       </c>
       <c r="B36" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>135384131</v>
       </c>
       <c r="B37" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>135384136</v>
       </c>
       <c r="B38" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>135384146</v>
       </c>
       <c r="B39" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>135384153</v>
       </c>
       <c r="B40" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>135384272</v>
       </c>
       <c r="B41" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>135385129</v>
       </c>
       <c r="B42" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>135386007</v>
       </c>
       <c r="B43" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>135379250</v>
       </c>
       <c r="B44" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>135382403</v>
       </c>
       <c r="B45" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>135383973</v>
       </c>
       <c r="B46" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>135385127</v>
       </c>
       <c r="B47" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>135383992</v>
       </c>
       <c r="B48" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>135382399</v>
       </c>
       <c r="B49" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>135382407</v>
       </c>
       <c r="B50" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>135379247</v>
       </c>
       <c r="B51" t="n">
-        <v>92332</v>
+        <v>92374</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>135357049</v>
       </c>
       <c r="B52" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>135357050</v>
       </c>
       <c r="B53" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>135384148</v>
       </c>
       <c r="B54" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>135385971</v>
       </c>
       <c r="B55" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135387640</v>
       </c>
       <c r="B56" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>135382727</v>
       </c>
       <c r="B57" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>135382741</v>
       </c>
       <c r="B58" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>135382757</v>
       </c>
       <c r="B59" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>135385962</v>
       </c>
       <c r="B60" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>135382999</v>
       </c>
       <c r="B61" t="n">
-        <v>92326</v>
+        <v>92368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>135382745</v>
       </c>
       <c r="B62" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>135380608</v>
       </c>
       <c r="B63" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>135382742</v>
       </c>
       <c r="B64" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135382748</v>
       </c>
       <c r="B65" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>135382753</v>
       </c>
       <c r="B66" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>135382767</v>
       </c>
       <c r="B67" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>135382773</v>
       </c>
       <c r="B68" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>135382778</v>
       </c>
       <c r="B69" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>135383981</v>
       </c>
       <c r="B70" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>135383962</v>
       </c>
       <c r="B71" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>135357046</v>
       </c>
       <c r="B72" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>135382034</v>
       </c>
       <c r="B73" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>135382036</v>
       </c>
       <c r="B74" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>135382400</v>
       </c>
       <c r="B75" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>135382417</v>
       </c>
       <c r="B76" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>135382419</v>
       </c>
       <c r="B77" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>135382466</v>
       </c>
       <c r="B78" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>135382731</v>
       </c>
       <c r="B79" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>135384252</v>
       </c>
       <c r="B80" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>135384261</v>
       </c>
       <c r="B81" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>135384285</v>
       </c>
       <c r="B82" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>135385123</v>
       </c>
       <c r="B83" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>135385124</v>
       </c>
       <c r="B84" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>135382396</v>
       </c>
       <c r="B85" t="n">
-        <v>75340</v>
+        <v>75373</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>135385120</v>
       </c>
       <c r="B86" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>135382391</v>
       </c>
       <c r="B87" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>135385941</v>
       </c>
       <c r="B88" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>135382746</v>
       </c>
       <c r="B89" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>135382749</v>
       </c>
       <c r="B90" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>135382463</v>
       </c>
       <c r="B91" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135382752</v>
       </c>
       <c r="B92" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>135382774</v>
       </c>
       <c r="B93" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>135382751</v>
       </c>
       <c r="B94" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>135382775</v>
       </c>
       <c r="B95" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>135382039</v>
       </c>
       <c r="B96" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>135382040</v>
       </c>
       <c r="B97" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>135382747</v>
       </c>
       <c r="B98" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>135384138</v>
       </c>
       <c r="B99" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>135384126</v>
       </c>
       <c r="B100" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>135384141</v>
       </c>
       <c r="B101" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>135385126</v>
       </c>
       <c r="B102" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>135383964</v>
       </c>
       <c r="B103" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>135357038</v>
       </c>
       <c r="B104" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>135383994</v>
       </c>
       <c r="B105" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>135384128</v>
       </c>
       <c r="B106" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>135385940</v>
       </c>
       <c r="B107" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>135385968</v>
       </c>
       <c r="B108" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>135385976</v>
       </c>
       <c r="B109" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>135385960</v>
       </c>
       <c r="B110" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>135385977</v>
       </c>
       <c r="B111" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>135382393</v>
       </c>
       <c r="B112" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>135357039</v>
       </c>
       <c r="B113" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>135385959</v>
       </c>
       <c r="B114" t="n">
-        <v>110150</v>
+        <v>110206</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>135385969</v>
       </c>
       <c r="B115" t="n">
-        <v>110150</v>
+        <v>110206</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>135358340</v>
       </c>
       <c r="B116" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>135382723</v>
       </c>
       <c r="B117" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>135382739</v>
       </c>
       <c r="B118" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>135383976</v>
       </c>
       <c r="B119" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>135385944</v>
       </c>
       <c r="B120" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>135382410</v>
       </c>
       <c r="B121" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>135382412</v>
       </c>
       <c r="B122" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>135384266</v>
       </c>
       <c r="B123" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>135384268</v>
       </c>
       <c r="B124" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>135384279</v>
       </c>
       <c r="B125" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>135384281</v>
       </c>
       <c r="B126" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>135384330</v>
       </c>
       <c r="B127" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>135385947</v>
       </c>
       <c r="B128" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>135385957</v>
       </c>
       <c r="B129" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>135382032</v>
       </c>
       <c r="B130" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>135384249</v>
       </c>
       <c r="B131" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135384258</v>
       </c>
       <c r="B132" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>135357042</v>
       </c>
       <c r="B133" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>135357048</v>
       </c>
       <c r="B134" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>135379237</v>
       </c>
       <c r="B135" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>135382041</v>
       </c>
       <c r="B136" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>135382721</v>
       </c>
       <c r="B137" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>135382730</v>
       </c>
       <c r="B138" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>135382770</v>
       </c>
       <c r="B139" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>135384251</v>
       </c>
       <c r="B140" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>135384256</v>
       </c>
       <c r="B141" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>135384278</v>
       </c>
       <c r="B142" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>135384291</v>
       </c>
       <c r="B143" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>135357041</v>
       </c>
       <c r="B144" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>135382744</v>
       </c>
       <c r="B145" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>135382754</v>
       </c>
       <c r="B146" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>135385964</v>
       </c>
       <c r="B147" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>135385967</v>
       </c>
       <c r="B148" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>135386008</v>
       </c>
       <c r="B149" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>135383990</v>
       </c>
       <c r="B150" t="n">
-        <v>99205</v>
+        <v>99252</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>135385954</v>
       </c>
       <c r="B151" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>135385951</v>
       </c>
       <c r="B152" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>135385942</v>
       </c>
       <c r="B153" t="n">
-        <v>99504</v>
+        <v>99551</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>135382724</v>
       </c>
       <c r="B154" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>135383978</v>
       </c>
       <c r="B155" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>135385955</v>
       </c>
       <c r="B156" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>135385946</v>
       </c>
       <c r="B157" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>135382758</v>
       </c>
       <c r="B158" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>135385950</v>
       </c>
       <c r="B159" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>135385958</v>
       </c>
       <c r="B160" t="n">
-        <v>101940</v>
+        <v>101988</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>135389393</v>
       </c>
       <c r="B161" t="n">
-        <v>105771</v>
+        <v>105825</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>135357037</v>
       </c>
       <c r="B162" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>135382722</v>
       </c>
       <c r="B163" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>135382737</v>
       </c>
       <c r="B164" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>135382743</v>
       </c>
       <c r="B165" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>135382755</v>
       </c>
       <c r="B166" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>135382759</v>
       </c>
       <c r="B167" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>135382768</v>
       </c>
       <c r="B168" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>135382777</v>
       </c>
       <c r="B169" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>135383977</v>
       </c>
       <c r="B170" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>135383986</v>
       </c>
       <c r="B171" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>135383995</v>
       </c>
       <c r="B172" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>135384133</v>
       </c>
       <c r="B173" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>135382053</v>
       </c>
       <c r="B174" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>135383947</v>
       </c>
       <c r="B175" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>135382043</v>
       </c>
       <c r="B176" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>135357031</v>
       </c>
       <c r="B177" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>135357033</v>
       </c>
       <c r="B178" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>135357035</v>
       </c>
       <c r="B179" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>135379257</v>
       </c>
       <c r="B180" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>135382440</v>
       </c>
       <c r="B181" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>135382442</v>
       </c>
       <c r="B182" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>135382445</v>
       </c>
       <c r="B183" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>135382448</v>
       </c>
       <c r="B184" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135382763</v>
       </c>
       <c r="B185" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>135383940</v>
       </c>
       <c r="B186" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>135385134</v>
       </c>
       <c r="B187" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>135385983</v>
       </c>
       <c r="B188" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>135379260</v>
       </c>
       <c r="B189" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>135382055</v>
       </c>
       <c r="B190" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>135384325</v>
       </c>
       <c r="B191" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>135382762</v>
       </c>
       <c r="B192" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>135383937</v>
       </c>
       <c r="B193" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>135385132</v>
       </c>
       <c r="B194" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>135382428</v>
       </c>
       <c r="B195" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>135384158</v>
       </c>
       <c r="B196" t="n">
-        <v>92332</v>
+        <v>92374</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>135385985</v>
       </c>
       <c r="B197" t="n">
-        <v>96425</v>
+        <v>96469</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>135386085</v>
       </c>
       <c r="B198" t="n">
-        <v>92199</v>
+        <v>92241</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>135382420</v>
       </c>
       <c r="B199" t="n">
-        <v>87625</v>
+        <v>87665</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>135385133</v>
       </c>
       <c r="B200" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>135357030</v>
       </c>
       <c r="B201" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>135382057</v>
       </c>
       <c r="B202" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>135382438</v>
       </c>
       <c r="B203" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>135382446</v>
       </c>
       <c r="B204" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>135382765</v>
       </c>
       <c r="B205" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>135382436</v>
       </c>
       <c r="B206" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>135382434</v>
       </c>
       <c r="B207" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>135383960</v>
       </c>
       <c r="B208" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>135384155</v>
       </c>
       <c r="B209" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>135385135</v>
       </c>
       <c r="B210" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>135385979</v>
       </c>
       <c r="B211" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>135382060</v>
       </c>
       <c r="B212" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>135382062</v>
       </c>
       <c r="B213" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>135385130</v>
       </c>
       <c r="B214" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>135385980</v>
       </c>
       <c r="B215" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>135384316</v>
       </c>
       <c r="B216" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>135382766</v>
       </c>
       <c r="B217" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>135382435</v>
       </c>
       <c r="B218" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>135383970</v>
       </c>
       <c r="B219" t="n">
-        <v>56539</v>
+        <v>56544</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>135384332</v>
       </c>
       <c r="B220" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>135384318</v>
       </c>
       <c r="B221" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>135383932</v>
       </c>
       <c r="B222" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>135384295</v>
       </c>
       <c r="B223" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>135384309</v>
       </c>
       <c r="B224" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>135384311</v>
       </c>
       <c r="B225" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>135384327</v>
       </c>
       <c r="B226" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>135384312</v>
       </c>
       <c r="B227" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>135384322</v>
       </c>
       <c r="B228" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>135382050</v>
       </c>
       <c r="B229" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>135382761</v>
       </c>
       <c r="B230" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>135384302</v>
       </c>
       <c r="B231" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>135384304</v>
       </c>
       <c r="B232" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>135384323</v>
       </c>
       <c r="B233" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>135384329</v>
       </c>
       <c r="B234" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>135383955</v>
       </c>
       <c r="B235" t="n">
-        <v>99205</v>
+        <v>99252</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>135383961</v>
       </c>
       <c r="B236" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>135383936</v>
       </c>
       <c r="B237" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>135383957</v>
       </c>
       <c r="B238" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>135382764</v>
       </c>
       <c r="B239" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>135383934</v>
       </c>
       <c r="B240" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>135383942</v>
       </c>
       <c r="B241" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>135383954</v>
       </c>
       <c r="B242" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>135383958</v>
       </c>
       <c r="B243" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>135383969</v>
       </c>
       <c r="B244" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>135380606</v>
       </c>
       <c r="B245" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>135357457</v>
       </c>
       <c r="B246" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>135354306</v>
       </c>
       <c r="B247" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>135351913</v>
       </c>
       <c r="B248" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>135386003</v>
       </c>
       <c r="B249" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>135350748</v>
       </c>
       <c r="B250" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>135354307</v>
       </c>
       <c r="B251" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>135383923</v>
       </c>
       <c r="B252" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>135357008</v>
       </c>
       <c r="B253" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>135383921</v>
       </c>
       <c r="B254" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>135383924</v>
       </c>
       <c r="B255" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>135383916</v>
       </c>
       <c r="B256" t="n">
-        <v>93089</v>
+        <v>93131</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>135353579</v>
       </c>
       <c r="B257" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>135357007</v>
       </c>
       <c r="B258" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>135357057</v>
       </c>
       <c r="B259" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>135357059</v>
       </c>
       <c r="B260" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>135380605</v>
       </c>
       <c r="B261" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>135350615</v>
       </c>
       <c r="B262" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>135351914</v>
       </c>
       <c r="B263" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>135354305</v>
       </c>
       <c r="B264" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>135382457</v>
       </c>
       <c r="B265" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>135382453</v>
       </c>
       <c r="B266" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>135382455</v>
       </c>
       <c r="B267" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>135385141</v>
       </c>
       <c r="B268" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>135386004</v>
       </c>
       <c r="B269" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>135357458</v>
       </c>
       <c r="B270" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>135363071</v>
       </c>
       <c r="B271" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>135382456</v>
       </c>
       <c r="B272" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>135383919</v>
       </c>
       <c r="B273" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>135386001</v>
       </c>
       <c r="B274" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>135386002</v>
       </c>
       <c r="B275" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>135353578</v>
       </c>
       <c r="B276" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>135351912</v>
       </c>
       <c r="B277" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>135357727</v>
       </c>
       <c r="B278" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>135382451</v>
       </c>
       <c r="B279" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135382462</v>
       </c>
       <c r="B280" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>135379281</v>
       </c>
       <c r="B281" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>135351911</v>
       </c>
       <c r="B282" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>135383925</v>
       </c>
       <c r="B283" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>135353582</v>
       </c>
       <c r="B284" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>135358339</v>
       </c>
       <c r="B285" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>135379275</v>
       </c>
       <c r="B286" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>135353577</v>
       </c>
       <c r="B287" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>135353581</v>
       </c>
       <c r="B288" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>135357058</v>
       </c>
       <c r="B289" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>135383915</v>
       </c>
       <c r="B290" t="n">
-        <v>99205</v>
+        <v>99252</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>135353580</v>
       </c>
       <c r="B291" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>135358334</v>
       </c>
       <c r="B292" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>135358336</v>
       </c>
       <c r="B293" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>135358338</v>
       </c>
       <c r="B294" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>135350617</v>
       </c>
       <c r="B295" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>135357009</v>
       </c>
       <c r="B296" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>135361457</v>
       </c>
       <c r="B297" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>135350633</v>
       </c>
       <c r="B298" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>135351916</v>
       </c>
       <c r="B299" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>135357469</v>
       </c>
       <c r="B300" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>135357024</v>
       </c>
       <c r="B301" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>135350626</v>
       </c>
       <c r="B302" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>135357468</v>
       </c>
       <c r="B303" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>135350629</v>
       </c>
       <c r="B304" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>135350753</v>
       </c>
       <c r="B305" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>135379266</v>
       </c>
       <c r="B306" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>135379272</v>
       </c>
       <c r="B307" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>135385139</v>
       </c>
       <c r="B308" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>135354411</v>
       </c>
       <c r="B309" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>135363074</v>
       </c>
       <c r="B310" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>135350627</v>
       </c>
       <c r="B311" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
@@ -36796,7 +36796,7 @@
         <v>135361715</v>
       </c>
       <c r="B312" t="n">
-        <v>92326</v>
+        <v>92368</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>135350628</v>
       </c>
       <c r="B313" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>135350755</v>
       </c>
       <c r="B314" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>135351919</v>
       </c>
       <c r="B315" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>135357023</v>
       </c>
       <c r="B316" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>135382450</v>
       </c>
       <c r="B317" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>135385136</v>
       </c>
       <c r="B318" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>135350625</v>
       </c>
       <c r="B319" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>135351917</v>
       </c>
       <c r="B320" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>135350623</v>
       </c>
       <c r="B321" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>135357459</v>
       </c>
       <c r="B322" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>135357463</v>
       </c>
       <c r="B323" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>135357467</v>
       </c>
       <c r="B324" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>135379269</v>
       </c>
       <c r="B325" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>135383930</v>
       </c>
       <c r="B326" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>135385988</v>
       </c>
       <c r="B327" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>135385990</v>
       </c>
       <c r="B328" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>135385992</v>
       </c>
       <c r="B329" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>135385993</v>
       </c>
       <c r="B330" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>135385996</v>
       </c>
       <c r="B331" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>135350624</v>
       </c>
       <c r="B332" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>135354309</v>
       </c>
       <c r="B333" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>135363072</v>
       </c>
       <c r="B334" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>135383929</v>
       </c>
       <c r="B335" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>135385987</v>
       </c>
       <c r="B336" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>135385989</v>
       </c>
       <c r="B337" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>135385997</v>
       </c>
       <c r="B338" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>135385999</v>
       </c>
       <c r="B339" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>135350620</v>
       </c>
       <c r="B340" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
         <v>135350622</v>
       </c>
       <c r="B341" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>135385986</v>
       </c>
       <c r="B342" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>135385991</v>
       </c>
       <c r="B343" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>135385994</v>
       </c>
       <c r="B344" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>135385995</v>
       </c>
       <c r="B345" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>135385998</v>
       </c>
       <c r="B346" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>135350752</v>
       </c>
       <c r="B347" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>135350754</v>
       </c>
       <c r="B348" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>135357018</v>
       </c>
       <c r="B349" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>135354310</v>
       </c>
       <c r="B350" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>135354407</v>
       </c>
       <c r="B351" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41460,7 +41460,7 @@
         <v>135357020</v>
       </c>
       <c r="B352" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>135357464</v>
       </c>
       <c r="B353" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>135357021</v>
       </c>
       <c r="B354" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>135357016</v>
       </c>
       <c r="B355" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>135383931</v>
       </c>
       <c r="B356" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>135357437</v>
       </c>
       <c r="B357" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>135357465</v>
       </c>
       <c r="B358" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>135382449</v>
       </c>
       <c r="B359" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>135357026</v>
       </c>
       <c r="B360" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>135357013</v>
       </c>
       <c r="B361" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>135357015</v>
       </c>
       <c r="B362" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>135357435</v>
       </c>
       <c r="B363" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>135379271</v>
       </c>
       <c r="B364" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>135357019</v>
       </c>
       <c r="B365" t="n">
-        <v>105771</v>
+        <v>105825</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>135357028</v>
       </c>
       <c r="B366" t="n">
-        <v>105771</v>
+        <v>105825</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>135354408</v>
       </c>
       <c r="B367" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>135357014</v>
       </c>
       <c r="B368" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>135350632</v>
       </c>
       <c r="B369" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>135350608</v>
       </c>
       <c r="B370" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Elin Kannerby, Marie Persson, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
@@ -43656,7 +43656,7 @@
         <v>135380604</v>
       </c>
       <c r="B371" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>135350612</v>
       </c>
       <c r="B372" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>135361453</v>
       </c>
       <c r="B373" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>135363070</v>
       </c>
       <c r="B374" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>135380603</v>
       </c>
       <c r="B375" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>135350613</v>
       </c>
       <c r="B376" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>135354304</v>
       </c>
       <c r="B377" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>135361454</v>
       </c>
       <c r="B378" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>135350604</v>
       </c>
       <c r="B379" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>135351906</v>
       </c>
       <c r="B380" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>135351907</v>
       </c>
       <c r="B381" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>135354303</v>
       </c>
       <c r="B382" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -45058,7 +45058,7 @@
         <v>135350607</v>
       </c>
       <c r="B383" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
@@ -45174,7 +45174,7 @@
         <v>135350745</v>
       </c>
       <c r="B384" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>135357004</v>
       </c>
       <c r="B385" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>135357726</v>
       </c>
       <c r="B386" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>135351909</v>
       </c>
       <c r="B387" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>135357006</v>
       </c>
       <c r="B388" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>135350609</v>
       </c>
       <c r="B389" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>135350743</v>
       </c>
       <c r="B390" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>135351905</v>
       </c>
       <c r="B391" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>135350611</v>
       </c>
       <c r="B392" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>135350746</v>
       </c>
       <c r="B393" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>135357725</v>
       </c>
       <c r="B394" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>135357432</v>
       </c>
       <c r="B395" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>135357005</v>
       </c>
       <c r="B396" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>135350610</v>
       </c>
       <c r="B397" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>135380601</v>
       </c>
       <c r="B398" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>135350655</v>
       </c>
       <c r="B399" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>135357454</v>
       </c>
       <c r="B400" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>135350666</v>
       </c>
       <c r="B401" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>135380602</v>
       </c>
       <c r="B402" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>135350644</v>
       </c>
       <c r="B403" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>135350649</v>
       </c>
       <c r="B404" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>135350658</v>
       </c>
       <c r="B405" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>135350665</v>
       </c>
       <c r="B406" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>135350758</v>
       </c>
       <c r="B407" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>135350760</v>
       </c>
       <c r="B408" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>135354420</v>
       </c>
       <c r="B409" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>135357478</v>
       </c>
       <c r="B410" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>135357482</v>
       </c>
       <c r="B411" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>135361459</v>
       </c>
       <c r="B412" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -48538,7 +48538,7 @@
         <v>135350653</v>
       </c>
       <c r="B413" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>135351898</v>
       </c>
       <c r="B414" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>135351904</v>
       </c>
       <c r="B415" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>135351922</v>
       </c>
       <c r="B416" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>135357002</v>
       </c>
       <c r="B417" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>135357476</v>
       </c>
       <c r="B418" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>135350651</v>
       </c>
       <c r="B419" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>135350659</v>
       </c>
       <c r="B420" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>135350663</v>
       </c>
       <c r="B421" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>135350672</v>
       </c>
       <c r="B422" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>135350757</v>
       </c>
       <c r="B423" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>135356998</v>
       </c>
       <c r="B424" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>135357474</v>
       </c>
       <c r="B425" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>135350643</v>
       </c>
       <c r="B426" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>135350646</v>
       </c>
       <c r="B427" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>135350650</v>
       </c>
       <c r="B428" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>135351926</v>
       </c>
       <c r="B429" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>135354300</v>
       </c>
       <c r="B430" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>135357064</v>
       </c>
       <c r="B431" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>135357473</v>
       </c>
       <c r="B432" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>135357480</v>
       </c>
       <c r="B433" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>135350654</v>
       </c>
       <c r="B434" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>135350657</v>
       </c>
       <c r="B435" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>135356995</v>
       </c>
       <c r="B436" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>135354312</v>
       </c>
       <c r="B437" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>135361460</v>
       </c>
       <c r="B438" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>135350647</v>
       </c>
       <c r="B439" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>135363069</v>
       </c>
       <c r="B440" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -51793,7 +51793,7 @@
         <v>135350669</v>
       </c>
       <c r="B441" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
       </c>
       <c r="AX441" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY441" t="inlineStr">
@@ -51909,7 +51909,7 @@
         <v>135356997</v>
       </c>
       <c r="B442" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>135350645</v>
       </c>
       <c r="B443" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>135350648</v>
       </c>
       <c r="B444" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>135350759</v>
       </c>
       <c r="B445" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>135350600</v>
       </c>
       <c r="B446" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>135361462</v>
       </c>
       <c r="B447" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>135351925</v>
       </c>
       <c r="B448" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>135350638</v>
       </c>
       <c r="B449" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
@@ -52837,7 +52837,7 @@
         <v>135350642</v>
       </c>
       <c r="B450" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>135350656</v>
       </c>
       <c r="B451" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>135350664</v>
       </c>
       <c r="B452" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -53185,7 +53185,7 @@
         <v>135351901</v>
       </c>
       <c r="B453" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>135351902</v>
       </c>
       <c r="B454" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
         <v>135351903</v>
       </c>
       <c r="B455" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -53533,7 +53533,7 @@
         <v>135351921</v>
       </c>
       <c r="B456" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>135354393</v>
       </c>
       <c r="B457" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>135356996</v>
       </c>
       <c r="B458" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>135357000</v>
       </c>
       <c r="B459" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -53997,7 +53997,7 @@
         <v>135357061</v>
       </c>
       <c r="B460" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -54113,7 +54113,7 @@
         <v>135357062</v>
       </c>
       <c r="B461" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -54229,7 +54229,7 @@
         <v>135361450</v>
       </c>
       <c r="B462" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>135361458</v>
       </c>
       <c r="B463" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -54461,7 +54461,7 @@
         <v>135354311</v>
       </c>
       <c r="B464" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>135357060</v>
       </c>
       <c r="B465" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>135350652</v>
       </c>
       <c r="B466" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>135350671</v>
       </c>
       <c r="B467" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -54925,7 +54925,7 @@
         <v>135361452</v>
       </c>
       <c r="B468" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -55046,7 +55046,7 @@
         <v>135363076</v>
       </c>
       <c r="B469" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>135350606</v>
       </c>
       <c r="B470" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>135361461</v>
       </c>
       <c r="B471" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -55399,7 +55399,7 @@
         <v>135350598</v>
       </c>
       <c r="B472" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -55515,7 +55515,7 @@
         <v>135354314</v>
       </c>
       <c r="B473" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -55631,7 +55631,7 @@
         <v>135350599</v>
       </c>
       <c r="B474" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>135350667</v>
       </c>
       <c r="B475" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -55873,7 +55873,7 @@
         <v>135350670</v>
       </c>
       <c r="B476" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>135350744</v>
       </c>
       <c r="B477" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -56115,7 +56115,7 @@
         <v>135357063</v>
       </c>
       <c r="B478" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>135357477</v>
       </c>
       <c r="B479" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>135357483</v>
       </c>
       <c r="B480" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>135363075</v>
       </c>
       <c r="B481" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>135350635</v>
       </c>
       <c r="B482" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -56743,7 +56743,7 @@
         <v>135363077</v>
       </c>
       <c r="B483" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -56859,7 +56859,7 @@
         <v>135354302</v>
       </c>
       <c r="B484" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>135354390</v>
       </c>
       <c r="B485" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -57091,7 +57091,7 @@
         <v>135354391</v>
       </c>
       <c r="B486" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -57207,7 +57207,7 @@
         <v>135350637</v>
       </c>
       <c r="B487" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>135354389</v>
       </c>
       <c r="B488" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>135357431</v>
       </c>
       <c r="B489" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -57555,7 +57555,7 @@
         <v>135351924</v>
       </c>
       <c r="B490" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>135357001</v>
       </c>
       <c r="B491" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>135361463</v>
       </c>
       <c r="B492" t="n">
-        <v>87161</v>
+        <v>87201</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>135350605</v>
       </c>
       <c r="B493" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>135350641</v>
       </c>
       <c r="B494" t="n">
-        <v>80390</v>
+        <v>80428</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -58135,7 +58135,7 @@
         <v>135351935</v>
       </c>
       <c r="B495" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>135350728</v>
       </c>
       <c r="B496" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -58367,7 +58367,7 @@
         <v>135354377</v>
       </c>
       <c r="B497" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -58483,7 +58483,7 @@
         <v>135354423</v>
       </c>
       <c r="B498" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -58599,7 +58599,7 @@
         <v>135361466</v>
       </c>
       <c r="B499" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -58715,7 +58715,7 @@
         <v>135356982</v>
       </c>
       <c r="B500" t="n">
-        <v>83353</v>
+        <v>83393</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -58837,7 +58837,7 @@
         <v>135356988</v>
       </c>
       <c r="B501" t="n">
-        <v>83353</v>
+        <v>83393</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -58954,7 +58954,7 @@
         <v>135350579</v>
       </c>
       <c r="B502" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -59070,7 +59070,7 @@
         <v>135350596</v>
       </c>
       <c r="B503" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -59167,7 +59167,7 @@
       </c>
       <c r="AX503" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY503" t="inlineStr">
@@ -59186,7 +59186,7 @@
         <v>135350679</v>
       </c>
       <c r="B504" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -59302,7 +59302,7 @@
         <v>135356980</v>
       </c>
       <c r="B505" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -59418,7 +59418,7 @@
         <v>135357075</v>
       </c>
       <c r="B506" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>135380600</v>
       </c>
       <c r="B507" t="n">
-        <v>83349</v>
+        <v>83389</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>135361449</v>
       </c>
       <c r="B508" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -59766,7 +59766,7 @@
         <v>135350594</v>
       </c>
       <c r="B509" t="n">
-        <v>79442</v>
+        <v>79480</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>135351897</v>
       </c>
       <c r="B510" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -60003,7 +60003,7 @@
         <v>135351929</v>
       </c>
       <c r="B511" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>135354318</v>
       </c>
       <c r="B512" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -60235,7 +60235,7 @@
         <v>135357068</v>
       </c>
       <c r="B513" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -60351,7 +60351,7 @@
         <v>135350575</v>
       </c>
       <c r="B514" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -60467,7 +60467,7 @@
         <v>135350592</v>
       </c>
       <c r="B515" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>135350677</v>
       </c>
       <c r="B516" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -60699,7 +60699,7 @@
         <v>135351934</v>
       </c>
       <c r="B517" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>135380595</v>
       </c>
       <c r="B518" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>135361446</v>
       </c>
       <c r="B519" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -61052,7 +61052,7 @@
         <v>135361447</v>
       </c>
       <c r="B520" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>135350581</v>
       </c>
       <c r="B521" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -61289,7 +61289,7 @@
         <v>135350674</v>
       </c>
       <c r="B522" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -61405,7 +61405,7 @@
         <v>135350740</v>
       </c>
       <c r="B523" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>135350763</v>
       </c>
       <c r="B524" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -61637,7 +61637,7 @@
         <v>135354382</v>
       </c>
       <c r="B525" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>135356975</v>
       </c>
       <c r="B526" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -61869,7 +61869,7 @@
         <v>135356977</v>
       </c>
       <c r="B527" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -61985,7 +61985,7 @@
         <v>135357066</v>
       </c>
       <c r="B528" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -62101,7 +62101,7 @@
         <v>135357076</v>
       </c>
       <c r="B529" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -62217,7 +62217,7 @@
         <v>135357445</v>
       </c>
       <c r="B530" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -62333,7 +62333,7 @@
         <v>135361445</v>
       </c>
       <c r="B531" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>135350730</v>
       </c>
       <c r="B532" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -62570,7 +62570,7 @@
         <v>135354295</v>
       </c>
       <c r="B533" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>135354297</v>
       </c>
       <c r="B534" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>135354322</v>
       </c>
       <c r="B535" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -62918,7 +62918,7 @@
         <v>135354383</v>
       </c>
       <c r="B536" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>135356976</v>
       </c>
       <c r="B537" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -63150,7 +63150,7 @@
         <v>135356983</v>
       </c>
       <c r="B538" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>135357441</v>
       </c>
       <c r="B539" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -63382,7 +63382,7 @@
         <v>135350675</v>
       </c>
       <c r="B540" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>135356985</v>
       </c>
       <c r="B541" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -63614,7 +63614,7 @@
         <v>135357073</v>
       </c>
       <c r="B542" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>135363066</v>
       </c>
       <c r="B543" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>135363078</v>
       </c>
       <c r="B544" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>135350680</v>
       </c>
       <c r="B545" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -64078,7 +64078,7 @@
         <v>135356978</v>
       </c>
       <c r="B546" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>135356987</v>
       </c>
       <c r="B547" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -64315,7 +64315,7 @@
         <v>135356989</v>
       </c>
       <c r="B548" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -64431,7 +64431,7 @@
         <v>135357452</v>
       </c>
       <c r="B549" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -64547,7 +64547,7 @@
         <v>135350673</v>
       </c>
       <c r="B550" t="n">
-        <v>92332</v>
+        <v>92374</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>135357450</v>
       </c>
       <c r="B551" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>135361448</v>
       </c>
       <c r="B552" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -64900,7 +64900,7 @@
         <v>135350590</v>
       </c>
       <c r="B553" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>135361465</v>
       </c>
       <c r="B554" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -65132,7 +65132,7 @@
         <v>135356973</v>
       </c>
       <c r="B555" t="n">
-        <v>96037</v>
+        <v>96081</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -65248,7 +65248,7 @@
         <v>135380594</v>
       </c>
       <c r="B556" t="n">
-        <v>96037</v>
+        <v>96081</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>135380599</v>
       </c>
       <c r="B557" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -65480,7 +65480,7 @@
         <v>135354296</v>
       </c>
       <c r="B558" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -65596,7 +65596,7 @@
         <v>135357067</v>
       </c>
       <c r="B559" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -65717,7 +65717,7 @@
         <v>135354381</v>
       </c>
       <c r="B560" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -65833,7 +65833,7 @@
         <v>135357072</v>
       </c>
       <c r="B561" t="n">
-        <v>91803</v>
+        <v>91843</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -65955,7 +65955,7 @@
         <v>135350569</v>
       </c>
       <c r="B562" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -66071,7 +66071,7 @@
         <v>135350570</v>
       </c>
       <c r="B563" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -66187,7 +66187,7 @@
         <v>135350588</v>
       </c>
       <c r="B564" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -66303,7 +66303,7 @@
         <v>135351882</v>
       </c>
       <c r="B565" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -66419,7 +66419,7 @@
         <v>135351891</v>
       </c>
       <c r="B566" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -66535,7 +66535,7 @@
         <v>135351896</v>
       </c>
       <c r="B567" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>135351933</v>
       </c>
       <c r="B568" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -66767,7 +66767,7 @@
         <v>135356965</v>
       </c>
       <c r="B569" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         <v>135356986</v>
       </c>
       <c r="B570" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -66999,7 +66999,7 @@
         <v>135357069</v>
       </c>
       <c r="B571" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -67115,7 +67115,7 @@
         <v>135357071</v>
       </c>
       <c r="B572" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -67231,7 +67231,7 @@
         <v>135357722</v>
       </c>
       <c r="B573" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -67351,7 +67351,7 @@
         <v>135356979</v>
       </c>
       <c r="B574" t="n">
-        <v>75340</v>
+        <v>75373</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -67467,7 +67467,7 @@
         <v>135350587</v>
       </c>
       <c r="B575" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -67564,7 +67564,7 @@
       </c>
       <c r="AX575" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY575" t="inlineStr">
@@ -67583,7 +67583,7 @@
         <v>135356993</v>
       </c>
       <c r="B576" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -67699,7 +67699,7 @@
         <v>135357451</v>
       </c>
       <c r="B577" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -67815,7 +67815,7 @@
         <v>135350572</v>
       </c>
       <c r="B578" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -67931,7 +67931,7 @@
         <v>135350580</v>
       </c>
       <c r="B579" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -68047,7 +68047,7 @@
         <v>135351877</v>
       </c>
       <c r="B580" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -68163,7 +68163,7 @@
         <v>135354294</v>
       </c>
       <c r="B581" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -68279,7 +68279,7 @@
         <v>135354298</v>
       </c>
       <c r="B582" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -68395,7 +68395,7 @@
         <v>135356964</v>
       </c>
       <c r="B583" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -68511,7 +68511,7 @@
         <v>135356969</v>
       </c>
       <c r="B584" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -68627,7 +68627,7 @@
         <v>135357070</v>
       </c>
       <c r="B585" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -68743,7 +68743,7 @@
         <v>135357077</v>
       </c>
       <c r="B586" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -68859,7 +68859,7 @@
         <v>135357444</v>
       </c>
       <c r="B587" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -68975,7 +68975,7 @@
         <v>135357486</v>
       </c>
       <c r="B588" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -69091,7 +69091,7 @@
         <v>135357447</v>
       </c>
       <c r="B589" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -69212,7 +69212,7 @@
         <v>135361464</v>
       </c>
       <c r="B590" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -69328,7 +69328,7 @@
         <v>135350593</v>
       </c>
       <c r="B591" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -69444,7 +69444,7 @@
         <v>135356991</v>
       </c>
       <c r="B592" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -69560,7 +69560,7 @@
         <v>135357721</v>
       </c>
       <c r="B593" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -69676,7 +69676,7 @@
         <v>135350576</v>
       </c>
       <c r="B594" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -69778,7 +69778,7 @@
       </c>
       <c r="AX594" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY594" t="inlineStr">
@@ -69797,7 +69797,7 @@
         <v>135350583</v>
       </c>
       <c r="B595" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -69918,7 +69918,7 @@
         <v>135350764</v>
       </c>
       <c r="B596" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -70039,7 +70039,7 @@
         <v>135354320</v>
       </c>
       <c r="B597" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -70160,7 +70160,7 @@
         <v>135357488</v>
       </c>
       <c r="B598" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -70289,7 +70289,7 @@
         <v>135363067</v>
       </c>
       <c r="B599" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -70415,7 +70415,7 @@
         <v>135350578</v>
       </c>
       <c r="B600" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -70531,7 +70531,7 @@
         <v>135354424</v>
       </c>
       <c r="B601" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -70647,7 +70647,7 @@
         <v>135356970</v>
       </c>
       <c r="B602" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -70763,7 +70763,7 @@
         <v>135357424</v>
       </c>
       <c r="B603" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -70879,7 +70879,7 @@
         <v>135354385</v>
       </c>
       <c r="B604" t="n">
-        <v>92661</v>
+        <v>92703</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -70995,7 +70995,7 @@
         <v>135363079</v>
       </c>
       <c r="B605" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -71111,7 +71111,7 @@
         <v>135354316</v>
       </c>
       <c r="B606" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -71227,7 +71227,7 @@
         <v>135356990</v>
       </c>
       <c r="B607" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -71343,7 +71343,7 @@
         <v>135357428</v>
       </c>
       <c r="B608" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -71459,7 +71459,7 @@
         <v>135357723</v>
       </c>
       <c r="B609" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>135363068</v>
       </c>
       <c r="B610" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -71691,7 +71691,7 @@
         <v>135357413</v>
       </c>
       <c r="B611" t="n">
-        <v>99094</v>
+        <v>99141</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -71807,7 +71807,7 @@
         <v>135351879</v>
       </c>
       <c r="B612" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -71923,7 +71923,7 @@
         <v>135350571</v>
       </c>
       <c r="B613" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>135357421</v>
       </c>
       <c r="B614" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -72155,7 +72155,7 @@
         <v>135356968</v>
       </c>
       <c r="B615" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -72271,7 +72271,7 @@
         <v>135357440</v>
       </c>
       <c r="B616" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -72387,7 +72387,7 @@
         <v>135354425</v>
       </c>
       <c r="B617" t="n">
-        <v>102541</v>
+        <v>102591</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -72504,7 +72504,7 @@
         <v>135351883</v>
       </c>
       <c r="B618" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -72620,7 +72620,7 @@
         <v>135351890</v>
       </c>
       <c r="B619" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -72736,7 +72736,7 @@
         <v>135351895</v>
       </c>
       <c r="B620" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -72852,7 +72852,7 @@
         <v>135357411</v>
       </c>
       <c r="B621" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -72968,7 +72968,7 @@
         <v>135357417</v>
       </c>
       <c r="B622" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -73084,7 +73084,7 @@
         <v>135357426</v>
       </c>
       <c r="B623" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -73200,7 +73200,7 @@
         <v>135357429</v>
       </c>
       <c r="B624" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -73316,7 +73316,7 @@
         <v>135351878</v>
       </c>
       <c r="B625" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -73432,7 +73432,7 @@
         <v>135351888</v>
       </c>
       <c r="B626" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -73548,7 +73548,7 @@
         <v>135356971</v>
       </c>
       <c r="B627" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -73664,7 +73664,7 @@
         <v>135357078</v>
       </c>
       <c r="B628" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -73780,7 +73780,7 @@
         <v>135357410</v>
       </c>
       <c r="B629" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -73896,7 +73896,7 @@
         <v>135357422</v>
       </c>
       <c r="B630" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -74012,7 +74012,7 @@
         <v>135357415</v>
       </c>
       <c r="B631" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -74128,7 +74128,7 @@
         <v>135357416</v>
       </c>
       <c r="B632" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -74244,7 +74244,7 @@
         <v>135357427</v>
       </c>
       <c r="B633" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -74360,7 +74360,7 @@
         <v>135380596</v>
       </c>
       <c r="B634" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -74476,7 +74476,7 @@
         <v>135357412</v>
       </c>
       <c r="B635" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -74592,7 +74592,7 @@
         <v>135351880</v>
       </c>
       <c r="B636" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -74708,7 +74708,7 @@
         <v>135357418</v>
       </c>
       <c r="B637" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -74824,7 +74824,7 @@
         <v>135357423</v>
       </c>
       <c r="B638" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -74940,7 +74940,7 @@
         <v>135356967</v>
       </c>
       <c r="B639" t="n">
-        <v>105771</v>
+        <v>105825</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -75052,7 +75052,7 @@
         <v>135351885</v>
       </c>
       <c r="B640" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -75168,7 +75168,7 @@
         <v>135356966</v>
       </c>
       <c r="B641" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -75284,7 +75284,7 @@
         <v>135350568</v>
       </c>
       <c r="B642" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -75400,7 +75400,7 @@
         <v>135350582</v>
       </c>
       <c r="B643" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -57903,7 +57903,7 @@
         <v>135350605</v>
       </c>
       <c r="B493" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135382760</v>
       </c>
       <c r="B2" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>135384331</v>
       </c>
       <c r="B3" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>135382413</v>
       </c>
       <c r="B4" t="n">
-        <v>83383</v>
+        <v>83410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>135384288</v>
       </c>
       <c r="B5" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135379254</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135379255</v>
       </c>
       <c r="B7" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135382735</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>135382750</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>135382772</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>135383974</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>135384144</v>
       </c>
       <c r="B12" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>135384270</v>
       </c>
       <c r="B13" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>135384286</v>
       </c>
       <c r="B14" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>135385128</v>
       </c>
       <c r="B15" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>135357040</v>
       </c>
       <c r="B16" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>135382042</v>
       </c>
       <c r="B17" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135383991</v>
       </c>
       <c r="B18" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>135379238</v>
       </c>
       <c r="B19" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135379243</v>
       </c>
       <c r="B20" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135379248</v>
       </c>
       <c r="B21" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135379249</v>
       </c>
       <c r="B22" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135379252</v>
       </c>
       <c r="B23" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>135382411</v>
       </c>
       <c r="B24" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>135382725</v>
       </c>
       <c r="B25" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135382733</v>
       </c>
       <c r="B26" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>135383965</v>
       </c>
       <c r="B27" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>135384150</v>
       </c>
       <c r="B28" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>135385952</v>
       </c>
       <c r="B29" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>135385965</v>
       </c>
       <c r="B30" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>135385966</v>
       </c>
       <c r="B31" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>135385973</v>
       </c>
       <c r="B32" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>135379246</v>
       </c>
       <c r="B33" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>135382064</v>
       </c>
       <c r="B34" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135382736</v>
       </c>
       <c r="B35" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>135383967</v>
       </c>
       <c r="B36" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>135384131</v>
       </c>
       <c r="B37" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>135384136</v>
       </c>
       <c r="B38" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>135384146</v>
       </c>
       <c r="B39" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>135384153</v>
       </c>
       <c r="B40" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>135384272</v>
       </c>
       <c r="B41" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>135385129</v>
       </c>
       <c r="B42" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>135386007</v>
       </c>
       <c r="B43" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>135379250</v>
       </c>
       <c r="B44" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>135382403</v>
       </c>
       <c r="B45" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>135383973</v>
       </c>
       <c r="B46" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>135385127</v>
       </c>
       <c r="B47" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>135383992</v>
       </c>
       <c r="B48" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>135382399</v>
       </c>
       <c r="B49" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>135382407</v>
       </c>
       <c r="B50" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>135379247</v>
       </c>
       <c r="B51" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>135357049</v>
       </c>
       <c r="B52" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>135357050</v>
       </c>
       <c r="B53" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>135384148</v>
       </c>
       <c r="B54" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>135385971</v>
       </c>
       <c r="B55" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135387640</v>
       </c>
       <c r="B56" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>135382727</v>
       </c>
       <c r="B57" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>135382741</v>
       </c>
       <c r="B58" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>135382757</v>
       </c>
       <c r="B59" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>135385962</v>
       </c>
       <c r="B60" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>135382999</v>
       </c>
       <c r="B61" t="n">
-        <v>92368</v>
+        <v>92395</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>135382745</v>
       </c>
       <c r="B62" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>135380608</v>
       </c>
       <c r="B63" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>135382742</v>
       </c>
       <c r="B64" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135382748</v>
       </c>
       <c r="B65" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>135382753</v>
       </c>
       <c r="B66" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>135382767</v>
       </c>
       <c r="B67" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>135382773</v>
       </c>
       <c r="B68" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>135382778</v>
       </c>
       <c r="B69" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>135383981</v>
       </c>
       <c r="B70" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>135383962</v>
       </c>
       <c r="B71" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>135357046</v>
       </c>
       <c r="B72" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>135382034</v>
       </c>
       <c r="B73" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>135382036</v>
       </c>
       <c r="B74" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>135382400</v>
       </c>
       <c r="B75" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>135382417</v>
       </c>
       <c r="B76" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>135382419</v>
       </c>
       <c r="B77" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>135382466</v>
       </c>
       <c r="B78" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>135382731</v>
       </c>
       <c r="B79" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>135384252</v>
       </c>
       <c r="B80" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>135384261</v>
       </c>
       <c r="B81" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>135384285</v>
       </c>
       <c r="B82" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>135385123</v>
       </c>
       <c r="B83" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>135385124</v>
       </c>
       <c r="B84" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>135382396</v>
       </c>
       <c r="B85" t="n">
-        <v>75373</v>
+        <v>75400</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>135385120</v>
       </c>
       <c r="B86" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>135382391</v>
       </c>
       <c r="B87" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>135385941</v>
       </c>
       <c r="B88" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>135382746</v>
       </c>
       <c r="B89" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>135382749</v>
       </c>
       <c r="B90" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>135382463</v>
       </c>
       <c r="B91" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>135382752</v>
       </c>
       <c r="B92" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>135382774</v>
       </c>
       <c r="B93" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>135382751</v>
       </c>
       <c r="B94" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>135382775</v>
       </c>
       <c r="B95" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>135382039</v>
       </c>
       <c r="B96" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>135382040</v>
       </c>
       <c r="B97" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>135382747</v>
       </c>
       <c r="B98" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11951,7 +11951,7 @@
         <v>135384138</v>
       </c>
       <c r="B99" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>135383994</v>
       </c>
       <c r="B105" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>135384128</v>
       </c>
       <c r="B106" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>135385940</v>
       </c>
       <c r="B107" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>135385968</v>
       </c>
       <c r="B108" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>135385976</v>
       </c>
       <c r="B109" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>135385960</v>
       </c>
       <c r="B110" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>135385977</v>
       </c>
       <c r="B111" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>135382393</v>
       </c>
       <c r="B112" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>135357039</v>
       </c>
       <c r="B113" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>135385959</v>
       </c>
       <c r="B114" t="n">
-        <v>110206</v>
+        <v>110233</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>135385969</v>
       </c>
       <c r="B115" t="n">
-        <v>110206</v>
+        <v>110233</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>135358340</v>
       </c>
       <c r="B116" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>135382723</v>
       </c>
       <c r="B117" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>135382739</v>
       </c>
       <c r="B118" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>135383976</v>
       </c>
       <c r="B119" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>135385944</v>
       </c>
       <c r="B120" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>135382410</v>
       </c>
       <c r="B121" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>135382412</v>
       </c>
       <c r="B122" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>135384266</v>
       </c>
       <c r="B123" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>135384268</v>
       </c>
       <c r="B124" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>135384279</v>
       </c>
       <c r="B125" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>135384281</v>
       </c>
       <c r="B126" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>135384330</v>
       </c>
       <c r="B127" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>135385947</v>
       </c>
       <c r="B128" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>135385957</v>
       </c>
       <c r="B129" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>135382032</v>
       </c>
       <c r="B130" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>135384249</v>
       </c>
       <c r="B131" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135384258</v>
       </c>
       <c r="B132" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>135357042</v>
       </c>
       <c r="B133" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>135357048</v>
       </c>
       <c r="B134" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>135379237</v>
       </c>
       <c r="B135" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>135382041</v>
       </c>
       <c r="B136" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>135382721</v>
       </c>
       <c r="B137" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>135382730</v>
       </c>
       <c r="B138" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>135382770</v>
       </c>
       <c r="B139" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>135384251</v>
       </c>
       <c r="B140" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>135384256</v>
       </c>
       <c r="B141" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>135384278</v>
       </c>
       <c r="B142" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>135384291</v>
       </c>
       <c r="B143" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>135357041</v>
       </c>
       <c r="B144" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>135382744</v>
       </c>
       <c r="B145" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>135382754</v>
       </c>
       <c r="B146" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>135385964</v>
       </c>
       <c r="B147" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>135385967</v>
       </c>
       <c r="B148" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>135386008</v>
       </c>
       <c r="B149" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>135383990</v>
       </c>
       <c r="B150" t="n">
-        <v>99252</v>
+        <v>99279</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>135385954</v>
       </c>
       <c r="B151" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>135385951</v>
       </c>
       <c r="B152" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>135385942</v>
       </c>
       <c r="B153" t="n">
-        <v>99551</v>
+        <v>99578</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>135382724</v>
       </c>
       <c r="B154" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>135383978</v>
       </c>
       <c r="B155" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>135385955</v>
       </c>
       <c r="B156" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>135385946</v>
       </c>
       <c r="B157" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>135382758</v>
       </c>
       <c r="B158" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>135385950</v>
       </c>
       <c r="B159" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>135385958</v>
       </c>
       <c r="B160" t="n">
-        <v>101988</v>
+        <v>102015</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>135389393</v>
       </c>
       <c r="B161" t="n">
-        <v>105825</v>
+        <v>105852</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>135357037</v>
       </c>
       <c r="B162" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>135382722</v>
       </c>
       <c r="B163" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>135382737</v>
       </c>
       <c r="B164" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>135382743</v>
       </c>
       <c r="B165" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>135382755</v>
       </c>
       <c r="B166" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>135382759</v>
       </c>
       <c r="B167" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>135382768</v>
       </c>
       <c r="B168" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>135382777</v>
       </c>
       <c r="B169" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>135383977</v>
       </c>
       <c r="B170" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>135383986</v>
       </c>
       <c r="B171" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>135383995</v>
       </c>
       <c r="B172" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>135384133</v>
       </c>
       <c r="B173" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>135382053</v>
       </c>
       <c r="B174" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>135383947</v>
       </c>
       <c r="B175" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20919,7 +20919,7 @@
         <v>135382043</v>
       </c>
       <c r="B176" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>135357031</v>
       </c>
       <c r="B177" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>135357033</v>
       </c>
       <c r="B178" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>135357035</v>
       </c>
       <c r="B179" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>135379257</v>
       </c>
       <c r="B180" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>135382440</v>
       </c>
       <c r="B181" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>135382442</v>
       </c>
       <c r="B182" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>135382445</v>
       </c>
       <c r="B183" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>135382448</v>
       </c>
       <c r="B184" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135382763</v>
       </c>
       <c r="B185" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>135383940</v>
       </c>
       <c r="B186" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>135385134</v>
       </c>
       <c r="B187" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>135385983</v>
       </c>
       <c r="B188" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>135379260</v>
       </c>
       <c r="B189" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>135382055</v>
       </c>
       <c r="B190" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>135384325</v>
       </c>
       <c r="B191" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>135382762</v>
       </c>
       <c r="B192" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>135383937</v>
       </c>
       <c r="B193" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>135385132</v>
       </c>
       <c r="B194" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>135382428</v>
       </c>
       <c r="B195" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>135384158</v>
       </c>
       <c r="B196" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>135385985</v>
       </c>
       <c r="B197" t="n">
-        <v>96469</v>
+        <v>96496</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>135386085</v>
       </c>
       <c r="B198" t="n">
-        <v>92241</v>
+        <v>92268</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>135382420</v>
       </c>
       <c r="B199" t="n">
-        <v>87665</v>
+        <v>87692</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>135385133</v>
       </c>
       <c r="B200" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23820,7 +23820,7 @@
         <v>135357030</v>
       </c>
       <c r="B201" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>135382057</v>
       </c>
       <c r="B202" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>135382438</v>
       </c>
       <c r="B203" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>135382446</v>
       </c>
       <c r="B204" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>135382765</v>
       </c>
       <c r="B205" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>135382436</v>
       </c>
       <c r="B206" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>135382434</v>
       </c>
       <c r="B207" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>135383960</v>
       </c>
       <c r="B208" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>135384155</v>
       </c>
       <c r="B209" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>135385135</v>
       </c>
       <c r="B210" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>135385979</v>
       </c>
       <c r="B211" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>135382060</v>
       </c>
       <c r="B212" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>135382062</v>
       </c>
       <c r="B213" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>135385130</v>
       </c>
       <c r="B214" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>135385980</v>
       </c>
       <c r="B215" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>135384332</v>
       </c>
       <c r="B220" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>135384318</v>
       </c>
       <c r="B221" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>135383932</v>
       </c>
       <c r="B222" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>135384295</v>
       </c>
       <c r="B223" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>135384309</v>
       </c>
       <c r="B224" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>135384311</v>
       </c>
       <c r="B225" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>135384327</v>
       </c>
       <c r="B226" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>135384312</v>
       </c>
       <c r="B227" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>135384322</v>
       </c>
       <c r="B228" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>135382050</v>
       </c>
       <c r="B229" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>135382761</v>
       </c>
       <c r="B230" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>135384302</v>
       </c>
       <c r="B231" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>135384304</v>
       </c>
       <c r="B232" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>135384323</v>
       </c>
       <c r="B233" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>135384329</v>
       </c>
       <c r="B234" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>135383955</v>
       </c>
       <c r="B235" t="n">
-        <v>99252</v>
+        <v>99279</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>135383961</v>
       </c>
       <c r="B236" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>135383936</v>
       </c>
       <c r="B237" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>135383957</v>
       </c>
       <c r="B238" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>135382764</v>
       </c>
       <c r="B239" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>135383934</v>
       </c>
       <c r="B240" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>135383942</v>
       </c>
       <c r="B241" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>135383954</v>
       </c>
       <c r="B242" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>135383958</v>
       </c>
       <c r="B243" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>135383969</v>
       </c>
       <c r="B244" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>135380606</v>
       </c>
       <c r="B245" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>135357457</v>
       </c>
       <c r="B246" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>135354306</v>
       </c>
       <c r="B247" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>135351913</v>
       </c>
       <c r="B248" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>135386003</v>
       </c>
       <c r="B249" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>135350748</v>
       </c>
       <c r="B250" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>135354307</v>
       </c>
       <c r="B251" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>135383923</v>
       </c>
       <c r="B252" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>135357008</v>
       </c>
       <c r="B253" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>135383921</v>
       </c>
       <c r="B254" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>135383924</v>
       </c>
       <c r="B255" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>135383916</v>
       </c>
       <c r="B256" t="n">
-        <v>93131</v>
+        <v>93158</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30370,7 +30370,7 @@
         <v>135353579</v>
       </c>
       <c r="B257" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>135357007</v>
       </c>
       <c r="B258" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>135357057</v>
       </c>
       <c r="B259" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>135357059</v>
       </c>
       <c r="B260" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>135380605</v>
       </c>
       <c r="B261" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>135350615</v>
       </c>
       <c r="B262" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31066,7 +31066,7 @@
         <v>135351914</v>
       </c>
       <c r="B263" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>135354305</v>
       </c>
       <c r="B264" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>135382457</v>
       </c>
       <c r="B265" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>135382453</v>
       </c>
       <c r="B266" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>135382455</v>
       </c>
       <c r="B267" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>135385141</v>
       </c>
       <c r="B268" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>135386004</v>
       </c>
       <c r="B269" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>135357458</v>
       </c>
       <c r="B270" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>135363071</v>
       </c>
       <c r="B271" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32133,7 +32133,7 @@
         <v>135382456</v>
       </c>
       <c r="B272" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>135383919</v>
       </c>
       <c r="B273" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>135386001</v>
       </c>
       <c r="B274" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>135386002</v>
       </c>
       <c r="B275" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135382462</v>
       </c>
       <c r="B280" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>135379281</v>
       </c>
       <c r="B281" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>135351911</v>
       </c>
       <c r="B282" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>135383925</v>
       </c>
       <c r="B283" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>135353582</v>
       </c>
       <c r="B284" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>135358339</v>
       </c>
       <c r="B285" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>135379275</v>
       </c>
       <c r="B286" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>135353577</v>
       </c>
       <c r="B287" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>135353581</v>
       </c>
       <c r="B288" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>135357058</v>
       </c>
       <c r="B289" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>135383915</v>
       </c>
       <c r="B290" t="n">
-        <v>99252</v>
+        <v>99279</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>135353580</v>
       </c>
       <c r="B291" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>135358334</v>
       </c>
       <c r="B292" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>135358336</v>
       </c>
       <c r="B293" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>135358338</v>
       </c>
       <c r="B294" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>135350617</v>
       </c>
       <c r="B295" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>135357009</v>
       </c>
       <c r="B296" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>135361457</v>
       </c>
       <c r="B297" t="n">
-        <v>92635</v>
+        <v>92662</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>135350633</v>
       </c>
       <c r="B298" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>135351916</v>
       </c>
       <c r="B299" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>135357469</v>
       </c>
       <c r="B300" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>135357024</v>
       </c>
       <c r="B301" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>135350626</v>
       </c>
       <c r="B302" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>135357468</v>
       </c>
       <c r="B303" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>135350629</v>
       </c>
       <c r="B304" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>135350753</v>
       </c>
       <c r="B305" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>135379266</v>
       </c>
       <c r="B306" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>135379272</v>
       </c>
       <c r="B307" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>135385139</v>
       </c>
       <c r="B308" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>135354411</v>
       </c>
       <c r="B309" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>135363074</v>
       </c>
       <c r="B310" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>135350627</v>
       </c>
       <c r="B311" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>135361715</v>
       </c>
       <c r="B312" t="n">
-        <v>92368</v>
+        <v>92395</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>135350628</v>
       </c>
       <c r="B313" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>135350755</v>
       </c>
       <c r="B314" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>135351919</v>
       </c>
       <c r="B315" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>135357023</v>
       </c>
       <c r="B316" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>135382450</v>
       </c>
       <c r="B317" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>135385136</v>
       </c>
       <c r="B318" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>135350625</v>
       </c>
       <c r="B319" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>135351917</v>
       </c>
       <c r="B320" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
         <v>135350623</v>
       </c>
       <c r="B321" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>135357459</v>
       </c>
       <c r="B322" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>135357463</v>
       </c>
       <c r="B323" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>135357467</v>
       </c>
       <c r="B324" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>135379269</v>
       </c>
       <c r="B325" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>135383930</v>
       </c>
       <c r="B326" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>135385988</v>
       </c>
       <c r="B327" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>135385990</v>
       </c>
       <c r="B328" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>135385992</v>
       </c>
       <c r="B329" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>135385993</v>
       </c>
       <c r="B330" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>135385996</v>
       </c>
       <c r="B331" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>135350624</v>
       </c>
       <c r="B332" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>135354309</v>
       </c>
       <c r="B333" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>135363072</v>
       </c>
       <c r="B334" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>135383929</v>
       </c>
       <c r="B335" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>135385987</v>
       </c>
       <c r="B336" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         <v>135385989</v>
       </c>
       <c r="B337" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>135385997</v>
       </c>
       <c r="B338" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>135385999</v>
       </c>
       <c r="B339" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>135350620</v>
       </c>
       <c r="B340" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
         <v>135350622</v>
       </c>
       <c r="B341" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>135385986</v>
       </c>
       <c r="B342" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>135385991</v>
       </c>
       <c r="B343" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>135385994</v>
       </c>
       <c r="B344" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>135385995</v>
       </c>
       <c r="B345" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>135385998</v>
       </c>
       <c r="B346" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>135357021</v>
       </c>
       <c r="B354" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>135357016</v>
       </c>
       <c r="B355" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>135383931</v>
       </c>
       <c r="B356" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>135357437</v>
       </c>
       <c r="B357" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>135357465</v>
       </c>
       <c r="B358" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>135382449</v>
       </c>
       <c r="B359" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>135357026</v>
       </c>
       <c r="B360" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>135357013</v>
       </c>
       <c r="B361" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>135357015</v>
       </c>
       <c r="B362" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>135357435</v>
       </c>
       <c r="B363" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>135379271</v>
       </c>
       <c r="B364" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>135357019</v>
       </c>
       <c r="B365" t="n">
-        <v>105825</v>
+        <v>105852</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>135357028</v>
       </c>
       <c r="B366" t="n">
-        <v>105825</v>
+        <v>105852</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>135354408</v>
       </c>
       <c r="B367" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>135357014</v>
       </c>
       <c r="B368" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>135350632</v>
       </c>
       <c r="B369" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>135350608</v>
       </c>
       <c r="B370" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>135380604</v>
       </c>
       <c r="B371" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>135350612</v>
       </c>
       <c r="B372" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>135361453</v>
       </c>
       <c r="B373" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>135363070</v>
       </c>
       <c r="B374" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>135380603</v>
       </c>
       <c r="B375" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>135350613</v>
       </c>
       <c r="B376" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>135354304</v>
       </c>
       <c r="B377" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>135361454</v>
       </c>
       <c r="B378" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>135350604</v>
       </c>
       <c r="B379" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>135351906</v>
       </c>
       <c r="B380" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>135351907</v>
       </c>
       <c r="B381" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -44942,7 +44942,7 @@
         <v>135354303</v>
       </c>
       <c r="B382" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -45058,7 +45058,7 @@
         <v>135350607</v>
       </c>
       <c r="B383" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>135350745</v>
       </c>
       <c r="B384" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>135357004</v>
       </c>
       <c r="B385" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>135357726</v>
       </c>
       <c r="B386" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>135351909</v>
       </c>
       <c r="B387" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>135357006</v>
       </c>
       <c r="B388" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>135350609</v>
       </c>
       <c r="B389" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>135350743</v>
       </c>
       <c r="B390" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>135351905</v>
       </c>
       <c r="B391" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>135350611</v>
       </c>
       <c r="B392" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>135357432</v>
       </c>
       <c r="B395" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -46571,7 +46571,7 @@
         <v>135357005</v>
       </c>
       <c r="B396" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         <v>135350610</v>
       </c>
       <c r="B397" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>135380601</v>
       </c>
       <c r="B398" t="n">
-        <v>92635</v>
+        <v>92662</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>135350655</v>
       </c>
       <c r="B399" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>135357454</v>
       </c>
       <c r="B400" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>135350666</v>
       </c>
       <c r="B401" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>135380602</v>
       </c>
       <c r="B402" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>135350644</v>
       </c>
       <c r="B403" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>135350649</v>
       </c>
       <c r="B404" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>135350658</v>
       </c>
       <c r="B405" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>135350665</v>
       </c>
       <c r="B406" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>135350758</v>
       </c>
       <c r="B407" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>135350760</v>
       </c>
       <c r="B408" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>135354420</v>
       </c>
       <c r="B409" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>135357478</v>
       </c>
       <c r="B410" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>135357482</v>
       </c>
       <c r="B411" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>135361459</v>
       </c>
       <c r="B412" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -48538,7 +48538,7 @@
         <v>135350653</v>
       </c>
       <c r="B413" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>135351898</v>
       </c>
       <c r="B414" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>135351904</v>
       </c>
       <c r="B415" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>135351922</v>
       </c>
       <c r="B416" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>135357002</v>
       </c>
       <c r="B417" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>135357476</v>
       </c>
       <c r="B418" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>135350651</v>
       </c>
       <c r="B419" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>135350659</v>
       </c>
       <c r="B420" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>135350663</v>
       </c>
       <c r="B421" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>135350672</v>
       </c>
       <c r="B422" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>135350757</v>
       </c>
       <c r="B423" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>135356998</v>
       </c>
       <c r="B424" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>135357474</v>
       </c>
       <c r="B425" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>135350643</v>
       </c>
       <c r="B426" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>135350646</v>
       </c>
       <c r="B427" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>135350650</v>
       </c>
       <c r="B428" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>135351926</v>
       </c>
       <c r="B429" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>135354300</v>
       </c>
       <c r="B430" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>135357064</v>
       </c>
       <c r="B431" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>135357473</v>
       </c>
       <c r="B432" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>135357480</v>
       </c>
       <c r="B433" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>135350654</v>
       </c>
       <c r="B434" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>135350657</v>
       </c>
       <c r="B435" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>135356995</v>
       </c>
       <c r="B436" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>135354312</v>
       </c>
       <c r="B437" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>135361460</v>
       </c>
       <c r="B438" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>135350647</v>
       </c>
       <c r="B439" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>135363069</v>
       </c>
       <c r="B440" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -51793,7 +51793,7 @@
         <v>135350669</v>
       </c>
       <c r="B441" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>135356997</v>
       </c>
       <c r="B442" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>135350645</v>
       </c>
       <c r="B443" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>135350648</v>
       </c>
       <c r="B444" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>135350759</v>
       </c>
       <c r="B445" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>135350600</v>
       </c>
       <c r="B446" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>135361462</v>
       </c>
       <c r="B447" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>135351925</v>
       </c>
       <c r="B448" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>135350638</v>
       </c>
       <c r="B449" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -52837,7 +52837,7 @@
         <v>135350642</v>
       </c>
       <c r="B450" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>135350656</v>
       </c>
       <c r="B451" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>135350664</v>
       </c>
       <c r="B452" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -53185,7 +53185,7 @@
         <v>135351901</v>
       </c>
       <c r="B453" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>135351902</v>
       </c>
       <c r="B454" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
         <v>135351903</v>
       </c>
       <c r="B455" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -53533,7 +53533,7 @@
         <v>135351921</v>
       </c>
       <c r="B456" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>135354393</v>
       </c>
       <c r="B457" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -53765,7 +53765,7 @@
         <v>135356996</v>
       </c>
       <c r="B458" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -53881,7 +53881,7 @@
         <v>135357000</v>
       </c>
       <c r="B459" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -53997,7 +53997,7 @@
         <v>135357061</v>
       </c>
       <c r="B460" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -54113,7 +54113,7 @@
         <v>135357062</v>
       </c>
       <c r="B461" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -54229,7 +54229,7 @@
         <v>135361450</v>
       </c>
       <c r="B462" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -54345,7 +54345,7 @@
         <v>135361458</v>
       </c>
       <c r="B463" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -54461,7 +54461,7 @@
         <v>135354311</v>
       </c>
       <c r="B464" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>135357060</v>
       </c>
       <c r="B465" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>135350652</v>
       </c>
       <c r="B466" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>135350671</v>
       </c>
       <c r="B467" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -54925,7 +54925,7 @@
         <v>135361452</v>
       </c>
       <c r="B468" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -55046,7 +55046,7 @@
         <v>135363076</v>
       </c>
       <c r="B469" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>135350606</v>
       </c>
       <c r="B470" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>135361461</v>
       </c>
       <c r="B471" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -55399,7 +55399,7 @@
         <v>135350598</v>
       </c>
       <c r="B472" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -55515,7 +55515,7 @@
         <v>135354314</v>
       </c>
       <c r="B473" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -56859,7 +56859,7 @@
         <v>135354302</v>
       </c>
       <c r="B484" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>135354390</v>
       </c>
       <c r="B485" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -57091,7 +57091,7 @@
         <v>135354391</v>
       </c>
       <c r="B486" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -57207,7 +57207,7 @@
         <v>135350637</v>
       </c>
       <c r="B487" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>135354389</v>
       </c>
       <c r="B488" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>135357431</v>
       </c>
       <c r="B489" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -57555,7 +57555,7 @@
         <v>135351924</v>
       </c>
       <c r="B490" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>135357001</v>
       </c>
       <c r="B491" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>135361463</v>
       </c>
       <c r="B492" t="n">
-        <v>87201</v>
+        <v>87228</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>135350641</v>
       </c>
       <c r="B494" t="n">
-        <v>80428</v>
+        <v>80455</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -58135,7 +58135,7 @@
         <v>135351935</v>
       </c>
       <c r="B495" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>135350728</v>
       </c>
       <c r="B496" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -58367,7 +58367,7 @@
         <v>135354377</v>
       </c>
       <c r="B497" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -58483,7 +58483,7 @@
         <v>135354423</v>
       </c>
       <c r="B498" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -58599,7 +58599,7 @@
         <v>135361466</v>
       </c>
       <c r="B499" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -58715,7 +58715,7 @@
         <v>135356982</v>
       </c>
       <c r="B500" t="n">
-        <v>83393</v>
+        <v>83420</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -58837,7 +58837,7 @@
         <v>135356988</v>
       </c>
       <c r="B501" t="n">
-        <v>83393</v>
+        <v>83420</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -58954,7 +58954,7 @@
         <v>135350579</v>
       </c>
       <c r="B502" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -59070,7 +59070,7 @@
         <v>135350596</v>
       </c>
       <c r="B503" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -59186,7 +59186,7 @@
         <v>135350679</v>
       </c>
       <c r="B504" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -59302,7 +59302,7 @@
         <v>135356980</v>
       </c>
       <c r="B505" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -59418,7 +59418,7 @@
         <v>135357075</v>
       </c>
       <c r="B506" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>135380600</v>
       </c>
       <c r="B507" t="n">
-        <v>83389</v>
+        <v>83416</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>135361449</v>
       </c>
       <c r="B508" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -59766,7 +59766,7 @@
         <v>135350594</v>
       </c>
       <c r="B509" t="n">
-        <v>79480</v>
+        <v>79507</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>135351897</v>
       </c>
       <c r="B510" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -60003,7 +60003,7 @@
         <v>135351929</v>
       </c>
       <c r="B511" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>135354318</v>
       </c>
       <c r="B512" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -60235,7 +60235,7 @@
         <v>135357068</v>
       </c>
       <c r="B513" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -60351,7 +60351,7 @@
         <v>135350575</v>
       </c>
       <c r="B514" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -60467,7 +60467,7 @@
         <v>135350592</v>
       </c>
       <c r="B515" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>135350677</v>
       </c>
       <c r="B516" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -60699,7 +60699,7 @@
         <v>135351934</v>
       </c>
       <c r="B517" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>135380595</v>
       </c>
       <c r="B518" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>135361446</v>
       </c>
       <c r="B519" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -61052,7 +61052,7 @@
         <v>135361447</v>
       </c>
       <c r="B520" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>135350581</v>
       </c>
       <c r="B521" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -61289,7 +61289,7 @@
         <v>135350674</v>
       </c>
       <c r="B522" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -61405,7 +61405,7 @@
         <v>135350740</v>
       </c>
       <c r="B523" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>135350763</v>
       </c>
       <c r="B524" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -61637,7 +61637,7 @@
         <v>135354382</v>
       </c>
       <c r="B525" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>135356975</v>
       </c>
       <c r="B526" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -61869,7 +61869,7 @@
         <v>135356977</v>
       </c>
       <c r="B527" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -61985,7 +61985,7 @@
         <v>135357066</v>
       </c>
       <c r="B528" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -62101,7 +62101,7 @@
         <v>135357076</v>
       </c>
       <c r="B529" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -62217,7 +62217,7 @@
         <v>135357445</v>
       </c>
       <c r="B530" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -62333,7 +62333,7 @@
         <v>135361445</v>
       </c>
       <c r="B531" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>135350730</v>
       </c>
       <c r="B532" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -62570,7 +62570,7 @@
         <v>135354295</v>
       </c>
       <c r="B533" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>135354297</v>
       </c>
       <c r="B534" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>135354322</v>
       </c>
       <c r="B535" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -62918,7 +62918,7 @@
         <v>135354383</v>
       </c>
       <c r="B536" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>135356976</v>
       </c>
       <c r="B537" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -63150,7 +63150,7 @@
         <v>135356983</v>
       </c>
       <c r="B538" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>135357441</v>
       </c>
       <c r="B539" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -63382,7 +63382,7 @@
         <v>135350675</v>
       </c>
       <c r="B540" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>135356985</v>
       </c>
       <c r="B541" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -63614,7 +63614,7 @@
         <v>135357073</v>
       </c>
       <c r="B542" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>135363066</v>
       </c>
       <c r="B543" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>135363078</v>
       </c>
       <c r="B544" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>135350680</v>
       </c>
       <c r="B545" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -64078,7 +64078,7 @@
         <v>135356978</v>
       </c>
       <c r="B546" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>135356987</v>
       </c>
       <c r="B547" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -64315,7 +64315,7 @@
         <v>135356989</v>
       </c>
       <c r="B548" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -64431,7 +64431,7 @@
         <v>135357452</v>
       </c>
       <c r="B549" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -64547,7 +64547,7 @@
         <v>135350673</v>
       </c>
       <c r="B550" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>135357450</v>
       </c>
       <c r="B551" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>135361448</v>
       </c>
       <c r="B552" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -64900,7 +64900,7 @@
         <v>135350590</v>
       </c>
       <c r="B553" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>135361465</v>
       </c>
       <c r="B554" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -65132,7 +65132,7 @@
         <v>135356973</v>
       </c>
       <c r="B555" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -65248,7 +65248,7 @@
         <v>135380594</v>
       </c>
       <c r="B556" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>135380599</v>
       </c>
       <c r="B557" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -65480,7 +65480,7 @@
         <v>135354296</v>
       </c>
       <c r="B558" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -65596,7 +65596,7 @@
         <v>135357067</v>
       </c>
       <c r="B559" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -65717,7 +65717,7 @@
         <v>135354381</v>
       </c>
       <c r="B560" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -65833,7 +65833,7 @@
         <v>135357072</v>
       </c>
       <c r="B561" t="n">
-        <v>91843</v>
+        <v>91870</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -65955,7 +65955,7 @@
         <v>135350569</v>
       </c>
       <c r="B562" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -66071,7 +66071,7 @@
         <v>135350570</v>
       </c>
       <c r="B563" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -66187,7 +66187,7 @@
         <v>135350588</v>
       </c>
       <c r="B564" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -66303,7 +66303,7 @@
         <v>135351882</v>
       </c>
       <c r="B565" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -66419,7 +66419,7 @@
         <v>135351891</v>
       </c>
       <c r="B566" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -66535,7 +66535,7 @@
         <v>135351896</v>
       </c>
       <c r="B567" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>135351933</v>
       </c>
       <c r="B568" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -66767,7 +66767,7 @@
         <v>135356965</v>
       </c>
       <c r="B569" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         <v>135356986</v>
       </c>
       <c r="B570" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -66999,7 +66999,7 @@
         <v>135357069</v>
       </c>
       <c r="B571" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -67115,7 +67115,7 @@
         <v>135357071</v>
       </c>
       <c r="B572" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -67231,7 +67231,7 @@
         <v>135357722</v>
       </c>
       <c r="B573" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -67351,7 +67351,7 @@
         <v>135356979</v>
       </c>
       <c r="B574" t="n">
-        <v>75373</v>
+        <v>75400</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -67467,7 +67467,7 @@
         <v>135350587</v>
       </c>
       <c r="B575" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -67583,7 +67583,7 @@
         <v>135356993</v>
       </c>
       <c r="B576" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -67699,7 +67699,7 @@
         <v>135357451</v>
       </c>
       <c r="B577" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -67815,7 +67815,7 @@
         <v>135350572</v>
       </c>
       <c r="B578" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -67931,7 +67931,7 @@
         <v>135350580</v>
       </c>
       <c r="B579" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -68047,7 +68047,7 @@
         <v>135351877</v>
       </c>
       <c r="B580" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -68163,7 +68163,7 @@
         <v>135354294</v>
       </c>
       <c r="B581" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -68279,7 +68279,7 @@
         <v>135354298</v>
       </c>
       <c r="B582" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -68395,7 +68395,7 @@
         <v>135356964</v>
       </c>
       <c r="B583" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -68511,7 +68511,7 @@
         <v>135356969</v>
       </c>
       <c r="B584" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -68627,7 +68627,7 @@
         <v>135357070</v>
       </c>
       <c r="B585" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -68743,7 +68743,7 @@
         <v>135357077</v>
       </c>
       <c r="B586" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -68859,7 +68859,7 @@
         <v>135357444</v>
       </c>
       <c r="B587" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -68975,7 +68975,7 @@
         <v>135357486</v>
       </c>
       <c r="B588" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -69091,7 +69091,7 @@
         <v>135357447</v>
       </c>
       <c r="B589" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -69212,7 +69212,7 @@
         <v>135361464</v>
       </c>
       <c r="B590" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -69328,7 +69328,7 @@
         <v>135350593</v>
       </c>
       <c r="B591" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -69444,7 +69444,7 @@
         <v>135356991</v>
       </c>
       <c r="B592" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -69560,7 +69560,7 @@
         <v>135357721</v>
       </c>
       <c r="B593" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -70879,7 +70879,7 @@
         <v>135354385</v>
       </c>
       <c r="B604" t="n">
-        <v>92703</v>
+        <v>92730</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -71111,7 +71111,7 @@
         <v>135354316</v>
       </c>
       <c r="B606" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -71227,7 +71227,7 @@
         <v>135356990</v>
       </c>
       <c r="B607" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -71343,7 +71343,7 @@
         <v>135357428</v>
       </c>
       <c r="B608" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -71459,7 +71459,7 @@
         <v>135357723</v>
       </c>
       <c r="B609" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>135363068</v>
       </c>
       <c r="B610" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -71691,7 +71691,7 @@
         <v>135357413</v>
       </c>
       <c r="B611" t="n">
-        <v>99141</v>
+        <v>99168</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -71807,7 +71807,7 @@
         <v>135351879</v>
       </c>
       <c r="B612" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -71923,7 +71923,7 @@
         <v>135350571</v>
       </c>
       <c r="B613" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>135357421</v>
       </c>
       <c r="B614" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -72155,7 +72155,7 @@
         <v>135356968</v>
       </c>
       <c r="B615" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -72271,7 +72271,7 @@
         <v>135357440</v>
       </c>
       <c r="B616" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -72387,7 +72387,7 @@
         <v>135354425</v>
       </c>
       <c r="B617" t="n">
-        <v>102591</v>
+        <v>102618</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -72504,7 +72504,7 @@
         <v>135351883</v>
       </c>
       <c r="B618" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -72620,7 +72620,7 @@
         <v>135351890</v>
       </c>
       <c r="B619" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -72736,7 +72736,7 @@
         <v>135351895</v>
       </c>
       <c r="B620" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -72852,7 +72852,7 @@
         <v>135357411</v>
       </c>
       <c r="B621" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -72968,7 +72968,7 @@
         <v>135357417</v>
       </c>
       <c r="B622" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -73084,7 +73084,7 @@
         <v>135357426</v>
       </c>
       <c r="B623" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -73200,7 +73200,7 @@
         <v>135357429</v>
       </c>
       <c r="B624" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -73316,7 +73316,7 @@
         <v>135351878</v>
       </c>
       <c r="B625" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -73432,7 +73432,7 @@
         <v>135351888</v>
       </c>
       <c r="B626" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -73548,7 +73548,7 @@
         <v>135356971</v>
       </c>
       <c r="B627" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -73664,7 +73664,7 @@
         <v>135357078</v>
       </c>
       <c r="B628" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -73780,7 +73780,7 @@
         <v>135357410</v>
       </c>
       <c r="B629" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -73896,7 +73896,7 @@
         <v>135357422</v>
       </c>
       <c r="B630" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -74012,7 +74012,7 @@
         <v>135357415</v>
       </c>
       <c r="B631" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -74128,7 +74128,7 @@
         <v>135357416</v>
       </c>
       <c r="B632" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -74244,7 +74244,7 @@
         <v>135357427</v>
       </c>
       <c r="B633" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -74360,7 +74360,7 @@
         <v>135380596</v>
       </c>
       <c r="B634" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -74476,7 +74476,7 @@
         <v>135357412</v>
       </c>
       <c r="B635" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -74592,7 +74592,7 @@
         <v>135351880</v>
       </c>
       <c r="B636" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -74708,7 +74708,7 @@
         <v>135357418</v>
       </c>
       <c r="B637" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -74824,7 +74824,7 @@
         <v>135357423</v>
       </c>
       <c r="B638" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -74940,7 +74940,7 @@
         <v>135356967</v>
       </c>
       <c r="B639" t="n">
-        <v>105825</v>
+        <v>105852</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -75052,7 +75052,7 @@
         <v>135351885</v>
       </c>
       <c r="B640" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -75168,7 +75168,7 @@
         <v>135356966</v>
       </c>
       <c r="B641" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -75284,7 +75284,7 @@
         <v>135350568</v>
       </c>
       <c r="B642" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -75400,7 +75400,7 @@
         <v>135350582</v>
       </c>
       <c r="B643" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -47591,7 +47591,7 @@
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr">
@@ -47707,7 +47707,7 @@
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr">
@@ -48635,7 +48635,7 @@
       </c>
       <c r="AX413" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström</t>
         </is>
       </c>
       <c r="AY413" t="inlineStr">
@@ -49332,7 +49332,7 @@
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr">
@@ -49680,7 +49680,7 @@
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr">
@@ -50261,7 +50261,7 @@
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
@@ -50377,7 +50377,7 @@
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr">
@@ -51189,7 +51189,7 @@
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
@@ -51658,7 +51658,7 @@
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr">
@@ -51890,7 +51890,7 @@
       </c>
       <c r="AX441" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY441" t="inlineStr">
@@ -52818,7 +52818,7 @@
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
@@ -52934,7 +52934,7 @@
       </c>
       <c r="AX450" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY450" t="inlineStr">
@@ -53166,7 +53166,7 @@
       </c>
       <c r="AX452" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY452" t="inlineStr">
@@ -54906,7 +54906,7 @@
       </c>
       <c r="AX467" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY467" t="inlineStr">
@@ -55975,7 +55975,7 @@
       </c>
       <c r="AX476" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY476" t="inlineStr">
@@ -59283,7 +59283,7 @@
       </c>
       <c r="AX504" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY504" t="inlineStr">
@@ -60680,7 +60680,7 @@
       </c>
       <c r="AX516" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, per-erik mukka, Helena Björnström, Jörgen Sundin, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY516" t="inlineStr">
@@ -63479,7 +63479,7 @@
       </c>
       <c r="AX540" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY540" t="inlineStr">
@@ -64059,7 +64059,7 @@
       </c>
       <c r="AX545" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY545" t="inlineStr">
@@ -64644,7 +64644,7 @@
       </c>
       <c r="AX550" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY550" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -47591,7 +47591,7 @@
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr">
@@ -47707,7 +47707,7 @@
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr">
@@ -48635,7 +48635,7 @@
       </c>
       <c r="AX413" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY413" t="inlineStr">
@@ -49332,7 +49332,7 @@
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr">
@@ -49680,7 +49680,7 @@
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr">
@@ -50029,7 +50029,7 @@
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr">
@@ -50261,7 +50261,7 @@
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
@@ -50377,7 +50377,7 @@
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr">
@@ -50841,7 +50841,7 @@
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
@@ -50957,7 +50957,7 @@
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
@@ -51189,7 +51189,7 @@
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
@@ -51658,7 +51658,7 @@
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr">
@@ -51890,7 +51890,7 @@
       </c>
       <c r="AX441" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY441" t="inlineStr">
@@ -52818,7 +52818,7 @@
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
@@ -52934,7 +52934,7 @@
       </c>
       <c r="AX450" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY450" t="inlineStr">
@@ -53166,7 +53166,7 @@
       </c>
       <c r="AX452" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY452" t="inlineStr">
@@ -54906,7 +54906,7 @@
       </c>
       <c r="AX467" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY467" t="inlineStr">
@@ -55975,7 +55975,7 @@
       </c>
       <c r="AX476" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY476" t="inlineStr">
@@ -59283,7 +59283,7 @@
       </c>
       <c r="AX504" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY504" t="inlineStr">
@@ -60680,7 +60680,7 @@
       </c>
       <c r="AX516" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, per-erik mukka, Helena Björnström, Jörgen Sundin, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY516" t="inlineStr">
@@ -63479,7 +63479,7 @@
       </c>
       <c r="AX540" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY540" t="inlineStr">
@@ -64059,7 +64059,7 @@
       </c>
       <c r="AX545" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY545" t="inlineStr">
@@ -64644,7 +64644,7 @@
       </c>
       <c r="AX550" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY550" t="inlineStr">
@@ -68956,7 +68956,7 @@
       </c>
       <c r="AX587" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY587" t="inlineStr">
@@ -72368,7 +72368,7 @@
       </c>
       <c r="AX616" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY616" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -50029,7 +50029,7 @@
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr">
@@ -50841,7 +50841,7 @@
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
@@ -50957,7 +50957,7 @@
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
@@ -68956,7 +68956,7 @@
       </c>
       <c r="AX587" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY587" t="inlineStr">
@@ -72368,7 +72368,7 @@
       </c>
       <c r="AX616" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY616" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -35500,7 +35500,7 @@
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd, Marie Persson</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
@@ -38052,7 +38052,7 @@
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
@@ -38289,7 +38289,7 @@
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -42253,7 +42253,7 @@
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
@@ -47127,7 +47127,7 @@
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AX479" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY479" t="inlineStr">
@@ -62314,7 +62314,7 @@
       </c>
       <c r="AX530" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
+          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
         </is>
       </c>
       <c r="AY530" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -35500,7 +35500,7 @@
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
@@ -36777,7 +36777,7 @@
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin, Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
@@ -38052,7 +38052,7 @@
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
@@ -38289,7 +38289,7 @@
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -42253,7 +42253,7 @@
       </c>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
@@ -43637,7 +43637,7 @@
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
@@ -45155,7 +45155,7 @@
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
@@ -47127,7 +47127,7 @@
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr">
@@ -47707,7 +47707,7 @@
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr">
@@ -51890,7 +51890,7 @@
       </c>
       <c r="AX441" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY441" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AX479" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY479" t="inlineStr">
@@ -59167,7 +59167,7 @@
       </c>
       <c r="AX503" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY503" t="inlineStr">
@@ -62314,7 +62314,7 @@
       </c>
       <c r="AX530" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Christina Boyd, Moa Turid Lövdahl, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, per-erik mukka, Lina Hällström, Jörgen Sundin, Cajsa Björkén, Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson, Cajsa Björkén, Jörgen Sundin, Lina Hällström, per-erik mukka, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Moa Turid Lövdahl, Christina Boyd</t>
         </is>
       </c>
       <c r="AY530" t="inlineStr">
@@ -67564,7 +67564,7 @@
       </c>
       <c r="AX575" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY575" t="inlineStr">
@@ -69778,7 +69778,7 @@
       </c>
       <c r="AX594" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY594" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -36777,7 +36777,7 @@
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin, Laura Dobrandt</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
@@ -43637,7 +43637,7 @@
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
@@ -45155,7 +45155,7 @@
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
@@ -47707,7 +47707,7 @@
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr">
@@ -51890,7 +51890,7 @@
       </c>
       <c r="AX441" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY441" t="inlineStr">
@@ -59167,7 +59167,7 @@
       </c>
       <c r="AX503" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY503" t="inlineStr">
@@ -67564,7 +67564,7 @@
       </c>
       <c r="AX575" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY575" t="inlineStr">
@@ -69778,7 +69778,7 @@
       </c>
       <c r="AX594" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY594" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135382760</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>135384331</v>
       </c>
       <c r="B3" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>135384288</v>
       </c>
       <c r="B5" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>135379254</v>
       </c>
       <c r="B6" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135379255</v>
       </c>
       <c r="B7" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135382735</v>
       </c>
       <c r="B8" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>135382750</v>
       </c>
       <c r="B9" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>135382772</v>
       </c>
       <c r="B10" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>135383974</v>
       </c>
       <c r="B11" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>135384144</v>
       </c>
       <c r="B12" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>135384270</v>
       </c>
       <c r="B13" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>135384286</v>
       </c>
       <c r="B14" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>135385128</v>
       </c>
       <c r="B15" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>135379238</v>
       </c>
       <c r="B19" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>135379243</v>
       </c>
       <c r="B20" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>135379248</v>
       </c>
       <c r="B21" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135379249</v>
       </c>
       <c r="B22" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>135379252</v>
       </c>
       <c r="B23" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>135382411</v>
       </c>
       <c r="B24" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>135382725</v>
       </c>
       <c r="B25" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135382733</v>
       </c>
       <c r="B26" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>135383965</v>
       </c>
       <c r="B27" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>135384150</v>
       </c>
       <c r="B28" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>135385952</v>
       </c>
       <c r="B29" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>135385965</v>
       </c>
       <c r="B30" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>135385966</v>
       </c>
       <c r="B31" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>135385973</v>
       </c>
       <c r="B32" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>135379246</v>
       </c>
       <c r="B33" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>135382064</v>
       </c>
       <c r="B34" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135382736</v>
       </c>
       <c r="B35" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>135383967</v>
       </c>
       <c r="B36" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>135384131</v>
       </c>
       <c r="B37" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>135384136</v>
       </c>
       <c r="B38" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>135384146</v>
       </c>
       <c r="B39" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>135384153</v>
       </c>
       <c r="B40" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>135384272</v>
       </c>
       <c r="B41" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>135385129</v>
       </c>
       <c r="B42" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>135386007</v>
       </c>
       <c r="B43" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>135379250</v>
       </c>
       <c r="B44" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>135382403</v>
       </c>
       <c r="B45" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>135383973</v>
       </c>
       <c r="B46" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>135385127</v>
       </c>
       <c r="B47" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>135379247</v>
       </c>
       <c r="B51" t="n">
-        <v>92406</v>
+        <v>92408</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>135357049</v>
       </c>
       <c r="B52" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>135357050</v>
       </c>
       <c r="B53" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>135384148</v>
       </c>
       <c r="B54" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>135385971</v>
       </c>
       <c r="B55" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>135387640</v>
       </c>
       <c r="B56" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>135382727</v>
       </c>
       <c r="B57" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>135382741</v>
       </c>
       <c r="B58" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>135382757</v>
       </c>
       <c r="B59" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>135385962</v>
       </c>
       <c r="B60" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>135382999</v>
       </c>
       <c r="B61" t="n">
-        <v>92400</v>
+        <v>92402</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>135380608</v>
       </c>
       <c r="B63" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>135382742</v>
       </c>
       <c r="B64" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>135382748</v>
       </c>
       <c r="B65" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>135382753</v>
       </c>
       <c r="B66" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>135382767</v>
       </c>
       <c r="B67" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>135382773</v>
       </c>
       <c r="B68" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>135382778</v>
       </c>
       <c r="B69" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>135383981</v>
       </c>
       <c r="B70" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>135383962</v>
       </c>
       <c r="B71" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>135383994</v>
       </c>
       <c r="B105" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>135384128</v>
       </c>
       <c r="B106" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>135385940</v>
       </c>
       <c r="B107" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>135385968</v>
       </c>
       <c r="B108" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>135385976</v>
       </c>
       <c r="B109" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>135385960</v>
       </c>
       <c r="B110" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>135385977</v>
       </c>
       <c r="B111" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>135382393</v>
       </c>
       <c r="B112" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>135357039</v>
       </c>
       <c r="B113" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>135385959</v>
       </c>
       <c r="B114" t="n">
-        <v>110238</v>
+        <v>110240</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>135385969</v>
       </c>
       <c r="B115" t="n">
-        <v>110238</v>
+        <v>110240</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>135358340</v>
       </c>
       <c r="B116" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>135382723</v>
       </c>
       <c r="B117" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>135382739</v>
       </c>
       <c r="B118" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>135383976</v>
       </c>
       <c r="B119" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>135385944</v>
       </c>
       <c r="B120" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>135382410</v>
       </c>
       <c r="B121" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>135382412</v>
       </c>
       <c r="B122" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>135384266</v>
       </c>
       <c r="B123" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>135384268</v>
       </c>
       <c r="B124" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>135384279</v>
       </c>
       <c r="B125" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>135384281</v>
       </c>
       <c r="B126" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>135384330</v>
       </c>
       <c r="B127" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>135385947</v>
       </c>
       <c r="B128" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>135385957</v>
       </c>
       <c r="B129" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>135382032</v>
       </c>
       <c r="B130" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>135384249</v>
       </c>
       <c r="B131" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135384258</v>
       </c>
       <c r="B132" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>135357042</v>
       </c>
       <c r="B133" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>135357048</v>
       </c>
       <c r="B134" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>135379237</v>
       </c>
       <c r="B135" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>135382041</v>
       </c>
       <c r="B136" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>135382721</v>
       </c>
       <c r="B137" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>135382730</v>
       </c>
       <c r="B138" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>135382770</v>
       </c>
       <c r="B139" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>135384251</v>
       </c>
       <c r="B140" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>135384256</v>
       </c>
       <c r="B141" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>135384278</v>
       </c>
       <c r="B142" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>135384291</v>
       </c>
       <c r="B143" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>135357041</v>
       </c>
       <c r="B144" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>135382744</v>
       </c>
       <c r="B145" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>135382754</v>
       </c>
       <c r="B146" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>135385964</v>
       </c>
       <c r="B147" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>135385967</v>
       </c>
       <c r="B148" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>135386008</v>
       </c>
       <c r="B149" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>135383990</v>
       </c>
       <c r="B150" t="n">
-        <v>99284</v>
+        <v>99286</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>135385954</v>
       </c>
       <c r="B151" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>135385951</v>
       </c>
       <c r="B152" t="n">
-        <v>98290</v>
+        <v>98292</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>135385942</v>
       </c>
       <c r="B153" t="n">
-        <v>99583</v>
+        <v>99585</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>135382724</v>
       </c>
       <c r="B154" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>135383978</v>
       </c>
       <c r="B155" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>135385955</v>
       </c>
       <c r="B156" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>135385946</v>
       </c>
       <c r="B157" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>135382758</v>
       </c>
       <c r="B158" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>135385950</v>
       </c>
       <c r="B159" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>135385958</v>
       </c>
       <c r="B160" t="n">
-        <v>102020</v>
+        <v>102022</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>135389393</v>
       </c>
       <c r="B161" t="n">
-        <v>105857</v>
+        <v>105859</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>135357037</v>
       </c>
       <c r="B162" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>135382722</v>
       </c>
       <c r="B163" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>135382737</v>
       </c>
       <c r="B164" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>135382743</v>
       </c>
       <c r="B165" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>135382755</v>
       </c>
       <c r="B166" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>135382759</v>
       </c>
       <c r="B167" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>135382768</v>
       </c>
       <c r="B168" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>135382777</v>
       </c>
       <c r="B169" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>135383977</v>
       </c>
       <c r="B170" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>135383986</v>
       </c>
       <c r="B171" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>135383995</v>
       </c>
       <c r="B172" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>135384133</v>
       </c>
       <c r="B173" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>135382053</v>
       </c>
       <c r="B174" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>135383947</v>
       </c>
       <c r="B175" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>135357031</v>
       </c>
       <c r="B177" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>135357033</v>
       </c>
       <c r="B178" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>135357035</v>
       </c>
       <c r="B179" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>135379257</v>
       </c>
       <c r="B180" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>135382440</v>
       </c>
       <c r="B181" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>135382442</v>
       </c>
       <c r="B182" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>135382445</v>
       </c>
       <c r="B183" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>135382448</v>
       </c>
       <c r="B184" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>135382763</v>
       </c>
       <c r="B185" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>135383940</v>
       </c>
       <c r="B186" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>135385134</v>
       </c>
       <c r="B187" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>135385983</v>
       </c>
       <c r="B188" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>135379260</v>
       </c>
       <c r="B189" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>135382055</v>
       </c>
       <c r="B190" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>135384325</v>
       </c>
       <c r="B191" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>135382762</v>
       </c>
       <c r="B192" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>135383937</v>
       </c>
       <c r="B193" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23008,7 +23008,7 @@
         <v>135385132</v>
       </c>
       <c r="B194" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>135384158</v>
       </c>
       <c r="B196" t="n">
-        <v>92406</v>
+        <v>92408</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>135385985</v>
       </c>
       <c r="B197" t="n">
-        <v>96501</v>
+        <v>96503</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>135386085</v>
       </c>
       <c r="B198" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>135382420</v>
       </c>
       <c r="B199" t="n">
-        <v>87695</v>
+        <v>87697</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>135385133</v>
       </c>
       <c r="B200" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>135384332</v>
       </c>
       <c r="B220" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>135384318</v>
       </c>
       <c r="B221" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>135383932</v>
       </c>
       <c r="B222" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>135384295</v>
       </c>
       <c r="B223" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>135384309</v>
       </c>
       <c r="B224" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>135384311</v>
       </c>
       <c r="B225" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>135384327</v>
       </c>
       <c r="B226" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>135384312</v>
       </c>
       <c r="B227" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>135384322</v>
       </c>
       <c r="B228" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>135382050</v>
       </c>
       <c r="B229" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>135382761</v>
       </c>
       <c r="B230" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>135384302</v>
       </c>
       <c r="B231" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>135384304</v>
       </c>
       <c r="B232" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>135384323</v>
       </c>
       <c r="B233" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>135384329</v>
       </c>
       <c r="B234" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>135383955</v>
       </c>
       <c r="B235" t="n">
-        <v>99284</v>
+        <v>99286</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>135383961</v>
       </c>
       <c r="B236" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>135383936</v>
       </c>
       <c r="B237" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>135383957</v>
       </c>
       <c r="B238" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>135382764</v>
       </c>
       <c r="B239" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>135383934</v>
       </c>
       <c r="B240" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>135383942</v>
       </c>
       <c r="B241" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>135383954</v>
       </c>
       <c r="B242" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>135383958</v>
       </c>
       <c r="B243" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>135383969</v>
       </c>
       <c r="B244" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>135354306</v>
       </c>
       <c r="B247" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>135386003</v>
       </c>
       <c r="B249" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>135350748</v>
       </c>
       <c r="B250" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>135354307</v>
       </c>
       <c r="B251" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>135383923</v>
       </c>
       <c r="B252" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>135357008</v>
       </c>
       <c r="B253" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>135383921</v>
       </c>
       <c r="B254" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>135383924</v>
       </c>
       <c r="B255" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>135383916</v>
       </c>
       <c r="B256" t="n">
-        <v>93163</v>
+        <v>93165</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>135382462</v>
       </c>
       <c r="B280" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>135379281</v>
       </c>
       <c r="B281" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>135351911</v>
       </c>
       <c r="B282" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>135383925</v>
       </c>
       <c r="B283" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>135353582</v>
       </c>
       <c r="B284" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>135358339</v>
       </c>
       <c r="B285" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33772,7 +33772,7 @@
         <v>135379275</v>
       </c>
       <c r="B286" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>135353577</v>
       </c>
       <c r="B287" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>135353581</v>
       </c>
       <c r="B288" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>135357058</v>
       </c>
       <c r="B289" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34236,7 +34236,7 @@
         <v>135383915</v>
       </c>
       <c r="B290" t="n">
-        <v>99284</v>
+        <v>99286</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>135353580</v>
       </c>
       <c r="B291" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>135358334</v>
       </c>
       <c r="B292" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>135358336</v>
       </c>
       <c r="B293" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>135358338</v>
       </c>
       <c r="B294" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>135361457</v>
       </c>
       <c r="B297" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>135357469</v>
       </c>
       <c r="B300" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>135357024</v>
       </c>
       <c r="B301" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35868,7 +35868,7 @@
         <v>135350629</v>
       </c>
       <c r="B304" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>135350753</v>
       </c>
       <c r="B305" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>135379266</v>
       </c>
       <c r="B306" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>135379272</v>
       </c>
       <c r="B307" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>135385139</v>
       </c>
       <c r="B308" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>135354411</v>
       </c>
       <c r="B309" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>135350627</v>
       </c>
       <c r="B311" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>135361715</v>
       </c>
       <c r="B312" t="n">
-        <v>92400</v>
+        <v>92402</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>135350628</v>
       </c>
       <c r="B313" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>135357021</v>
       </c>
       <c r="B354" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>135357016</v>
       </c>
       <c r="B355" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>135383931</v>
       </c>
       <c r="B356" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -42040,7 +42040,7 @@
         <v>135357437</v>
       </c>
       <c r="B357" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>135357465</v>
       </c>
       <c r="B358" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>135382449</v>
       </c>
       <c r="B359" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>135357026</v>
       </c>
       <c r="B360" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>135357013</v>
       </c>
       <c r="B361" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>135357015</v>
       </c>
       <c r="B362" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>135357435</v>
       </c>
       <c r="B363" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -42852,7 +42852,7 @@
         <v>135379271</v>
       </c>
       <c r="B364" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>135357019</v>
       </c>
       <c r="B365" t="n">
-        <v>105857</v>
+        <v>105859</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>135357028</v>
       </c>
       <c r="B366" t="n">
-        <v>105857</v>
+        <v>105859</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>135354408</v>
       </c>
       <c r="B367" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>135357014</v>
       </c>
       <c r="B368" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>135380604</v>
       </c>
       <c r="B371" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>135350612</v>
       </c>
       <c r="B372" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -43888,7 +43888,7 @@
         <v>135361453</v>
       </c>
       <c r="B373" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>135350613</v>
       </c>
       <c r="B376" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>135354304</v>
       </c>
       <c r="B377" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>135361454</v>
       </c>
       <c r="B378" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>135357432</v>
       </c>
       <c r="B395" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>135380601</v>
       </c>
       <c r="B398" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>135350666</v>
       </c>
       <c r="B401" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>135380602</v>
       </c>
       <c r="B402" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>135350644</v>
       </c>
       <c r="B403" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>135350649</v>
       </c>
       <c r="B404" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>135350658</v>
       </c>
       <c r="B405" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>135350665</v>
       </c>
       <c r="B406" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>135350758</v>
       </c>
       <c r="B407" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -47958,7 +47958,7 @@
         <v>135350760</v>
       </c>
       <c r="B408" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>135354420</v>
       </c>
       <c r="B409" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>135357478</v>
       </c>
       <c r="B410" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>135357482</v>
       </c>
       <c r="B411" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>135361459</v>
       </c>
       <c r="B412" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>135357476</v>
       </c>
       <c r="B418" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -49235,7 +49235,7 @@
         <v>135350651</v>
       </c>
       <c r="B419" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>135350659</v>
       </c>
       <c r="B420" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>135350663</v>
       </c>
       <c r="B421" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>135350672</v>
       </c>
       <c r="B422" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>135350757</v>
       </c>
       <c r="B423" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>135356998</v>
       </c>
       <c r="B424" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>135357474</v>
       </c>
       <c r="B425" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>135350643</v>
       </c>
       <c r="B426" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>135350646</v>
       </c>
       <c r="B427" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>135350650</v>
       </c>
       <c r="B428" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>135351926</v>
       </c>
       <c r="B429" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>135354300</v>
       </c>
       <c r="B430" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -50628,7 +50628,7 @@
         <v>135357064</v>
       </c>
       <c r="B431" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -50744,7 +50744,7 @@
         <v>135357473</v>
       </c>
       <c r="B432" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>135357480</v>
       </c>
       <c r="B433" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>135350654</v>
       </c>
       <c r="B434" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>135350657</v>
       </c>
       <c r="B435" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -51208,7 +51208,7 @@
         <v>135356995</v>
       </c>
       <c r="B436" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>135354312</v>
       </c>
       <c r="B437" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>135361460</v>
       </c>
       <c r="B438" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -52025,7 +52025,7 @@
         <v>135350645</v>
       </c>
       <c r="B443" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -52141,7 +52141,7 @@
         <v>135350648</v>
       </c>
       <c r="B444" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>135350759</v>
       </c>
       <c r="B445" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>135351925</v>
       </c>
       <c r="B448" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -56859,7 +56859,7 @@
         <v>135354302</v>
       </c>
       <c r="B484" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -56975,7 +56975,7 @@
         <v>135354390</v>
       </c>
       <c r="B485" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -57091,7 +57091,7 @@
         <v>135354391</v>
       </c>
       <c r="B486" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -57207,7 +57207,7 @@
         <v>135350637</v>
       </c>
       <c r="B487" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>135354389</v>
       </c>
       <c r="B488" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>135357431</v>
       </c>
       <c r="B489" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -57555,7 +57555,7 @@
         <v>135351924</v>
       </c>
       <c r="B490" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -58135,7 +58135,7 @@
         <v>135351935</v>
       </c>
       <c r="B495" t="n">
-        <v>92275</v>
+        <v>92277</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>135350728</v>
       </c>
       <c r="B496" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -58367,7 +58367,7 @@
         <v>135354377</v>
       </c>
       <c r="B497" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -58483,7 +58483,7 @@
         <v>135354423</v>
       </c>
       <c r="B498" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -58599,7 +58599,7 @@
         <v>135361466</v>
       </c>
       <c r="B499" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>135361449</v>
       </c>
       <c r="B508" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>135351897</v>
       </c>
       <c r="B510" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -60003,7 +60003,7 @@
         <v>135351929</v>
       </c>
       <c r="B511" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -60119,7 +60119,7 @@
         <v>135354318</v>
       </c>
       <c r="B512" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -60235,7 +60235,7 @@
         <v>135357068</v>
       </c>
       <c r="B513" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>135361446</v>
       </c>
       <c r="B519" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -61052,7 +61052,7 @@
         <v>135361447</v>
       </c>
       <c r="B520" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>135350581</v>
       </c>
       <c r="B521" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -61289,7 +61289,7 @@
         <v>135350674</v>
       </c>
       <c r="B522" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -61405,7 +61405,7 @@
         <v>135350740</v>
       </c>
       <c r="B523" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>135350763</v>
       </c>
       <c r="B524" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -61637,7 +61637,7 @@
         <v>135354382</v>
       </c>
       <c r="B525" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>135356975</v>
       </c>
       <c r="B526" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -61869,7 +61869,7 @@
         <v>135356977</v>
       </c>
       <c r="B527" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -61985,7 +61985,7 @@
         <v>135357066</v>
       </c>
       <c r="B528" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -62101,7 +62101,7 @@
         <v>135357076</v>
       </c>
       <c r="B529" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -62217,7 +62217,7 @@
         <v>135357445</v>
       </c>
       <c r="B530" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -62333,7 +62333,7 @@
         <v>135361445</v>
       </c>
       <c r="B531" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>135350730</v>
       </c>
       <c r="B532" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -62570,7 +62570,7 @@
         <v>135354295</v>
       </c>
       <c r="B533" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>135354297</v>
       </c>
       <c r="B534" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>135354322</v>
       </c>
       <c r="B535" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -62918,7 +62918,7 @@
         <v>135354383</v>
       </c>
       <c r="B536" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -63034,7 +63034,7 @@
         <v>135356976</v>
       </c>
       <c r="B537" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -63150,7 +63150,7 @@
         <v>135356983</v>
       </c>
       <c r="B538" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>135357441</v>
       </c>
       <c r="B539" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -63382,7 +63382,7 @@
         <v>135350675</v>
       </c>
       <c r="B540" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -64547,7 +64547,7 @@
         <v>135350673</v>
       </c>
       <c r="B550" t="n">
-        <v>92406</v>
+        <v>92408</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>135357450</v>
       </c>
       <c r="B551" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>135361448</v>
       </c>
       <c r="B552" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -64900,7 +64900,7 @@
         <v>135350590</v>
       </c>
       <c r="B553" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -65132,7 +65132,7 @@
         <v>135356973</v>
       </c>
       <c r="B555" t="n">
-        <v>96113</v>
+        <v>96115</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -65248,7 +65248,7 @@
         <v>135380594</v>
       </c>
       <c r="B556" t="n">
-        <v>96113</v>
+        <v>96115</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>135380599</v>
       </c>
       <c r="B557" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -65480,7 +65480,7 @@
         <v>135354296</v>
       </c>
       <c r="B558" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -65596,7 +65596,7 @@
         <v>135357067</v>
       </c>
       <c r="B559" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -65717,7 +65717,7 @@
         <v>135354381</v>
       </c>
       <c r="B560" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -65833,7 +65833,7 @@
         <v>135357072</v>
       </c>
       <c r="B561" t="n">
-        <v>91875</v>
+        <v>91877</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -70879,7 +70879,7 @@
         <v>135354385</v>
       </c>
       <c r="B604" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -71111,7 +71111,7 @@
         <v>135354316</v>
       </c>
       <c r="B606" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -71227,7 +71227,7 @@
         <v>135356990</v>
       </c>
       <c r="B607" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -71343,7 +71343,7 @@
         <v>135357428</v>
       </c>
       <c r="B608" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -71459,7 +71459,7 @@
         <v>135357723</v>
       </c>
       <c r="B609" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>135363068</v>
       </c>
       <c r="B610" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -71691,7 +71691,7 @@
         <v>135357413</v>
       </c>
       <c r="B611" t="n">
-        <v>99173</v>
+        <v>99175</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -71807,7 +71807,7 @@
         <v>135351879</v>
       </c>
       <c r="B612" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -71923,7 +71923,7 @@
         <v>135350571</v>
       </c>
       <c r="B613" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -72039,7 +72039,7 @@
         <v>135357421</v>
       </c>
       <c r="B614" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -72155,7 +72155,7 @@
         <v>135356968</v>
       </c>
       <c r="B615" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -72271,7 +72271,7 @@
         <v>135357440</v>
       </c>
       <c r="B616" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -72387,7 +72387,7 @@
         <v>135354425</v>
       </c>
       <c r="B617" t="n">
-        <v>102623</v>
+        <v>102625</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -72504,7 +72504,7 @@
         <v>135351883</v>
       </c>
       <c r="B618" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -72620,7 +72620,7 @@
         <v>135351890</v>
       </c>
       <c r="B619" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -72736,7 +72736,7 @@
         <v>135351895</v>
       </c>
       <c r="B620" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -72852,7 +72852,7 @@
         <v>135357411</v>
       </c>
       <c r="B621" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -72968,7 +72968,7 @@
         <v>135357417</v>
       </c>
       <c r="B622" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -73084,7 +73084,7 @@
         <v>135357426</v>
       </c>
       <c r="B623" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -73200,7 +73200,7 @@
         <v>135357429</v>
       </c>
       <c r="B624" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -73316,7 +73316,7 @@
         <v>135351878</v>
       </c>
       <c r="B625" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -73432,7 +73432,7 @@
         <v>135351888</v>
       </c>
       <c r="B626" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -73548,7 +73548,7 @@
         <v>135356971</v>
       </c>
       <c r="B627" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -73664,7 +73664,7 @@
         <v>135357078</v>
       </c>
       <c r="B628" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -73780,7 +73780,7 @@
         <v>135357410</v>
       </c>
       <c r="B629" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -73896,7 +73896,7 @@
         <v>135357422</v>
       </c>
       <c r="B630" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -74012,7 +74012,7 @@
         <v>135357415</v>
       </c>
       <c r="B631" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -74128,7 +74128,7 @@
         <v>135357416</v>
       </c>
       <c r="B632" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -74244,7 +74244,7 @@
         <v>135357427</v>
       </c>
       <c r="B633" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -74360,7 +74360,7 @@
         <v>135380596</v>
       </c>
       <c r="B634" t="n">
-        <v>98290</v>
+        <v>98292</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -74476,7 +74476,7 @@
         <v>135357412</v>
       </c>
       <c r="B635" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -74592,7 +74592,7 @@
         <v>135351880</v>
       </c>
       <c r="B636" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -74708,7 +74708,7 @@
         <v>135357418</v>
       </c>
       <c r="B637" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -74824,7 +74824,7 @@
         <v>135357423</v>
       </c>
       <c r="B638" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -74940,7 +74940,7 @@
         <v>135356967</v>
       </c>
       <c r="B639" t="n">
-        <v>105857</v>
+        <v>105859</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -75052,7 +75052,7 @@
         <v>135351885</v>
       </c>
       <c r="B640" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -75168,7 +75168,7 @@
         <v>135356966</v>
       </c>
       <c r="B641" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135382760</v>
       </c>
       <c r="B2" t="n">
-        <v>92000</v>
+        <v>92014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>135382999</v>
       </c>
       <c r="B61" t="n">
-        <v>92402</v>
+        <v>92414</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>135386085</v>
       </c>
       <c r="B198" t="n">
-        <v>92275</v>
+        <v>92289</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>135383921</v>
       </c>
       <c r="B254" t="n">
-        <v>92446</v>
+        <v>92460</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>135350605</v>
       </c>
       <c r="B493" t="n">
-        <v>80335</v>
+        <v>80337</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29879,48 +29879,51 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135357008</v>
+        <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>92446</v>
+        <v>93179</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4217</v>
+        <v>2055</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Olivinkremla</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Russula olivina</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Ruots. &amp; Vauras</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>599335</v>
+        <v>598772</v>
       </c>
       <c r="R253" t="n">
-        <v>7331086</v>
+        <v>7330870</v>
       </c>
       <c r="S253" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -29944,47 +29947,48 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Kollekt samlat. 2-sporig. Sekvenseras inom projektet Boreala Svampskogar.  Äldre granskog, hög bonitet, rörligt markvatten, mosaik med översilat, bitvis mindre bäckar, glupar och torrare partier. Örtrikt med orkideér, nordisk stormhatt, torta, violer, midsommarblomster, pyrolor,</t>
         </is>
       </c>
       <c r="AD253" t="b">
         <v>0</v>
       </c>
       <c r="AE253" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF253" t="inlineStr"/>
       <c r="AG253" t="b">
         <v>0</v>
       </c>
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -29994,16 +29998,16 @@
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135357008</t>
+          <t>https://artportalen.se/Sighting/135383916</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135383921</v>
+        <v>135357008</v>
       </c>
       <c r="B254" t="n">
-        <v>92460</v>
+        <v>92446</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30031,17 +30035,17 @@
       <c r="I254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>598743</v>
+        <v>599335</v>
       </c>
       <c r="R254" t="n">
-        <v>7331037</v>
+        <v>7331086</v>
       </c>
       <c r="S254" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -30065,27 +30069,27 @@
       </c>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -30100,12 +30104,12 @@
       <c r="AT254" t="inlineStr"/>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
@@ -30115,16 +30119,16 @@
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135383921</t>
+          <t>https://artportalen.se/Sighting/135357008</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>135383924</v>
+        <v>135383921</v>
       </c>
       <c r="B255" t="n">
-        <v>92446</v>
+        <v>92460</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30156,10 +30160,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>598716</v>
+        <v>598743</v>
       </c>
       <c r="R255" t="n">
-        <v>7331115</v>
+        <v>7331037</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -30191,7 +30195,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -30201,7 +30205,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC255" t="inlineStr">
@@ -30236,54 +30240,51 @@
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135383924</t>
+          <t>https://artportalen.se/Sighting/135383921</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>135383916</v>
+        <v>135383924</v>
       </c>
       <c r="B256" t="n">
-        <v>93165</v>
+        <v>92446</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5906</v>
+        <v>4217</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Olivbrun kremla</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Russula olivobrunnea</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Ruots. &amp; Vauras</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
           <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>598772</v>
+        <v>598716</v>
       </c>
       <c r="R256" t="n">
-        <v>7330870</v>
+        <v>7331115</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -30315,7 +30316,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -30325,21 +30326,20 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>Kollekt samlat. Sekvenseras inom projektet Boreala Svampskogar.  Äldre granskog, hög bonitet, rörligt markvatten, mosaik med översilat, bitvis mindre bäckar, glupar och torrare partier. Örtrikt med orkideér, nordisk stormhatt, torta, violer, midsommarblomster, pyrolor,</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD256" t="b">
         <v>0</v>
       </c>
       <c r="AE256" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF256" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG256" t="b">
         <v>0</v>
       </c>
@@ -30361,7 +30361,7 @@
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135383916</t>
+          <t>https://artportalen.se/Sighting/135383924</t>
         </is>
       </c>
     </row>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93179</v>
+        <v>93180</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>135350605</v>
       </c>
       <c r="B493" t="n">
-        <v>80337</v>
+        <v>80338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93180</v>
+        <v>93181</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93181</v>
+        <v>93182</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>135350605</v>
       </c>
       <c r="B493" t="n">
-        <v>80338</v>
+        <v>80339</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93182</v>
+        <v>93188</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>135350605</v>
       </c>
       <c r="B493" t="n">
-        <v>80339</v>
+        <v>80343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93188</v>
+        <v>93189</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>135350605</v>
       </c>
       <c r="B493" t="n">
-        <v>80343</v>
+        <v>80344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93189</v>
+        <v>93195</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93195</v>
+        <v>93202</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93202</v>
+        <v>93203</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93203</v>
+        <v>93216</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93216</v>
+        <v>93217</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
